--- a/research/traditional_assets/database/data/bermuda/bermuda_information_services.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_information_services.xlsx
@@ -650,10 +650,10 @@
         <v>0.3299825827320229</v>
       </c>
       <c r="X2">
-        <v>0.1151669029296562</v>
+        <v>0.1151384933289879</v>
       </c>
       <c r="Y2">
-        <v>0.2148156798023667</v>
+        <v>0.214844089403035</v>
       </c>
       <c r="Z2">
         <v>3.481385581723464</v>
@@ -662,10 +662,10 @@
         <v>0.5162786456156404</v>
       </c>
       <c r="AB2">
-        <v>0.1058867324728055</v>
+        <v>0.1058639340558001</v>
       </c>
       <c r="AC2">
-        <v>0.4103919131428349</v>
+        <v>0.4104147115598403</v>
       </c>
       <c r="AD2">
         <v>1646.1</v>
@@ -787,10 +787,10 @@
         <v>0.3299825827320229</v>
       </c>
       <c r="X3">
-        <v>0.1151669029296562</v>
+        <v>0.1151384933289879</v>
       </c>
       <c r="Y3">
-        <v>0.2148156798023667</v>
+        <v>0.214844089403035</v>
       </c>
       <c r="Z3">
         <v>3.481385581723464</v>
@@ -799,10 +799,10 @@
         <v>0.5162786456156404</v>
       </c>
       <c r="AB3">
-        <v>0.1058867324728055</v>
+        <v>0.1058639340558001</v>
       </c>
       <c r="AC3">
-        <v>0.4103919131428349</v>
+        <v>0.4104147115598403</v>
       </c>
       <c r="AD3">
         <v>1646.1</v>
@@ -1157,13 +1157,13 @@
         <v>7574.7</v>
       </c>
       <c r="L2">
-        <v>9871.4002674082</v>
+        <v>9871.409639791211</v>
       </c>
       <c r="M2">
         <v>8416.39754668046</v>
       </c>
       <c r="N2">
-        <v>8848.8002674082</v>
+        <v>8848.8096397912</v>
       </c>
       <c r="O2">
         <v>1864.29754668046</v>
@@ -1172,16 +1172,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.105886732472806</v>
+        <v>0.1058639340558</v>
       </c>
       <c r="R2">
-        <v>0.101466237545114</v>
+        <v>0.101443439128109</v>
       </c>
       <c r="S2">
         <v>0.0681811058765187</v>
       </c>
       <c r="T2">
-        <v>0.0600811058765187</v>
+        <v>0.0586811058765187</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.115166902929656</v>
+        <v>0.115138493328988</v>
       </c>
       <c r="X2">
-        <v>0.101466237545114</v>
+        <v>0.101443439128109</v>
       </c>
       <c r="Y2">
         <v>1.26995885599346</v>
@@ -1236,7 +1236,7 @@
         <v>7574.7</v>
       </c>
       <c r="AK2">
-        <v>0.05462137816692637</v>
+        <v>0.05459900767788711</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.1014662375451144</v>
+        <v>0.101443439128109</v>
       </c>
       <c r="C2">
-        <v>9871.400267408202</v>
+        <v>9871.409639791205</v>
       </c>
       <c r="D2">
-        <v>8848.800267408202</v>
+        <v>8848.809639791205</v>
       </c>
       <c r="E2">
         <v>-1864.297546680461</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.1014662375451144</v>
+        <v>0.101443439128109</v>
       </c>
       <c r="T2">
         <v>1.01912912879999</v>
       </c>
       <c r="U2">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V2">
         <v>0</v>
       </c>
       <c r="W2">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1016090486038796</v>
+        <v>0.1015722501868742</v>
       </c>
       <c r="C3">
-        <v>9762.347479762813</v>
+        <v>9763.791822431904</v>
       </c>
       <c r="D3">
-        <v>8834.137455229618</v>
+        <v>8835.581797898709</v>
       </c>
       <c r="E3">
         <v>-1769.907571213656</v>
@@ -1539,37 +1539,37 @@
         <v>803.5</v>
       </c>
       <c r="M3">
-        <v>5.671054109703094</v>
+        <v>5.538908144049567</v>
       </c>
       <c r="N3">
-        <v>797.8289458902969</v>
+        <v>797.9610918559505</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>797.8289458902969</v>
+        <v>797.9610918559505</v>
       </c>
       <c r="Q3">
-        <v>825.2289458902969</v>
+        <v>825.3610918559505</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1020285227728429</v>
+        <v>0.102005494068797</v>
       </c>
       <c r="T3">
         <v>1.029423362424232</v>
       </c>
       <c r="U3">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V3">
         <v>0</v>
       </c>
       <c r="W3">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>141.6844178272295</v>
+        <v>145.0646912899608</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1017518596626448</v>
+        <v>0.1017010612456394</v>
       </c>
       <c r="C4">
-        <v>9653.34320544886</v>
+        <v>9656.213493915098</v>
       </c>
       <c r="D4">
-        <v>8819.523156382469</v>
+        <v>8822.393444848707</v>
       </c>
       <c r="E4">
         <v>-1675.517595746852</v>
@@ -1621,37 +1621,37 @@
         <v>803.5</v>
       </c>
       <c r="M4">
-        <v>11.34210821940619</v>
+        <v>11.07781628809913</v>
       </c>
       <c r="N4">
-        <v>792.1578917805938</v>
+        <v>792.4221837119009</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>792.1578917805938</v>
+        <v>792.4221837119009</v>
       </c>
       <c r="Q4">
-        <v>819.5578917805938</v>
+        <v>819.8221837119008</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1026022832093005</v>
+        <v>0.1025790195184786</v>
       </c>
       <c r="T4">
         <v>1.039927682448969</v>
       </c>
       <c r="U4">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V4">
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>70.84220891361474</v>
+        <v>72.53234564498038</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.10189467072141</v>
+        <v>0.1018298723044046</v>
       </c>
       <c r="C5">
-        <v>9544.387204097402</v>
+        <v>9548.674477676313</v>
       </c>
       <c r="D5">
-        <v>8804.957130497816</v>
+        <v>8809.244404076728</v>
       </c>
       <c r="E5">
         <v>-1581.127620280047</v>
@@ -1703,37 +1703,37 @@
         <v>803.5</v>
       </c>
       <c r="M5">
-        <v>17.01316232910928</v>
+        <v>16.6167244321487</v>
       </c>
       <c r="N5">
-        <v>786.4868376708907</v>
+        <v>786.8832755678513</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>786.4868376708907</v>
+        <v>786.8832755678513</v>
       </c>
       <c r="Q5">
-        <v>813.8868376708907</v>
+        <v>814.2832755678513</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1031878737578499</v>
+        <v>0.1031643702351639</v>
       </c>
       <c r="T5">
         <v>1.050648586391742</v>
       </c>
       <c r="U5">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V5">
         <v>0</v>
       </c>
       <c r="W5">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>47.22813927574317</v>
+        <v>48.35489709665359</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1020374817801752</v>
+        <v>0.1019586833631698</v>
       </c>
       <c r="C6">
-        <v>9435.479236924839</v>
+        <v>9441.174598202138</v>
       </c>
       <c r="D6">
-        <v>8790.439138792057</v>
+        <v>8796.134500069356</v>
       </c>
       <c r="E6">
         <v>-1486.737644813242</v>
@@ -1785,37 +1785,37 @@
         <v>803.5</v>
       </c>
       <c r="M6">
-        <v>22.68421643881237</v>
+        <v>22.15563257619827</v>
       </c>
       <c r="N6">
-        <v>780.8157835611876</v>
+        <v>781.3443674238017</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>780.8157835611876</v>
+        <v>781.3443674238017</v>
       </c>
       <c r="Q6">
-        <v>808.2157835611875</v>
+        <v>808.7443674238017</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1037856641094942</v>
+        <v>0.1037619157584469</v>
       </c>
       <c r="T6">
         <v>1.061592842499989</v>
       </c>
       <c r="U6">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V6">
         <v>0</v>
       </c>
       <c r="W6">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>35.42110445680737</v>
+        <v>36.26617282249019</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1021802928389404</v>
+        <v>0.102087494421935</v>
       </c>
       <c r="C7">
-        <v>9326.619066719837</v>
+        <v>9333.713681022396</v>
       </c>
       <c r="D7">
-        <v>8775.96894405386</v>
+        <v>8783.06355835642</v>
       </c>
       <c r="E7">
         <v>-1392.347669346438</v>
@@ -1867,37 +1867,37 @@
         <v>803.5</v>
       </c>
       <c r="M7">
-        <v>28.35527054851547</v>
+        <v>27.69454072024784</v>
       </c>
       <c r="N7">
-        <v>775.1447294514845</v>
+        <v>775.8054592797522</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>775.1447294514845</v>
+        <v>775.8054592797522</v>
       </c>
       <c r="Q7">
-        <v>802.5447294514845</v>
+        <v>803.2054592797522</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1043960395211731</v>
+        <v>0.1043720411874832</v>
       </c>
       <c r="T7">
         <v>1.072767503999989</v>
       </c>
       <c r="U7">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V7">
         <v>0</v>
       </c>
       <c r="W7">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>28.3368835654459</v>
+        <v>29.01293825799215</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1023231038977056</v>
+        <v>0.1022163054807001</v>
       </c>
       <c r="C8">
-        <v>9217.806457830424</v>
+        <v>9226.291552702423</v>
       </c>
       <c r="D8">
-        <v>8761.546310631251</v>
+        <v>8770.03140550325</v>
       </c>
       <c r="E8">
         <v>-1297.957693879633</v>
@@ -1949,37 +1949,37 @@
         <v>803.5</v>
       </c>
       <c r="M8">
-        <v>34.02632465821856</v>
+        <v>33.2334488642974</v>
       </c>
       <c r="N8">
-        <v>769.4736753417815</v>
+        <v>770.2665511357026</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>769.4736753417815</v>
+        <v>770.2665511357026</v>
       </c>
       <c r="Q8">
-        <v>796.8736753417814</v>
+        <v>797.6665511357025</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1050194016437388</v>
+        <v>0.1049951480086266</v>
       </c>
       <c r="T8">
         <v>1.084179924255308</v>
       </c>
       <c r="U8">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.61406963787158</v>
+        <v>24.17744854832679</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1024659149564708</v>
+        <v>0.1023451165394653</v>
       </c>
       <c r="C9">
-        <v>9109.04117615118</v>
+        <v>9118.908040835375</v>
       </c>
       <c r="D9">
-        <v>8747.171004418813</v>
+        <v>8757.037869103007</v>
       </c>
       <c r="E9">
         <v>-1203.567718412829</v>
@@ -2031,37 +2031,37 @@
         <v>803.5</v>
       </c>
       <c r="M9">
-        <v>39.69737876792166</v>
+        <v>38.77235700834697</v>
       </c>
       <c r="N9">
-        <v>763.8026212320783</v>
+        <v>764.7276429916531</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>763.8026212320783</v>
+        <v>764.7276429916531</v>
       </c>
       <c r="Q9">
-        <v>791.2026212320783</v>
+        <v>792.127642991653</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1056561694033489</v>
+        <v>0.1056316549764613</v>
       </c>
       <c r="T9">
         <v>1.095837772903214</v>
       </c>
       <c r="U9">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V9">
         <v>0</v>
       </c>
       <c r="W9">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.24063111817564</v>
+        <v>20.72352732713725</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1026087260152359</v>
+        <v>0.1024739275982305</v>
       </c>
       <c r="C10">
-        <v>9000.322989110593</v>
+        <v>9011.562974034649</v>
       </c>
       <c r="D10">
-        <v>8732.842792845029</v>
+        <v>8744.082777769085</v>
       </c>
       <c r="E10">
         <v>-1109.177742946024</v>
@@ -2113,37 +2113,37 @@
         <v>803.5</v>
       </c>
       <c r="M10">
-        <v>45.36843287762475</v>
+        <v>44.31126515239654</v>
       </c>
       <c r="N10">
-        <v>758.1315671223753</v>
+        <v>759.1887348476034</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>758.1315671223753</v>
+        <v>759.1887348476034</v>
       </c>
       <c r="Q10">
-        <v>785.5315671223752</v>
+        <v>786.5887348476034</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1063067799403418</v>
+        <v>0.1062819990522924</v>
       </c>
       <c r="T10">
         <v>1.107749053043467</v>
       </c>
       <c r="U10">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.71055222840369</v>
+        <v>18.1330864112451</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1027515370740011</v>
+        <v>0.1026027386569957</v>
       </c>
       <c r="C11">
-        <v>8891.651665658494</v>
+        <v>8904.256181926319</v>
       </c>
       <c r="D11">
-        <v>8718.561444859735</v>
+        <v>8731.165961127561</v>
       </c>
       <c r="E11">
         <v>-1014.787767479219</v>
@@ -2195,37 +2195,37 @@
         <v>803.5</v>
       </c>
       <c r="M11">
-        <v>51.03948698732783</v>
+        <v>49.8501732964461</v>
       </c>
       <c r="N11">
-        <v>752.4605130126722</v>
+        <v>753.6498267035539</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>752.4605130126722</v>
+        <v>753.6498267035539</v>
       </c>
       <c r="Q11">
-        <v>779.8605130126722</v>
+        <v>781.0498267035539</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1069716896100159</v>
+        <v>0.1069466364045154</v>
       </c>
       <c r="T11">
         <v>1.119922119560428</v>
       </c>
       <c r="U11">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V11">
         <v>0</v>
       </c>
       <c r="W11">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.74271309191439</v>
+        <v>16.11829903221786</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1028943481327663</v>
+        <v>0.1027315497157609</v>
       </c>
       <c r="C12">
-        <v>8783.026976253655</v>
+        <v>8796.987495141708</v>
       </c>
       <c r="D12">
-        <v>8704.326730921701</v>
+        <v>8718.287249809753</v>
       </c>
       <c r="E12">
         <v>-920.3977920124148</v>
@@ -2277,37 +2277,37 @@
         <v>803.5</v>
       </c>
       <c r="M12">
-        <v>56.71054109703093</v>
+        <v>55.38908144049567</v>
       </c>
       <c r="N12">
-        <v>746.789458902969</v>
+        <v>748.1109185595043</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>746.789458902969</v>
+        <v>748.1109185595043</v>
       </c>
       <c r="Q12">
-        <v>774.189458902969</v>
+        <v>775.5109185595043</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1076513750501272</v>
+        <v>0.1076260434756767</v>
       </c>
       <c r="T12">
         <v>1.132365698666655</v>
       </c>
       <c r="U12">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.16844178272295</v>
+        <v>14.50646912899608</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1030371591915315</v>
+        <v>0.1028603607745261</v>
       </c>
       <c r="C13">
-        <v>8674.448692851473</v>
+        <v>8689.75674530994</v>
       </c>
       <c r="D13">
-        <v>8690.138422986323</v>
+        <v>8705.446475444791</v>
       </c>
       <c r="E13">
         <v>-826.0078165456102</v>
@@ -2359,37 +2359,37 @@
         <v>803.5</v>
       </c>
       <c r="M13">
-        <v>62.38159520673403</v>
+        <v>60.92798958454524</v>
       </c>
       <c r="N13">
-        <v>741.118404793266</v>
+        <v>742.5720104154548</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>741.118404793266</v>
+        <v>742.5720104154548</v>
       </c>
       <c r="Q13">
-        <v>768.518404793266</v>
+        <v>769.9720104154547</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1083463343203533</v>
+        <v>0.1083207181214708</v>
       </c>
       <c r="T13">
         <v>1.145088908764033</v>
       </c>
       <c r="U13">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V13">
         <v>0</v>
       </c>
       <c r="W13">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.88040162065723</v>
+        <v>13.18769920817825</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1031799702502967</v>
+        <v>0.1029891718332913</v>
       </c>
       <c r="C14">
-        <v>8565.916588891823</v>
+        <v>8582.563765050638</v>
       </c>
       <c r="D14">
-        <v>8675.996294493478</v>
+        <v>8692.643470652292</v>
       </c>
       <c r="E14">
         <v>-731.6178410788057</v>
@@ -2441,37 +2441,37 @@
         <v>803.5</v>
       </c>
       <c r="M14">
-        <v>68.05264931643711</v>
+        <v>66.4668977285948</v>
       </c>
       <c r="N14">
-        <v>735.4473506835629</v>
+        <v>737.0331022714051</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>735.4473506835629</v>
+        <v>737.0331022714051</v>
       </c>
       <c r="Q14">
-        <v>762.8473506835629</v>
+        <v>764.4331022714051</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1090570881194482</v>
+        <v>0.1090311808273966</v>
       </c>
       <c r="T14">
         <v>1.158101282727261</v>
       </c>
       <c r="U14">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V14">
         <v>0</v>
       </c>
       <c r="W14">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.80703481893579</v>
+        <v>12.0887242741634</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1033227813090619</v>
+        <v>0.1031179828920565</v>
       </c>
       <c r="C15">
-        <v>8457.430439286953</v>
+        <v>8475.408387966621</v>
       </c>
       <c r="D15">
-        <v>8661.900120355413</v>
+        <v>8679.878069035081</v>
       </c>
       <c r="E15">
         <v>-637.2278656120011</v>
@@ -2523,37 +2523,37 @@
         <v>803.5</v>
       </c>
       <c r="M15">
-        <v>73.7237034261402</v>
+        <v>72.00580587264436</v>
       </c>
       <c r="N15">
-        <v>729.7762965738598</v>
+        <v>731.4941941273556</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>729.7762965738598</v>
+        <v>731.4941941273556</v>
       </c>
       <c r="Q15">
-        <v>757.1762965738598</v>
+        <v>758.8941941273556</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1097841810863384</v>
+        <v>0.1097579760093207</v>
       </c>
       <c r="T15">
         <v>1.171412791724126</v>
       </c>
       <c r="U15">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.89880137132535</v>
+        <v>11.15882240692006</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1034655923678271</v>
+        <v>0.1032467939508216</v>
       </c>
       <c r="C16">
-        <v>8348.99002040959</v>
+        <v>8368.29044863673</v>
       </c>
       <c r="D16">
-        <v>8647.849676944854</v>
+        <v>8667.150105171993</v>
       </c>
       <c r="E16">
         <v>-542.8378901451963</v>
@@ -2605,37 +2605,37 @@
         <v>803.5</v>
       </c>
       <c r="M16">
-        <v>79.39475753584331</v>
+        <v>77.54471401669394</v>
       </c>
       <c r="N16">
-        <v>724.1052424641567</v>
+        <v>725.9552859833061</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>724.1052424641567</v>
+        <v>725.9552859833061</v>
       </c>
       <c r="Q16">
-        <v>751.5052424641567</v>
+        <v>753.3552859833061</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1105281831919935</v>
+        <v>0.1105016734047779</v>
       </c>
       <c r="T16">
         <v>1.185033870697662</v>
       </c>
       <c r="U16">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.12031555908782</v>
+        <v>10.36176366356863</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1036084034265922</v>
+        <v>0.1033756050095868</v>
       </c>
       <c r="C17">
-        <v>8240.595110081076</v>
+        <v>8261.209782608648</v>
       </c>
       <c r="D17">
-        <v>8633.844742083145</v>
+        <v>8654.459414610717</v>
       </c>
       <c r="E17">
         <v>-448.447914678392</v>
@@ -2687,37 +2687,37 @@
         <v>803.5</v>
       </c>
       <c r="M17">
-        <v>85.06581164554639</v>
+        <v>83.08362216074349</v>
       </c>
       <c r="N17">
-        <v>718.4341883544536</v>
+        <v>720.4163778392565</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>718.4341883544536</v>
+        <v>720.4163778392565</v>
       </c>
       <c r="Q17">
-        <v>745.8341883544535</v>
+        <v>747.8163778392565</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1112896912295464</v>
+        <v>0.1112628695624812</v>
       </c>
       <c r="T17">
         <v>1.198975445647047</v>
       </c>
       <c r="U17">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V17">
         <v>0</v>
       </c>
       <c r="W17">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.445627855148633</v>
+        <v>9.67097941933072</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1037512144853574</v>
+        <v>0.103504416068352</v>
       </c>
       <c r="C18">
-        <v>8132.245487559684</v>
+        <v>8154.166226391849</v>
       </c>
       <c r="D18">
-        <v>8619.885095028558</v>
+        <v>8641.805833860722</v>
       </c>
       <c r="E18">
         <v>-354.0579392115872</v>
@@ -2769,37 +2769,37 @@
         <v>803.5</v>
       </c>
       <c r="M18">
-        <v>90.7368657552495</v>
+        <v>88.62253030479307</v>
       </c>
       <c r="N18">
-        <v>712.7631342447505</v>
+        <v>714.877469695207</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>712.7631342447505</v>
+        <v>714.877469695207</v>
       </c>
       <c r="Q18">
-        <v>740.1631342447505</v>
+        <v>742.2774696952069</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1120693304108505</v>
+        <v>0.112042189438225</v>
       </c>
       <c r="T18">
         <v>1.21324896285713</v>
       </c>
       <c r="U18">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0.06008110587651873</v>
+        <v>0.05868110587651873</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.855276114201843</v>
+        <v>9.066543205622548</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1040810255441226</v>
+        <v>0.1038882271271172</v>
       </c>
       <c r="C19">
-        <v>8005.788653104462</v>
+        <v>8022.291516482552</v>
       </c>
       <c r="D19">
-        <v>8587.818236040141</v>
+        <v>8604.32109941823</v>
       </c>
       <c r="E19">
         <v>-259.6679637447826</v>
@@ -2851,37 +2851,37 @@
         <v>803.5</v>
       </c>
       <c r="M19">
-        <v>98.17301240618183</v>
+        <v>96.56838282324614</v>
       </c>
       <c r="N19">
-        <v>705.3269875938182</v>
+        <v>706.9316171767539</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>705.3269875938182</v>
+        <v>706.9316171767539</v>
       </c>
       <c r="Q19">
-        <v>732.7269875938182</v>
+        <v>734.3316171767539</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1128677560784511</v>
+        <v>0.1128402881061555</v>
       </c>
       <c r="T19">
         <v>1.227866420240951</v>
       </c>
       <c r="U19">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.18453035418321</v>
+        <v>8.320528691783993</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1042348366028878</v>
+        <v>0.1040320381858824</v>
       </c>
       <c r="C20">
-        <v>7896.525377989897</v>
+        <v>7913.939912716588</v>
       </c>
       <c r="D20">
-        <v>8572.94493639238</v>
+        <v>8590.359471119071</v>
       </c>
       <c r="E20">
         <v>-165.277988277978</v>
@@ -2933,37 +2933,37 @@
         <v>803.5</v>
       </c>
       <c r="M20">
-        <v>103.9478954888984</v>
+        <v>102.2488759304959</v>
       </c>
       <c r="N20">
-        <v>699.5521045111016</v>
+        <v>701.251124069504</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>699.5521045111016</v>
+        <v>701.251124069504</v>
       </c>
       <c r="Q20">
-        <v>726.9521045111015</v>
+        <v>728.651124069504</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1136856555428225</v>
+        <v>0.1136578525952549</v>
       </c>
       <c r="T20">
         <v>1.242840400975597</v>
       </c>
       <c r="U20">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.729834223395254</v>
+        <v>7.858277097795993</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.104388647661653</v>
+        <v>0.1041758492446476</v>
       </c>
       <c r="C21">
-        <v>7787.313532138249</v>
+        <v>7805.633544659622</v>
       </c>
       <c r="D21">
-        <v>8558.123066007536</v>
+        <v>8576.44307852891</v>
       </c>
       <c r="E21">
         <v>-70.88801281117344</v>
@@ -3015,37 +3015,37 @@
         <v>803.5</v>
       </c>
       <c r="M21">
-        <v>109.722778571615</v>
+        <v>107.9293690377457</v>
       </c>
       <c r="N21">
-        <v>693.777221428385</v>
+        <v>695.5706309622543</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>693.777221428385</v>
+        <v>695.5706309622543</v>
       </c>
       <c r="Q21">
-        <v>721.177221428385</v>
+        <v>722.9706309622543</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1145237500556968</v>
+        <v>0.114495603861863</v>
       </c>
       <c r="T21">
         <v>1.258184109629617</v>
       </c>
       <c r="U21">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.323000843216557</v>
+        <v>7.444683566333046</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1045424587204182</v>
+        <v>0.1043196603034128</v>
       </c>
       <c r="C22">
-        <v>7678.152849259853</v>
+        <v>7697.372192821521</v>
       </c>
       <c r="D22">
-        <v>8543.352358595945</v>
+        <v>8562.571702157613</v>
       </c>
       <c r="E22">
         <v>23.50196265563136</v>
@@ -3097,37 +3097,37 @@
         <v>803.5</v>
       </c>
       <c r="M22">
-        <v>115.4976616543316</v>
+        <v>113.6098621449955</v>
       </c>
       <c r="N22">
-        <v>688.0023383456685</v>
+        <v>689.8901378550045</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>688.0023383456685</v>
+        <v>689.8901378550045</v>
       </c>
       <c r="Q22">
-        <v>715.4023383456685</v>
+        <v>717.2901378550044</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1153827969313931</v>
+        <v>0.1153542989101363</v>
       </c>
       <c r="T22">
         <v>1.273911410999987</v>
       </c>
       <c r="U22">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22">
-        <v>0.06118110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.956850801055729</v>
+        <v>7.072449388016392</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.1051582697791834</v>
+        <v>0.104463471362178</v>
       </c>
       <c r="C23">
-        <v>7525.1328159237</v>
+        <v>7589.155639129856</v>
       </c>
       <c r="D23">
-        <v>8484.722300726597</v>
+        <v>8548.745123932753</v>
       </c>
       <c r="E23">
         <v>117.8919381224357</v>
@@ -3179,45 +3179,45 @@
         <v>803.5</v>
       </c>
       <c r="M23">
-        <v>125.6333616036145</v>
+        <v>119.2903552522452</v>
       </c>
       <c r="N23">
-        <v>677.8666383963855</v>
+        <v>684.2096447477547</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>677.8666383963855</v>
+        <v>684.2096447477547</v>
       </c>
       <c r="Q23">
-        <v>705.2666383963855</v>
+        <v>711.6096447477547</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1162635918292588</v>
+        <v>0.1162347330735557</v>
       </c>
       <c r="T23">
         <v>1.290036871898721</v>
       </c>
       <c r="U23">
-        <v>0.06338110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.06338110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.395594209562909</v>
+        <v>6.735666083825136</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1053340808379486</v>
+        <v>0.1049812824209432</v>
       </c>
       <c r="C24">
-        <v>7414.151621992761</v>
+        <v>7445.348918141129</v>
       </c>
       <c r="D24">
-        <v>8468.131082262462</v>
+        <v>8499.32837841083</v>
       </c>
       <c r="E24">
         <v>212.2819135892405</v>
@@ -3261,37 +3261,37 @@
         <v>803.5</v>
       </c>
       <c r="M24">
-        <v>131.6159026323581</v>
+        <v>128.5010334419535</v>
       </c>
       <c r="N24">
-        <v>671.884097367642</v>
+        <v>674.9989665580465</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>671.884097367642</v>
+        <v>674.9989665580465</v>
       </c>
       <c r="Q24">
-        <v>699.2840973676419</v>
+        <v>702.3989665580465</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1171669712116852</v>
+        <v>0.1171377424719346</v>
       </c>
       <c r="T24">
         <v>1.306575806153833</v>
       </c>
       <c r="U24">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.104885381855504</v>
+        <v>6.252868000185829</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1055098918967138</v>
+        <v>0.1051420934797083</v>
       </c>
       <c r="C25">
-        <v>7303.235187120406</v>
+        <v>7335.728167151305</v>
       </c>
       <c r="D25">
-        <v>8451.604622856912</v>
+        <v>8484.09760288781</v>
       </c>
       <c r="E25">
         <v>306.6718890560451</v>
@@ -3343,37 +3343,37 @@
         <v>803.5</v>
       </c>
       <c r="M25">
-        <v>137.5984436611016</v>
+        <v>134.3419895074968</v>
       </c>
       <c r="N25">
-        <v>665.9015563388984</v>
+        <v>669.1580104925032</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>665.9015563388984</v>
+        <v>669.1580104925032</v>
       </c>
       <c r="Q25">
-        <v>693.3015563388984</v>
+        <v>696.5580104925032</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1180938149936551</v>
+        <v>0.1180642066598818</v>
       </c>
       <c r="T25">
         <v>1.32354432311687</v>
       </c>
       <c r="U25">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25">
-        <v>0.06338110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.839455582644395</v>
+        <v>5.981004174090793</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1060457029554789</v>
+        <v>0.1053029045384735</v>
       </c>
       <c r="C26">
-        <v>7158.873819183492</v>
+        <v>7226.1619055411</v>
       </c>
       <c r="D26">
-        <v>8401.633230386802</v>
+        <v>8468.92131674441</v>
       </c>
       <c r="E26">
         <v>401.0618645228496</v>
@@ -3425,45 +3425,45 @@
         <v>803.5</v>
       </c>
       <c r="M26">
-        <v>146.9790238066501</v>
+        <v>140.1829455730402</v>
       </c>
       <c r="N26">
-        <v>656.5209761933498</v>
+        <v>663.3170544269599</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>656.5209761933498</v>
+        <v>663.3170544269599</v>
       </c>
       <c r="Q26">
-        <v>683.9209761933498</v>
+        <v>690.7170544269599</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1190450494014664</v>
+        <v>0.119015051484354</v>
       </c>
       <c r="T26">
         <v>1.340959379999986</v>
       </c>
       <c r="U26">
-        <v>0.06488110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.06488110587651873</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>5.466766475854395</v>
+        <v>5.73179566683701</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1062365140142441</v>
+        <v>0.1056637155972387</v>
       </c>
       <c r="C27">
-        <v>7046.830605526846</v>
+        <v>7097.917748231956</v>
       </c>
       <c r="D27">
-        <v>8383.979992196961</v>
+        <v>8435.06713490207</v>
       </c>
       <c r="E27">
         <v>495.4518399896542</v>
@@ -3507,37 +3507,37 @@
         <v>803.5</v>
       </c>
       <c r="M27">
-        <v>153.1031497985939</v>
+        <v>147.9117011479196</v>
       </c>
       <c r="N27">
-        <v>650.3968502014061</v>
+        <v>655.5882988520804</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>650.3968502014061</v>
+        <v>655.5882988520804</v>
       </c>
       <c r="Q27">
-        <v>677.7968502014061</v>
+        <v>682.9882988520803</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1200216500601526</v>
+        <v>0.119991252170812</v>
       </c>
       <c r="T27">
         <v>1.358838838399986</v>
       </c>
       <c r="U27">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V27">
         <v>0</v>
       </c>
       <c r="W27">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.24809581682022</v>
+        <v>5.432295036593872</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1064273250730093</v>
+        <v>0.1058325266560039</v>
       </c>
       <c r="C28">
-        <v>6934.86142114091</v>
+        <v>6987.781334650405</v>
       </c>
       <c r="D28">
-        <v>8366.40078327783</v>
+        <v>8419.320696787325</v>
       </c>
       <c r="E28">
         <v>589.8418154564588</v>
@@ -3589,37 +3589,37 @@
         <v>803.5</v>
       </c>
       <c r="M28">
-        <v>159.2272757905376</v>
+        <v>153.8281691938364</v>
       </c>
       <c r="N28">
-        <v>644.2727242094624</v>
+        <v>649.6718308061636</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>644.2727242094624</v>
+        <v>649.6718308061636</v>
       </c>
       <c r="Q28">
-        <v>671.6727242094623</v>
+        <v>677.0718308061636</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1210246453312357</v>
+        <v>0.1209938366596068</v>
       </c>
       <c r="T28">
         <v>1.377201525405391</v>
       </c>
       <c r="U28">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V28">
         <v>0</v>
       </c>
       <c r="W28">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.04624597771175</v>
+        <v>5.223360612109492</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1066181361317745</v>
+        <v>0.1060013377147691</v>
       </c>
       <c r="C29">
-        <v>6822.965801334791</v>
+        <v>6877.703601883701</v>
       </c>
       <c r="D29">
-        <v>8348.895138938515</v>
+        <v>8403.632939487425</v>
       </c>
       <c r="E29">
         <v>684.2317909232638</v>
@@ -3671,37 +3671,37 @@
         <v>803.5</v>
       </c>
       <c r="M29">
-        <v>165.3514017824814</v>
+        <v>159.7446372397532</v>
       </c>
       <c r="N29">
-        <v>638.1485982175186</v>
+        <v>643.7553627602467</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>638.1485982175186</v>
+        <v>643.7553627602467</v>
       </c>
       <c r="Q29">
-        <v>665.5485982175186</v>
+        <v>671.1553627602467</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1220551199248143</v>
+        <v>0.1220238892165877</v>
       </c>
       <c r="T29">
         <v>1.396067299726013</v>
       </c>
       <c r="U29">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V29">
         <v>0</v>
       </c>
       <c r="W29">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.85934797853724</v>
+        <v>5.029902811660993</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1068089471905397</v>
+        <v>0.1061701487735343</v>
       </c>
       <c r="C30">
-        <v>6711.143285298707</v>
+        <v>6767.684222521253</v>
       </c>
       <c r="D30">
-        <v>8331.462598369237</v>
+        <v>8388.003535591783</v>
       </c>
       <c r="E30">
         <v>778.6217663900684</v>
@@ -3753,37 +3753,37 @@
         <v>803.5</v>
       </c>
       <c r="M30">
-        <v>171.4755277744252</v>
+        <v>165.66110528567</v>
       </c>
       <c r="N30">
-        <v>632.0244722255749</v>
+        <v>637.83889471433</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>632.0244722255749</v>
+        <v>637.83889471433</v>
       </c>
       <c r="Q30">
-        <v>659.4244722255748</v>
+        <v>665.2388947143299</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1231142188126589</v>
+        <v>0.1230825543445959</v>
       </c>
       <c r="T30">
         <v>1.415457123333319</v>
       </c>
       <c r="U30">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V30">
         <v>0</v>
       </c>
       <c r="W30">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.685799836446625</v>
+        <v>4.850263425530242</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1069997582493049</v>
+        <v>0.1063389598322994</v>
       </c>
       <c r="C31">
-        <v>6599.393416063551</v>
+        <v>6657.722871583665</v>
       </c>
       <c r="D31">
-        <v>8314.102704600884</v>
+        <v>8372.432160120998</v>
       </c>
       <c r="E31">
         <v>873.0117418568725</v>
@@ -3835,37 +3835,37 @@
         <v>803.5</v>
       </c>
       <c r="M31">
-        <v>177.5996537663689</v>
+        <v>171.5775733315868</v>
       </c>
       <c r="N31">
-        <v>625.9003462336311</v>
+        <v>631.9224266684132</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>625.9003462336311</v>
+        <v>631.9224266684132</v>
       </c>
       <c r="Q31">
-        <v>653.3003462336311</v>
+        <v>659.3224266684132</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1242031514719922</v>
+        <v>0.1241710410255057</v>
       </c>
       <c r="T31">
         <v>1.435393139154915</v>
       </c>
       <c r="U31">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V31">
         <v>0</v>
       </c>
       <c r="W31">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.52422053174157</v>
+        <v>4.683012962580925</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1071905693080701</v>
+        <v>0.1065077708910646</v>
       </c>
       <c r="C32">
-        <v>6487.715740460947</v>
+        <v>6547.819226500217</v>
       </c>
       <c r="D32">
-        <v>8296.815004465085</v>
+        <v>8356.918490504355</v>
       </c>
       <c r="E32">
         <v>967.4017173236771</v>
@@ -3917,37 +3917,37 @@
         <v>803.5</v>
       </c>
       <c r="M32">
-        <v>183.7237797583126</v>
+        <v>177.4940413775035</v>
       </c>
       <c r="N32">
-        <v>619.7762202416874</v>
+        <v>626.0059586224965</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>619.7762202416874</v>
+        <v>626.0059586224965</v>
       </c>
       <c r="Q32">
-        <v>647.1762202416874</v>
+        <v>653.4059586224964</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1253231964930206</v>
+        <v>0.12529062732587</v>
       </c>
       <c r="T32">
         <v>1.455898755428557</v>
       </c>
       <c r="U32">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V32">
         <v>0</v>
       </c>
       <c r="W32">
-        <v>0.06488110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.373413180683517</v>
+        <v>4.526912530494894</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1078153803668352</v>
+        <v>0.1066765819498298</v>
       </c>
       <c r="C33">
-        <v>6337.216906907099</v>
+        <v>6437.972967086602</v>
       </c>
       <c r="D33">
-        <v>8240.706146378041</v>
+        <v>8341.462206557544</v>
       </c>
       <c r="E33">
         <v>1061.791692790482</v>
@@ -3999,45 +3999,45 @@
         <v>803.5</v>
       </c>
       <c r="M33">
-        <v>193.9444306855157</v>
+        <v>183.4105094234203</v>
       </c>
       <c r="N33">
-        <v>609.5555693144843</v>
+        <v>620.0894905765797</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>609.5555693144843</v>
+        <v>620.0894905765797</v>
       </c>
       <c r="Q33">
-        <v>636.9555693144843</v>
+        <v>647.4894905765797</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1264757065871224</v>
+        <v>0.1264426654030566</v>
       </c>
       <c r="T33">
         <v>1.476998737391289</v>
       </c>
       <c r="U33">
-        <v>0.06628110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V33">
         <v>0</v>
       </c>
       <c r="W33">
-        <v>0.06628110587651873</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.142939279874911</v>
+        <v>4.380883094027316</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1080201914256004</v>
+        <v>0.107165393008595</v>
       </c>
       <c r="C34">
-        <v>6224.599416119308</v>
+        <v>6299.148360031922</v>
       </c>
       <c r="D34">
-        <v>8222.478631057056</v>
+        <v>8297.02757496967</v>
       </c>
       <c r="E34">
         <v>1156.181668257287</v>
@@ -4081,37 +4081,37 @@
         <v>803.5</v>
       </c>
       <c r="M34">
-        <v>200.200702643113</v>
+        <v>192.3474566842749</v>
       </c>
       <c r="N34">
-        <v>603.299297356887</v>
+        <v>611.1525433157251</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>603.299297356887</v>
+        <v>611.1525433157251</v>
       </c>
       <c r="Q34">
-        <v>630.699297356887</v>
+        <v>638.5525433157251</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.127662114036933</v>
+        <v>0.1276285869531015</v>
       </c>
       <c r="T34">
         <v>1.498719307058808</v>
       </c>
       <c r="U34">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V34">
         <v>0</v>
       </c>
       <c r="W34">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.01347242737882</v>
+        <v>4.177336232310521</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1082250024843656</v>
+        <v>0.1073442040673602</v>
       </c>
       <c r="C35">
-        <v>6112.06238179924</v>
+        <v>6188.621866801333</v>
       </c>
       <c r="D35">
-        <v>8204.331572203791</v>
+        <v>8280.891057205885</v>
       </c>
       <c r="E35">
         <v>1250.571643724091</v>
@@ -4163,37 +4163,37 @@
         <v>803.5</v>
       </c>
       <c r="M35">
-        <v>206.4569746007103</v>
+        <v>198.3583147056585</v>
       </c>
       <c r="N35">
-        <v>597.0430253992897</v>
+        <v>605.1416852943415</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>597.0430253992897</v>
+        <v>605.1416852943415</v>
       </c>
       <c r="Q35">
-        <v>624.4430253992897</v>
+        <v>632.5416852943415</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1288839366344992</v>
+        <v>0.1288499091464314</v>
       </c>
       <c r="T35">
         <v>1.521088251940283</v>
       </c>
       <c r="U35">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V35">
         <v>0</v>
       </c>
       <c r="W35">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.891852050791583</v>
+        <v>4.05075028587687</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1084298135431308</v>
+        <v>0.1075230151261254</v>
       </c>
       <c r="C36">
-        <v>5999.605272416284</v>
+        <v>6078.158018119229</v>
       </c>
       <c r="D36">
-        <v>8186.264438287641</v>
+        <v>8264.817183990586</v>
       </c>
       <c r="E36">
         <v>1344.961619190896</v>
@@ -4245,37 +4245,37 @@
         <v>803.5</v>
       </c>
       <c r="M36">
-        <v>212.7132465583076</v>
+        <v>204.3691727270421</v>
       </c>
       <c r="N36">
-        <v>590.7867534416924</v>
+        <v>599.130827272958</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>590.7867534416924</v>
+        <v>599.130827272958</v>
       </c>
       <c r="Q36">
-        <v>618.1867534416924</v>
+        <v>626.5308272729579</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1301427841592643</v>
+        <v>0.1301082411031955</v>
       </c>
       <c r="T36">
         <v>1.544135043636348</v>
       </c>
       <c r="U36">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V36">
         <v>0</v>
       </c>
       <c r="W36">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.777385814003595</v>
+        <v>3.931610571586373</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.108634624601896</v>
+        <v>0.1077018261848906</v>
       </c>
       <c r="C37">
-        <v>5887.227561111582</v>
+        <v>5967.756449898066</v>
       </c>
       <c r="D37">
-        <v>8168.276702449743</v>
+        <v>8248.805591236227</v>
       </c>
       <c r="E37">
         <v>1439.3515946577</v>
@@ -4327,37 +4327,37 @@
         <v>803.5</v>
       </c>
       <c r="M37">
-        <v>218.9695185159048</v>
+        <v>210.3800307484257</v>
       </c>
       <c r="N37">
-        <v>584.5304814840952</v>
+        <v>593.1199692515743</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>584.5304814840952</v>
+        <v>593.1199692515743</v>
       </c>
       <c r="Q37">
-        <v>611.9304814840951</v>
+        <v>620.5199692515743</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1314403654540222</v>
+        <v>0.1314052909663216</v>
       </c>
       <c r="T37">
         <v>1.567890967384599</v>
       </c>
       <c r="U37">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V37">
         <v>0</v>
       </c>
       <c r="W37">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.669460505032064</v>
+        <v>3.819278840969619</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1088394356606612</v>
+        <v>0.1078806372436558</v>
       </c>
       <c r="C38">
-        <v>5774.928725646798</v>
+        <v>5857.416800866262</v>
       </c>
       <c r="D38">
-        <v>8150.367842451764</v>
+        <v>8232.855917671228</v>
       </c>
       <c r="E38">
         <v>1533.741570124505</v>
@@ -4409,37 +4409,37 @@
         <v>803.5</v>
       </c>
       <c r="M38">
-        <v>225.2257904735021</v>
+        <v>216.3908887698092</v>
       </c>
       <c r="N38">
-        <v>578.2742095264979</v>
+        <v>587.1091112301908</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>578.2742095264979</v>
+        <v>587.1091112301908</v>
       </c>
       <c r="Q38">
-        <v>605.6742095264979</v>
+        <v>614.5091112301908</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1327784961642413</v>
+        <v>0.1327428736376703</v>
       </c>
       <c r="T38">
         <v>1.592389263749984</v>
       </c>
       <c r="U38">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V38">
         <v>0</v>
       </c>
       <c r="W38">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.567531046558951</v>
+        <v>3.713187762053797</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1090442467194264</v>
+        <v>0.108059448302421</v>
       </c>
       <c r="C39">
-        <v>5662.708248353591</v>
+        <v>5747.138712541015</v>
       </c>
       <c r="D39">
-        <v>8132.537340625361</v>
+        <v>8216.967804812784</v>
       </c>
       <c r="E39">
         <v>1628.13154559131</v>
@@ -4491,37 +4491,37 @@
         <v>803.5</v>
       </c>
       <c r="M39">
-        <v>231.4820624310994</v>
+        <v>222.4017467911928</v>
       </c>
       <c r="N39">
-        <v>572.0179375689006</v>
+        <v>581.0982532088071</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>572.0179375689006</v>
+        <v>581.0982532088071</v>
       </c>
       <c r="Q39">
-        <v>599.4179375689006</v>
+        <v>608.4982532088071</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1341591072144674</v>
+        <v>0.1341229192509667</v>
       </c>
       <c r="T39">
         <v>1.617665283809507</v>
       </c>
       <c r="U39">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V39">
         <v>0</v>
       </c>
       <c r="W39">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.471111288543844</v>
+        <v>3.612831336052342</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1092490577781915</v>
+        <v>0.1082382593611862</v>
       </c>
       <c r="C40">
-        <v>5550.565616083724</v>
+        <v>5636.92182920147</v>
       </c>
       <c r="D40">
-        <v>8114.7846838223</v>
+        <v>8201.140896940045</v>
       </c>
       <c r="E40">
         <v>1722.521521058114</v>
@@ -4573,37 +4573,37 @@
         <v>803.5</v>
       </c>
       <c r="M40">
-        <v>237.7383343886967</v>
+        <v>228.4126048125764</v>
       </c>
       <c r="N40">
-        <v>565.7616656113033</v>
+        <v>575.0873951874236</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>565.7616656113033</v>
+        <v>575.0873951874236</v>
       </c>
       <c r="Q40">
-        <v>593.1616656113033</v>
+        <v>602.4873951874235</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1355842541050233</v>
+        <v>0.135547482464692</v>
       </c>
       <c r="T40">
         <v>1.643756659354822</v>
       </c>
       <c r="U40">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V40">
         <v>0</v>
       </c>
       <c r="W40">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.379766254634796</v>
+        <v>3.51775682720886</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1094538688369568</v>
+        <v>0.1084170704199513</v>
       </c>
       <c r="C41">
-        <v>5438.500320159843</v>
+        <v>5526.765797862139</v>
       </c>
       <c r="D41">
-        <v>8097.109363365223</v>
+        <v>8185.374841067518</v>
       </c>
       <c r="E41">
         <v>1816.911496524919</v>
@@ -4655,37 +4655,37 @@
         <v>803.5</v>
       </c>
       <c r="M41">
-        <v>243.994606346294</v>
+        <v>234.42346283396</v>
       </c>
       <c r="N41">
-        <v>559.5053936537061</v>
+        <v>569.07653716604</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>559.5053936537061</v>
+        <v>569.07653716604</v>
       </c>
       <c r="Q41">
-        <v>586.905393653706</v>
+        <v>596.47653716604</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1370561271231384</v>
+        <v>0.1370187526690312</v>
       </c>
       <c r="T41">
         <v>1.670703489836048</v>
       </c>
       <c r="U41">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V41">
         <v>0</v>
       </c>
       <c r="W41">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.293105581439031</v>
+        <v>3.427557934203505</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1096586798957219</v>
+        <v>0.1085958814787165</v>
       </c>
       <c r="C42">
-        <v>5326.511856326892</v>
+        <v>5416.670268246678</v>
       </c>
       <c r="D42">
-        <v>8079.510874999076</v>
+        <v>8169.669286918863</v>
       </c>
       <c r="E42">
         <v>1911.301471991724</v>
@@ -4737,37 +4737,37 @@
         <v>803.5</v>
       </c>
       <c r="M42">
-        <v>250.2508783038913</v>
+        <v>240.4343208553436</v>
       </c>
       <c r="N42">
-        <v>553.2491216961087</v>
+        <v>563.0656791446563</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>553.2491216961087</v>
+        <v>563.0656791446563</v>
       </c>
       <c r="Q42">
-        <v>580.6491216961086</v>
+        <v>590.4656791446563</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1385770625751908</v>
+        <v>0.1385390652135151</v>
       </c>
       <c r="T42">
         <v>1.698548547999983</v>
       </c>
       <c r="U42">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V42">
         <v>0</v>
       </c>
       <c r="W42">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.210777941903055</v>
+        <v>3.341868985848417</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1098634909544871</v>
+        <v>0.1087746925374817</v>
       </c>
       <c r="C43">
-        <v>5214.599724704155</v>
+        <v>5306.63489276195</v>
       </c>
       <c r="D43">
-        <v>8061.988718843145</v>
+        <v>8154.023886900939</v>
       </c>
       <c r="E43">
         <v>2005.691447458528</v>
@@ -4819,37 +4819,37 @@
         <v>803.5</v>
       </c>
       <c r="M43">
-        <v>256.5071502614886</v>
+        <v>246.4451788767272</v>
       </c>
       <c r="N43">
-        <v>546.9928497385115</v>
+        <v>557.0548211232727</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>546.9928497385115</v>
+        <v>557.0548211232727</v>
       </c>
       <c r="Q43">
-        <v>574.3928497385115</v>
+        <v>584.4548211232727</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1401495551612109</v>
+        <v>0.140110913776456</v>
       </c>
       <c r="T43">
         <v>1.72733750644066</v>
       </c>
       <c r="U43">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.132466284783469</v>
+        <v>3.260359986193577</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1100683020132523</v>
+        <v>0.1089535035962469</v>
       </c>
       <c r="C44">
-        <v>5102.763429737921</v>
+        <v>5196.659326472369</v>
       </c>
       <c r="D44">
-        <v>8044.542399343714</v>
+        <v>8138.438296078163</v>
       </c>
       <c r="E44">
         <v>2100.081422925332</v>
@@ -4901,37 +4901,37 @@
         <v>803.5</v>
       </c>
       <c r="M44">
-        <v>262.7634222190858</v>
+        <v>252.4560368981108</v>
       </c>
       <c r="N44">
-        <v>540.7365777809142</v>
+        <v>551.0439631018892</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>540.7365777809142</v>
+        <v>551.0439631018892</v>
       </c>
       <c r="Q44">
-        <v>568.1365777809142</v>
+        <v>578.4439631018892</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1417762716295076</v>
+        <v>0.1417369640139811</v>
       </c>
       <c r="T44">
         <v>1.757119187586189</v>
       </c>
       <c r="U44">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V44">
         <v>0</v>
       </c>
       <c r="W44">
-        <v>0.06628110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.057883754193387</v>
+        <v>3.182732367474683</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1113911130720175</v>
+        <v>0.1091323146550121</v>
       </c>
       <c r="C45">
-        <v>4897.486769370142</v>
+        <v>5086.743227074558</v>
       </c>
       <c r="D45">
-        <v>7933.655714442739</v>
+        <v>8122.912172147155</v>
       </c>
       <c r="E45">
         <v>2194.471398392137</v>
@@ -4983,45 +4983,45 @@
         <v>803.5</v>
       </c>
       <c r="M45">
-        <v>279.5724934338718</v>
+        <v>258.4668949194943</v>
       </c>
       <c r="N45">
-        <v>523.9275065661282</v>
+        <v>545.0331050805057</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>523.9275065661282</v>
+        <v>545.0331050805057</v>
       </c>
       <c r="Q45">
-        <v>551.3275065661281</v>
+        <v>572.4331050805057</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1434600658686218</v>
+        <v>0.1434200686458053</v>
       </c>
       <c r="T45">
         <v>1.787945839999981</v>
       </c>
       <c r="U45">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.874030953943094</v>
+        <v>3.108715335672946</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1116219241307827</v>
+        <v>0.1093111257137773</v>
       </c>
       <c r="C46">
-        <v>4784.061178370061</v>
+        <v>4976.886254872275</v>
       </c>
       <c r="D46">
-        <v>7914.620098909463</v>
+        <v>8107.445175411678</v>
       </c>
       <c r="E46">
         <v>2288.861373858942</v>
@@ -5065,45 +5065,45 @@
         <v>803.5</v>
       </c>
       <c r="M46">
-        <v>286.0741793276828</v>
+        <v>264.477752940878</v>
       </c>
       <c r="N46">
-        <v>517.4258206723172</v>
+        <v>539.022247059122</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>517.4258206723172</v>
+        <v>539.022247059122</v>
       </c>
       <c r="Q46">
-        <v>544.8258206723171</v>
+        <v>566.422247059122</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1452039956162758</v>
+        <v>0.1451632841573375</v>
       </c>
       <c r="T46">
         <v>1.819873444285695</v>
       </c>
       <c r="U46">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V46">
         <v>0</v>
       </c>
       <c r="W46">
-        <v>0.06888110587651872</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.808712068626205</v>
+        <v>3.038062714407652</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1118527351895479</v>
+        <v>0.1106149367725425</v>
       </c>
       <c r="C47">
-        <v>4670.726714925094</v>
+        <v>4771.473965612763</v>
       </c>
       <c r="D47">
-        <v>7895.675610931302</v>
+        <v>7996.42286161897</v>
       </c>
       <c r="E47">
         <v>2383.251349325747</v>
@@ -5147,37 +5147,37 @@
         <v>803.5</v>
       </c>
       <c r="M47">
-        <v>292.5758652214938</v>
+        <v>281.107483202277</v>
       </c>
       <c r="N47">
-        <v>510.9241347785062</v>
+        <v>522.3925167977229</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>510.9241347785062</v>
+        <v>522.3925167977229</v>
       </c>
       <c r="Q47">
-        <v>538.3241347785063</v>
+        <v>549.7925167977229</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1470113409911172</v>
+        <v>0.1469698893238346</v>
       </c>
       <c r="T47">
         <v>1.852962052363617</v>
       </c>
       <c r="U47">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V47">
         <v>0</v>
       </c>
       <c r="W47">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.746296244878956</v>
+        <v>2.858337283827567</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1120835462483131</v>
+        <v>0.1108187478313077</v>
       </c>
       <c r="C48">
-        <v>4557.482726227216</v>
+        <v>4660.00326024879</v>
       </c>
       <c r="D48">
-        <v>7876.821597700228</v>
+        <v>7979.342131721803</v>
       </c>
       <c r="E48">
         <v>2477.641324792551</v>
@@ -5229,37 +5229,37 @@
         <v>803.5</v>
       </c>
       <c r="M48">
-        <v>299.0775511153047</v>
+        <v>287.3543161623276</v>
       </c>
       <c r="N48">
-        <v>504.4224488846953</v>
+        <v>516.1456838376723</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>504.4224488846953</v>
+        <v>516.1456838376723</v>
       </c>
       <c r="Q48">
-        <v>531.8224488846953</v>
+        <v>543.5456838376723</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1488856250835453</v>
+        <v>0.1488434057927945</v>
       </c>
       <c r="T48">
         <v>1.887276164444425</v>
       </c>
       <c r="U48">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V48">
         <v>0</v>
       </c>
       <c r="W48">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.686594152598979</v>
+        <v>2.796199516787837</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1123143573070783</v>
+        <v>0.1110225588900728</v>
       </c>
       <c r="C49">
-        <v>4444.328565688887</v>
+        <v>4548.6053698104</v>
       </c>
       <c r="D49">
-        <v>7858.057412628704</v>
+        <v>7962.334216750217</v>
       </c>
       <c r="E49">
         <v>2572.031300259356</v>
@@ -5311,37 +5311,37 @@
         <v>803.5</v>
       </c>
       <c r="M49">
-        <v>305.5792370091157</v>
+        <v>293.6011491223782</v>
       </c>
       <c r="N49">
-        <v>497.9207629908843</v>
+        <v>509.8988508776218</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>497.9207629908843</v>
+        <v>509.8988508776218</v>
       </c>
       <c r="Q49">
-        <v>525.3207629908843</v>
+        <v>537.2988508776218</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1508306368775744</v>
+        <v>0.1507876209964321</v>
       </c>
       <c r="T49">
         <v>1.922885148679226</v>
       </c>
       <c r="U49">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V49">
         <v>0</v>
       </c>
       <c r="W49">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.629432574884107</v>
+        <v>2.736705910047671</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1125451683658434</v>
+        <v>0.111226369948838</v>
       </c>
       <c r="C50">
-        <v>4331.263592869136</v>
+        <v>4437.279829674331</v>
       </c>
       <c r="D50">
-        <v>7839.382415275758</v>
+        <v>7945.398652080952</v>
       </c>
       <c r="E50">
         <v>2666.42127572616</v>
@@ -5393,37 +5393,37 @@
         <v>803.5</v>
       </c>
       <c r="M50">
-        <v>312.0809229029267</v>
+        <v>299.8479820824288</v>
       </c>
       <c r="N50">
-        <v>491.4190770970733</v>
+        <v>503.6520179175712</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>491.4190770970733</v>
+        <v>503.6520179175712</v>
       </c>
       <c r="Q50">
-        <v>518.8190770970733</v>
+        <v>531.0520179175712</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1528504568175278</v>
+        <v>0.152806613707902</v>
       </c>
       <c r="T50">
         <v>1.959863709230749</v>
       </c>
       <c r="U50">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V50">
         <v>0</v>
       </c>
       <c r="W50">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.574652729574022</v>
+        <v>2.679691203588344</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1127759794246086</v>
+        <v>0.1114301810076032</v>
       </c>
       <c r="C51">
-        <v>4218.287173400694</v>
+        <v>4326.026179161879</v>
       </c>
       <c r="D51">
-        <v>7820.795971274119</v>
+        <v>7928.534977035304</v>
       </c>
       <c r="E51">
         <v>2760.811251192965</v>
@@ -5475,37 +5475,37 @@
         <v>803.5</v>
       </c>
       <c r="M51">
-        <v>318.5826087967376</v>
+        <v>306.0948150424794</v>
       </c>
       <c r="N51">
-        <v>484.9173912032624</v>
+        <v>497.4051849575206</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>484.9173912032624</v>
+        <v>497.4051849575206</v>
       </c>
       <c r="Q51">
-        <v>512.3173912032623</v>
+        <v>524.8051849575206</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1549494853825773</v>
+        <v>0.1549047826041353</v>
       </c>
       <c r="T51">
         <v>1.998292409411744</v>
       </c>
       <c r="U51">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V51">
         <v>0</v>
       </c>
       <c r="W51">
-        <v>0.06888110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.522108796317409</v>
+        <v>2.625003628004909</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1143567904833738</v>
+        <v>0.1116339920663684</v>
       </c>
       <c r="C52">
-        <v>3998.930800237657</v>
+        <v>4214.843961497119</v>
       </c>
       <c r="D52">
-        <v>7695.829573577887</v>
+        <v>7911.742734837349</v>
       </c>
       <c r="E52">
         <v>2855.201226659769</v>
@@ -5557,45 +5557,45 @@
         <v>803.5</v>
       </c>
       <c r="M52">
-        <v>337.8269413785673</v>
+        <v>312.34164800253</v>
       </c>
       <c r="N52">
-        <v>465.6730586214327</v>
+        <v>491.15835199747</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>465.6730586214327</v>
+        <v>491.15835199747</v>
       </c>
       <c r="Q52">
-        <v>493.0730586214327</v>
+        <v>518.55835199747</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1571324750902289</v>
+        <v>0.1570868782562181</v>
       </c>
       <c r="T52">
         <v>2.038258257599979</v>
       </c>
       <c r="U52">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V52">
         <v>0</v>
       </c>
       <c r="W52">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.37843671295476</v>
+        <v>2.572503555444811</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.114614601542139</v>
+        <v>0.1118378031251336</v>
       </c>
       <c r="C53">
-        <v>3884.538105427207</v>
+        <v>4103.732723765658</v>
       </c>
       <c r="D53">
-        <v>7675.826854234241</v>
+        <v>7895.021472572694</v>
       </c>
       <c r="E53">
         <v>2949.591202126574</v>
@@ -5639,45 +5639,45 @@
         <v>803.5</v>
       </c>
       <c r="M53">
-        <v>344.5834802061386</v>
+        <v>318.5884809625806</v>
       </c>
       <c r="N53">
-        <v>458.9165197938614</v>
+        <v>484.9115190374194</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>458.9165197938614</v>
+        <v>484.9115190374194</v>
       </c>
       <c r="Q53">
-        <v>486.3165197938613</v>
+        <v>512.3115190374194</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1594045664186009</v>
+        <v>0.1593580390369572</v>
       </c>
       <c r="T53">
         <v>2.079855364897938</v>
       </c>
       <c r="U53">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V53">
         <v>0</v>
       </c>
       <c r="W53">
-        <v>0.07158110587651872</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.331800698975255</v>
+        <v>2.522062309259618</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1148724126009042</v>
+        <v>0.1138616141838988</v>
       </c>
       <c r="C54">
-        <v>3770.24912173072</v>
+        <v>3847.05996203784</v>
       </c>
       <c r="D54">
-        <v>7655.927846004559</v>
+        <v>7732.73868631168</v>
       </c>
       <c r="E54">
         <v>3043.981177593379</v>
@@ -5721,37 +5721,37 @@
         <v>803.5</v>
       </c>
       <c r="M54">
-        <v>351.34001903371</v>
+        <v>342.0142894575897</v>
       </c>
       <c r="N54">
-        <v>452.15998096629</v>
+        <v>461.4857105424103</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>452.15998096629</v>
+        <v>461.4857105424103</v>
       </c>
       <c r="Q54">
-        <v>479.55998096629</v>
+        <v>488.8857105424103</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1617713282189884</v>
+        <v>0.1617238315168938</v>
       </c>
       <c r="T54">
         <v>2.123185684999978</v>
       </c>
       <c r="U54">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V54">
         <v>0</v>
       </c>
       <c r="W54">
-        <v>0.07158110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.286958377841116</v>
+        <v>2.349317045420219</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1176212236596694</v>
+        <v>0.1141004252426639</v>
       </c>
       <c r="C55">
-        <v>3469.935542975106</v>
+        <v>3733.959510745845</v>
       </c>
       <c r="D55">
-        <v>7450.00424271575</v>
+        <v>7714.02821048649</v>
       </c>
       <c r="E55">
         <v>3138.371153060183</v>
@@ -5803,45 +5803,45 @@
         <v>803.5</v>
       </c>
       <c r="M55">
-        <v>381.6091007500624</v>
+        <v>348.5914873317741</v>
       </c>
       <c r="N55">
-        <v>421.8908992499376</v>
+        <v>454.9085126682259</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>421.8908992499376</v>
+        <v>454.9085126682259</v>
       </c>
       <c r="Q55">
-        <v>449.2908992499376</v>
+        <v>482.3085126682259</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1642388032874776</v>
+        <v>0.1641902960172532</v>
       </c>
       <c r="T55">
         <v>2.168359848510616</v>
       </c>
       <c r="U55">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V55">
         <v>0</v>
       </c>
       <c r="W55">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.105557751166574</v>
+        <v>2.304990308714177</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1179260347184345</v>
+        <v>0.1143392363014291</v>
       </c>
       <c r="C56">
-        <v>3353.39130735569</v>
+        <v>3620.949386281333</v>
       </c>
       <c r="D56">
-        <v>7427.84998256314</v>
+        <v>7695.408061488783</v>
       </c>
       <c r="E56">
         <v>3232.761128526989</v>
@@ -5885,45 +5885,45 @@
         <v>803.5</v>
       </c>
       <c r="M56">
-        <v>388.8092724623278</v>
+        <v>355.1686852059586</v>
       </c>
       <c r="N56">
-        <v>414.6907275376722</v>
+        <v>448.3313147940414</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>414.6907275376722</v>
+        <v>448.3313147940414</v>
       </c>
       <c r="Q56">
-        <v>442.0907275376722</v>
+        <v>475.7313147940414</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1668135598806836</v>
+        <v>0.1667639981045848</v>
       </c>
       <c r="T56">
         <v>2.215498106086934</v>
       </c>
       <c r="U56">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V56">
         <v>0</v>
       </c>
       <c r="W56">
-        <v>0.07628110587651873</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.066565940959785</v>
+        <v>2.262305302997247</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1182308457771998</v>
+        <v>0.1161180473601943</v>
       </c>
       <c r="C57">
-        <v>3236.978442408541</v>
+        <v>3390.64361177212</v>
       </c>
       <c r="D57">
-        <v>7405.827093082796</v>
+        <v>7559.492262446375</v>
       </c>
       <c r="E57">
         <v>3327.151103993793</v>
@@ -5967,37 +5967,37 @@
         <v>803.5</v>
       </c>
       <c r="M57">
-        <v>396.0094441745931</v>
+        <v>376.2819393020309</v>
       </c>
       <c r="N57">
-        <v>407.4905558254069</v>
+        <v>427.2180606979691</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>407.4905558254069</v>
+        <v>427.2180606979691</v>
       </c>
       <c r="Q57">
-        <v>434.8905558254069</v>
+        <v>454.6180606979691</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1695027501002543</v>
+        <v>0.1694520869513534</v>
       </c>
       <c r="T57">
         <v>2.26473139733331</v>
       </c>
       <c r="U57">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V57">
         <v>0</v>
       </c>
       <c r="W57">
-        <v>0.07628110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.028992014760516</v>
+        <v>2.135366904641823</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1237436568359649</v>
+        <v>0.1163848584189595</v>
       </c>
       <c r="C58">
-        <v>2765.674904608515</v>
+        <v>3276.280056191353</v>
       </c>
       <c r="D58">
-        <v>7028.913530749574</v>
+        <v>7539.518682332411</v>
       </c>
       <c r="E58">
         <v>3421.541079460598</v>
@@ -6049,45 +6049,45 @@
         <v>803.5</v>
       </c>
       <c r="M58">
-        <v>452.3679151099702</v>
+        <v>383.1234291075223</v>
       </c>
       <c r="N58">
-        <v>351.1320848900298</v>
+        <v>420.3765708924777</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>351.1320848900298</v>
+        <v>420.3765708924777</v>
       </c>
       <c r="Q58">
-        <v>378.5320848900298</v>
+        <v>447.7765708924777</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1723141762388965</v>
+        <v>0.1722623616547933</v>
       </c>
       <c r="T58">
         <v>2.316202565454522</v>
       </c>
       <c r="U58">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V58">
         <v>0</v>
       </c>
       <c r="W58">
-        <v>0.08558110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>1.776209083716005</v>
+        <v>2.097235352773219</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1268204678947301</v>
+        <v>0.1166516694777247</v>
       </c>
       <c r="C59">
-        <v>2477.142747089274</v>
+        <v>3162.021770272288</v>
       </c>
       <c r="D59">
-        <v>6834.771348697137</v>
+        <v>7519.65037188015</v>
       </c>
       <c r="E59">
         <v>3515.931054927402</v>
@@ -6131,45 +6131,45 @@
         <v>803.5</v>
       </c>
       <c r="M59">
-        <v>485.7329880216338</v>
+        <v>389.9649189130138</v>
       </c>
       <c r="N59">
-        <v>317.7670119783662</v>
+        <v>413.5350810869862</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>317.7670119783662</v>
+        <v>413.5350810869862</v>
       </c>
       <c r="Q59">
-        <v>345.1670119783662</v>
+        <v>440.9350810869861</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1752563663839871</v>
+        <v>0.1752033468095559</v>
       </c>
       <c r="T59">
         <v>2.370067741395325</v>
       </c>
       <c r="U59">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V59">
         <v>0</v>
       </c>
       <c r="W59">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.654201011285265</v>
+        <v>2.060441750092987</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1272652789534953</v>
+        <v>0.1169184805364899</v>
       </c>
       <c r="C60">
-        <v>2355.569624792956</v>
+        <v>3047.867923975273</v>
       </c>
       <c r="D60">
-        <v>6807.588201867623</v>
+        <v>7499.886501049939</v>
       </c>
       <c r="E60">
         <v>3610.321030394206</v>
@@ -6213,45 +6213,45 @@
         <v>803.5</v>
       </c>
       <c r="M60">
-        <v>494.2546193904342</v>
+        <v>396.8064087185052</v>
       </c>
       <c r="N60">
-        <v>309.2453806095658</v>
+        <v>406.6935912814948</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>309.2453806095658</v>
+        <v>406.6935912814948</v>
       </c>
       <c r="Q60">
-        <v>336.6453806095657</v>
+        <v>434.0935912814948</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1783386608217011</v>
+        <v>0.17828437887645</v>
       </c>
       <c r="T60">
         <v>2.42649792571426</v>
       </c>
       <c r="U60">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V60">
         <v>0</v>
       </c>
       <c r="W60">
-        <v>0.09028110587651872</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.62568030419414</v>
+        <v>2.024916892332763</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1277100900122605</v>
+        <v>0.1217872915952551</v>
       </c>
       <c r="C61">
-        <v>2234.211870719219</v>
+        <v>2610.234082380697</v>
       </c>
       <c r="D61">
-        <v>6780.620423260691</v>
+        <v>7156.642634922168</v>
       </c>
       <c r="E61">
         <v>3704.711005861011</v>
@@ -6295,45 +6295,45 @@
         <v>803.5</v>
       </c>
       <c r="M61">
-        <v>502.7762507592349</v>
+        <v>447.0861652338202</v>
       </c>
       <c r="N61">
-        <v>300.7237492407651</v>
+        <v>356.4138347661798</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>300.7237492407651</v>
+        <v>356.4138347661798</v>
       </c>
       <c r="Q61">
-        <v>328.1237492407651</v>
+        <v>383.8138347661798</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1815713110856449</v>
+        <v>0.1815157051905098</v>
       </c>
       <c r="T61">
         <v>2.485680801951193</v>
       </c>
       <c r="U61">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V61">
         <v>0</v>
       </c>
       <c r="W61">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.598126400733222</v>
+        <v>1.797192716933614</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1281549010710257</v>
+        <v>0.1221321026540203</v>
       </c>
       <c r="C62">
-        <v>2113.066935469427</v>
+        <v>2492.722909106579</v>
       </c>
       <c r="D62">
-        <v>6753.865463477703</v>
+        <v>7133.521437114855</v>
       </c>
       <c r="E62">
         <v>3799.100981327815</v>
@@ -6377,45 +6377,45 @@
         <v>803.5</v>
       </c>
       <c r="M62">
-        <v>511.2978821280354</v>
+        <v>454.6638968479528</v>
       </c>
       <c r="N62">
-        <v>292.2021178719646</v>
+        <v>348.8361031520472</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>292.2021178719646</v>
+        <v>348.8361031520472</v>
       </c>
       <c r="Q62">
-        <v>319.6021178719645</v>
+        <v>376.2361031520472</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1849655938627861</v>
+        <v>0.1849085978202726</v>
       </c>
       <c r="T62">
         <v>2.547822821999974</v>
       </c>
       <c r="U62">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V62">
         <v>0</v>
       </c>
       <c r="W62">
-        <v>0.09028110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.571490960721002</v>
+        <v>1.76723950498472</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1285997121297909</v>
+        <v>0.1248559137127855</v>
       </c>
       <c r="C63">
-        <v>1992.132309724463</v>
+        <v>2220.809280821872</v>
       </c>
       <c r="D63">
-        <v>6727.320813199543</v>
+        <v>6955.997784296952</v>
       </c>
       <c r="E63">
         <v>3893.49095679462</v>
@@ -6459,37 +6459,37 @@
         <v>803.5</v>
       </c>
       <c r="M63">
-        <v>519.8195134968361</v>
+        <v>484.697003625638</v>
       </c>
       <c r="N63">
-        <v>283.6804865031639</v>
+        <v>318.802996374362</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>283.6804865031639</v>
+        <v>318.802996374362</v>
       </c>
       <c r="Q63">
-        <v>311.0804865031639</v>
+        <v>346.2029963743619</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1885339424233704</v>
+        <v>0.1884754849438693</v>
       </c>
       <c r="T63">
         <v>2.613151612307665</v>
       </c>
       <c r="U63">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V63">
         <v>0</v>
       </c>
       <c r="W63">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.545728813823936</v>
+        <v>1.657736676706575</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1290445231885561</v>
+        <v>0.1252397247715507</v>
       </c>
       <c r="C64">
-        <v>1871.405523460172</v>
+        <v>2102.112273002615</v>
       </c>
       <c r="D64">
-        <v>6700.984002402057</v>
+        <v>6931.690751944499</v>
       </c>
       <c r="E64">
         <v>3987.880932261424</v>
@@ -6541,37 +6541,37 @@
         <v>803.5</v>
       </c>
       <c r="M64">
-        <v>528.3411448656366</v>
+        <v>492.6428561440911</v>
       </c>
       <c r="N64">
-        <v>275.1588551343634</v>
+        <v>310.8571438559089</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>275.1588551343634</v>
+        <v>310.8571438559089</v>
       </c>
       <c r="Q64">
-        <v>302.5588551343634</v>
+        <v>338.2571438559089</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1922900988029328</v>
+        <v>0.192230102968708</v>
       </c>
       <c r="T64">
         <v>2.681918759999973</v>
       </c>
       <c r="U64">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V64">
         <v>0</v>
       </c>
       <c r="W64">
-        <v>0.09028110587651872</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.52079770392355</v>
+        <v>1.630998988372598</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1397583342473212</v>
+        <v>0.1256235358303158</v>
       </c>
       <c r="C65">
-        <v>1199.59325031407</v>
+        <v>1983.584550576275</v>
       </c>
       <c r="D65">
-        <v>6123.561704722761</v>
+        <v>6907.553004984966</v>
       </c>
       <c r="E65">
         <v>4082.27090772823</v>
@@ -6623,45 +6623,45 @@
         <v>803.5</v>
       </c>
       <c r="M65">
-        <v>633.791842041299</v>
+        <v>500.5887086625443</v>
       </c>
       <c r="N65">
-        <v>169.708157958701</v>
+        <v>302.9112913374557</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>169.708157958701</v>
+        <v>302.9112913374557</v>
       </c>
       <c r="Q65">
-        <v>197.108157958701</v>
+        <v>330.3112913374557</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1962492906624715</v>
+        <v>0.1961876733192136</v>
       </c>
       <c r="T65">
         <v>2.754403050810782</v>
       </c>
       <c r="U65">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V65">
         <v>0</v>
       </c>
       <c r="W65">
-        <v>0.1065811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.26776639694842</v>
+        <v>1.605110115541287</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1612941453060864</v>
+        <v>0.126007346889081</v>
       </c>
       <c r="C66">
-        <v>201.1361633299002</v>
+        <v>1865.224351207292</v>
       </c>
       <c r="D66">
-        <v>5219.494593205395</v>
+        <v>6883.582781082787</v>
       </c>
       <c r="E66">
         <v>4176.660883195034</v>
@@ -6705,45 +6705,45 @@
         <v>803.5</v>
       </c>
       <c r="M66">
-        <v>841.3913706671373</v>
+        <v>508.5345611809974</v>
       </c>
       <c r="N66">
-        <v>-37.89137066713727</v>
+        <v>294.9654388190026</v>
       </c>
       <c r="O66">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>-37.89137066713727</v>
+        <v>294.9654388190026</v>
       </c>
       <c r="Q66">
-        <v>-10.49137066713727</v>
+        <v>322.3654388190026</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2004284376253179</v>
+        <v>0.2003651086891917</v>
       </c>
       <c r="T66">
         <v>2.830914246666637</v>
       </c>
       <c r="U66">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V66">
         <v>0</v>
       </c>
       <c r="W66">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.954965819726564</v>
+        <v>1.580030269985954</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1622289563648516</v>
+        <v>0.1263911579478462</v>
       </c>
       <c r="C67">
-        <v>73.50983819151679</v>
+        <v>1747.029936937755</v>
       </c>
       <c r="D67">
-        <v>5186.258243533816</v>
+        <v>6859.778342280055</v>
       </c>
       <c r="E67">
         <v>4271.050858661839</v>
@@ -6787,45 +6787,45 @@
         <v>803.5</v>
       </c>
       <c r="M67">
-        <v>854.5381108338113</v>
+        <v>516.4804136994504</v>
       </c>
       <c r="N67">
-        <v>-51.03811083381129</v>
+        <v>287.0195863005496</v>
       </c>
       <c r="O67">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>-51.03811083381129</v>
+        <v>287.0195863005496</v>
       </c>
       <c r="Q67">
-        <v>-23.63811083381129</v>
+        <v>314.4195863005496</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2048463929860413</v>
+        <v>0.2047812546517401</v>
       </c>
       <c r="T67">
         <v>2.911797510857113</v>
       </c>
       <c r="U67">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V67">
         <v>0</v>
       </c>
       <c r="W67">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.9402740378846168</v>
+        <v>1.55572211198617</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1631637674236168</v>
+        <v>0.1267749690066114</v>
       </c>
       <c r="C68">
-        <v>-53.69588480618859</v>
+        <v>1628.999593767369</v>
       </c>
       <c r="D68">
-        <v>5153.442496002916</v>
+        <v>6836.137974576473</v>
       </c>
       <c r="E68">
         <v>4365.440834128643</v>
@@ -6869,45 +6869,45 @@
         <v>803.5</v>
       </c>
       <c r="M68">
-        <v>867.6848510004853</v>
+        <v>524.4262662179035</v>
       </c>
       <c r="N68">
-        <v>-64.18485100048531</v>
+        <v>279.0737337820965</v>
       </c>
       <c r="O68">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P68">
-        <v>-64.18485100048531</v>
+        <v>279.0737337820965</v>
       </c>
       <c r="Q68">
-        <v>-36.78485100048531</v>
+        <v>306.4737337820965</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.209524228073866</v>
+        <v>0.2094571739062031</v>
       </c>
       <c r="T68">
         <v>2.997438614117617</v>
       </c>
       <c r="U68">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V68">
         <v>0</v>
       </c>
       <c r="W68">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.9260274615530317</v>
+        <v>1.532150564834865</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.164098578482382</v>
+        <v>0.1271587800653766</v>
       </c>
       <c r="C69">
-        <v>-180.4889394692955</v>
+        <v>1511.131631242043</v>
       </c>
       <c r="D69">
-        <v>5121.039416806613</v>
+        <v>6812.659987517952</v>
       </c>
       <c r="E69">
         <v>4459.830809595448</v>
@@ -6951,45 +6951,45 @@
         <v>803.5</v>
       </c>
       <c r="M69">
-        <v>880.8315911671593</v>
+        <v>532.3721187363566</v>
       </c>
       <c r="N69">
-        <v>-77.33159116715933</v>
+        <v>271.1278812636434</v>
       </c>
       <c r="O69">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>-77.33159116715933</v>
+        <v>271.1278812636434</v>
       </c>
       <c r="Q69">
-        <v>-49.93159116715933</v>
+        <v>298.5278812636434</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2144855683185286</v>
+        <v>0.214416482206391</v>
       </c>
       <c r="T69">
         <v>3.088270087272696</v>
       </c>
       <c r="U69">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V69">
         <v>0</v>
       </c>
       <c r="W69">
-        <v>0.1392811058765187</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.9122061561567179</v>
+        <v>1.509282645956732</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1650333895411472</v>
+        <v>0.1371985911241418</v>
       </c>
       <c r="C70">
-        <v>-306.8770613104871</v>
+        <v>855.1598537421269</v>
       </c>
       <c r="D70">
-        <v>5089.041270432226</v>
+        <v>6251.07818548484</v>
       </c>
       <c r="E70">
         <v>4554.220785062253</v>
@@ -7033,45 +7033,45 @@
         <v>803.5</v>
       </c>
       <c r="M70">
-        <v>893.9783313338332</v>
+        <v>631.4609315655563</v>
       </c>
       <c r="N70">
-        <v>-90.47833133383324</v>
+        <v>172.0390684344437</v>
       </c>
       <c r="O70">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P70">
-        <v>-90.47833133383324</v>
+        <v>172.0390684344437</v>
       </c>
       <c r="Q70">
-        <v>-63.07833133383324</v>
+        <v>199.4390684344437</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2197569923284827</v>
+        <v>0.2196857472753407</v>
       </c>
       <c r="T70">
         <v>3.184778527499968</v>
       </c>
       <c r="U70">
-        <v>0.1392811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V70">
         <v>0</v>
       </c>
       <c r="W70">
-        <v>0.1392811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.8987913597426486</v>
+        <v>1.272446100517912</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1659682005999124</v>
+        <v>0.137724402182907</v>
       </c>
       <c r="C71">
-        <v>-432.8677937056091</v>
+        <v>733.8988351797843</v>
       </c>
       <c r="D71">
-        <v>5057.440513503909</v>
+        <v>6224.207142389302</v>
       </c>
       <c r="E71">
         <v>4648.610760529057</v>
@@ -7115,45 +7115,45 @@
         <v>803.5</v>
       </c>
       <c r="M71">
-        <v>907.1250715005073</v>
+        <v>640.747121735638</v>
       </c>
       <c r="N71">
-        <v>-103.6250715005073</v>
+        <v>162.752878264362</v>
       </c>
       <c r="O71">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>-103.6250715005073</v>
+        <v>162.752878264362</v>
       </c>
       <c r="Q71">
-        <v>-76.22507150050725</v>
+        <v>190.152878264362</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2253685082100466</v>
+        <v>0.225294964929384</v>
       </c>
       <c r="T71">
         <v>3.287513318709644</v>
       </c>
       <c r="U71">
-        <v>0.1392811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V71">
         <v>0</v>
       </c>
       <c r="W71">
-        <v>0.1392811058765187</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.8857653980072479</v>
+        <v>1.254004852684319</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1669030116586776</v>
+        <v>0.1582702132416721</v>
       </c>
       <c r="C72">
-        <v>-558.4684938223163</v>
+        <v>-255.6018401452739</v>
       </c>
       <c r="D72">
-        <v>5026.229788854006</v>
+        <v>5329.096442531049</v>
       </c>
       <c r="E72">
         <v>4743.000735995862</v>
@@ -7197,37 +7197,37 @@
         <v>803.5</v>
       </c>
       <c r="M72">
-        <v>920.2718116671813</v>
+        <v>839.0020427902625</v>
       </c>
       <c r="N72">
-        <v>-116.7718116671813</v>
+        <v>-35.50204279026252</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-116.7718116671813</v>
+        <v>-35.50204279026252</v>
       </c>
       <c r="Q72">
-        <v>-89.37181166718128</v>
+        <v>-8.102042790262523</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2313541251503815</v>
+        <v>0.2312781304270301</v>
       </c>
       <c r="T72">
         <v>3.397097095999966</v>
       </c>
       <c r="U72">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V72">
         <v>0</v>
       </c>
       <c r="W72">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8731116066071443</v>
+        <v>0.9576853917158609</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1678378227174427</v>
+        <v>0.1590820243004373</v>
       </c>
       <c r="C73">
-        <v>-683.6863383304981</v>
+        <v>-380.1022593750295</v>
       </c>
       <c r="D73">
-        <v>4995.401919812628</v>
+        <v>5298.985998768097</v>
       </c>
       <c r="E73">
         <v>4837.390711462665</v>
@@ -7279,37 +7279,37 @@
         <v>803.5</v>
       </c>
       <c r="M73">
-        <v>933.4185518338552</v>
+        <v>850.9877862586948</v>
       </c>
       <c r="N73">
-        <v>-129.9185518338552</v>
+        <v>-47.48778625869477</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-129.9185518338552</v>
+        <v>-47.48778625869477</v>
       </c>
       <c r="Q73">
-        <v>-102.5185518338552</v>
+        <v>-20.08778625869477</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2377525432590153</v>
+        <v>0.2376739280279621</v>
       </c>
       <c r="T73">
         <v>3.514238375172377</v>
       </c>
       <c r="U73">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V73">
         <v>0</v>
       </c>
       <c r="W73">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8608142600352129</v>
+        <v>0.9441968650719755</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1687726337762079</v>
+        <v>0.1598938353592025</v>
       </c>
       <c r="C74">
-        <v>-808.5283289038762</v>
+        <v>-504.2643304712537</v>
       </c>
       <c r="D74">
-        <v>4964.949904706055</v>
+        <v>5269.213903138678</v>
       </c>
       <c r="E74">
         <v>4931.780686929471</v>
@@ -7361,37 +7361,37 @@
         <v>803.5</v>
       </c>
       <c r="M74">
-        <v>946.5652920005293</v>
+        <v>862.9735297271271</v>
       </c>
       <c r="N74">
-        <v>-143.0652920005293</v>
+        <v>-59.47352972712713</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-143.0652920005293</v>
+        <v>-59.47352972712713</v>
       </c>
       <c r="Q74">
-        <v>-115.6652920005293</v>
+        <v>-32.07352972712713</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2446079912325516</v>
+        <v>0.2445265683146751</v>
       </c>
       <c r="T74">
         <v>3.639746888571391</v>
       </c>
       <c r="U74">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V74">
         <v>0</v>
       </c>
       <c r="W74">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8488585064236125</v>
+        <v>0.9310830197237536</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1697074448349731</v>
+        <v>0.1607056464179677</v>
       </c>
       <c r="C75">
-        <v>-933.0012975215577</v>
+        <v>-628.0937245487548</v>
       </c>
       <c r="D75">
-        <v>4934.866911555178</v>
+        <v>5239.774484527981</v>
       </c>
       <c r="E75">
         <v>5026.170662396275</v>
@@ -7443,37 +7443,37 @@
         <v>803.5</v>
       </c>
       <c r="M75">
-        <v>959.7120321672033</v>
+        <v>874.9592731955595</v>
       </c>
       <c r="N75">
-        <v>-156.2120321672033</v>
+        <v>-71.45927319555949</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-156.2120321672033</v>
+        <v>-71.45927319555949</v>
       </c>
       <c r="Q75">
-        <v>-128.8120321672033</v>
+        <v>-44.05927319555949</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2519712501670905</v>
+        <v>0.251886811585589</v>
       </c>
       <c r="T75">
         <v>3.77455232888885</v>
       </c>
       <c r="U75">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V75">
         <v>0</v>
       </c>
       <c r="W75">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8372303077054808</v>
+        <v>0.9183284578097296</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1706422558937383</v>
+        <v>0.1615174574767329</v>
       </c>
       <c r="C76">
-        <v>-1057.11191157805</v>
+        <v>-751.5959866870608</v>
       </c>
       <c r="D76">
-        <v>4905.14627296549</v>
+        <v>5210.66219785648</v>
       </c>
       <c r="E76">
         <v>5120.56063786308</v>
@@ -7525,37 +7525,37 @@
         <v>803.5</v>
       </c>
       <c r="M76">
-        <v>972.8587723338774</v>
+        <v>886.9450166639917</v>
       </c>
       <c r="N76">
-        <v>-169.3587723338774</v>
+        <v>-83.44501666399174</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-169.3587723338774</v>
+        <v>-83.44501666399174</v>
       </c>
       <c r="Q76">
-        <v>-141.9587723338774</v>
+        <v>-56.04501666399174</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2599009136350555</v>
+        <v>0.2598132274158039</v>
       </c>
       <c r="T76">
         <v>3.919727418461498</v>
       </c>
       <c r="U76">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V76">
         <v>0</v>
       </c>
       <c r="W76">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8259163846283798</v>
+        <v>0.9059186137852738</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1715770669525035</v>
+        <v>0.1623292685354981</v>
       </c>
       <c r="C77">
-        <v>-1180.866678809702</v>
+        <v>-874.7765394123344</v>
       </c>
       <c r="D77">
-        <v>4875.781481200644</v>
+        <v>5181.871620598011</v>
       </c>
       <c r="E77">
         <v>5214.950613329885</v>
@@ -7607,37 +7607,37 @@
         <v>803.5</v>
       </c>
       <c r="M77">
-        <v>986.0055125005514</v>
+        <v>898.9307601324241</v>
       </c>
       <c r="N77">
-        <v>-182.5055125005514</v>
+        <v>-95.4307601324241</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-182.5055125005514</v>
+        <v>-95.4307601324241</v>
       </c>
       <c r="Q77">
-        <v>-155.1055125005514</v>
+        <v>-68.03076013242409</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2684649501804577</v>
+        <v>0.2683737565124361</v>
       </c>
       <c r="T77">
         <v>4.076516515199958</v>
       </c>
       <c r="U77">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V77">
         <v>0</v>
       </c>
       <c r="W77">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8149041661666681</v>
+        <v>0.8938396989348035</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1725118780112687</v>
+        <v>0.1631410795942633</v>
       </c>
       <c r="C78">
-        <v>-1304.27195204526</v>
+        <v>-997.6406860645129</v>
       </c>
       <c r="D78">
-        <v>4846.76618343189</v>
+        <v>5153.397449412637</v>
       </c>
       <c r="E78">
         <v>5309.340588796689</v>
@@ -7689,37 +7689,37 @@
         <v>803.5</v>
       </c>
       <c r="M78">
-        <v>999.1522526672254</v>
+        <v>910.9165036008565</v>
       </c>
       <c r="N78">
-        <v>-195.6522526672254</v>
+        <v>-107.4165036008565</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-195.6522526672254</v>
+        <v>-107.4165036008565</v>
       </c>
       <c r="Q78">
-        <v>-168.2522526672254</v>
+        <v>-80.01650360085645</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2777426564379769</v>
+        <v>0.2776476630337876</v>
       </c>
       <c r="T78">
         <v>4.246371369999957</v>
       </c>
       <c r="U78">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V78">
         <v>0</v>
       </c>
       <c r="W78">
-        <v>0.1392811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8041817429276329</v>
+        <v>0.8820786502646086</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2388196890700339</v>
+        <v>0.1639528906530284</v>
       </c>
       <c r="C79">
-        <v>-2837.272072089339</v>
+        <v>-1120.193614054015</v>
       </c>
       <c r="D79">
-        <v>3408.156038854615</v>
+        <v>5125.23449688994</v>
       </c>
       <c r="E79">
         <v>5403.730564263494</v>
@@ -7771,45 +7771,45 @@
         <v>803.5</v>
       </c>
       <c r="M79">
-        <v>1629.354579453041</v>
+        <v>922.9022470692887</v>
       </c>
       <c r="N79">
-        <v>-825.8545794530412</v>
+        <v>-119.4022470692887</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-825.8545794530412</v>
+        <v>-119.4022470692887</v>
       </c>
       <c r="Q79">
-        <v>-798.4545794530412</v>
+        <v>-92.0022470692887</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2878271197613672</v>
+        <v>0.2877279962091697</v>
       </c>
       <c r="T79">
         <v>4.430996212173867</v>
       </c>
       <c r="U79">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V79">
         <v>0</v>
       </c>
       <c r="W79">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.4931400507492527</v>
+        <v>0.8706230833780554</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2406035001287991</v>
+        <v>0.1647647017117936</v>
       </c>
       <c r="C80">
-        <v>-2958.660608025268</v>
+        <v>-1242.440398012273</v>
       </c>
       <c r="D80">
-        <v>3381.157478385491</v>
+        <v>5097.377688398486</v>
       </c>
       <c r="E80">
         <v>5498.120539730298</v>
@@ -7853,45 +7853,45 @@
         <v>803.5</v>
       </c>
       <c r="M80">
-        <v>1650.515028536847</v>
+        <v>934.8879905377211</v>
       </c>
       <c r="N80">
-        <v>-847.015028536847</v>
+        <v>-131.3879905377211</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-847.015028536847</v>
+        <v>-131.3879905377211</v>
       </c>
       <c r="Q80">
-        <v>-819.615028536847</v>
+        <v>-103.9879905377211</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.298828352477793</v>
+        <v>0.2987247233095865</v>
       </c>
       <c r="T80">
         <v>4.632405130909044</v>
       </c>
       <c r="U80">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V80">
         <v>0</v>
       </c>
       <c r="W80">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.4868177424063135</v>
+        <v>0.8594612489757726</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2423873111875642</v>
+        <v>0.1655765127705588</v>
       </c>
       <c r="C81">
-        <v>-3079.624754172423</v>
+        <v>-1364.386002840049</v>
       </c>
       <c r="D81">
-        <v>3354.583307705141</v>
+        <v>5069.822059037516</v>
       </c>
       <c r="E81">
         <v>5592.510515197104</v>
@@ -7935,45 +7935,45 @@
         <v>803.5</v>
       </c>
       <c r="M81">
-        <v>1671.675477620653</v>
+        <v>946.8737340061534</v>
       </c>
       <c r="N81">
-        <v>-868.1754776206528</v>
+        <v>-143.3737340061534</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-868.1754776206528</v>
+        <v>-143.3737340061534</v>
       </c>
       <c r="Q81">
-        <v>-840.7754776206529</v>
+        <v>-115.9737340061534</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.3108773216434021</v>
+        <v>0.3107687577529002</v>
       </c>
       <c r="T81">
         <v>4.852995851428522</v>
       </c>
       <c r="U81">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V81">
         <v>0</v>
       </c>
       <c r="W81">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.4806554925024361</v>
+        <v>0.8485819926596235</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2441711222463295</v>
+        <v>0.166388323829324</v>
       </c>
       <c r="C82">
-        <v>-3200.174438959312</v>
+        <v>-1486.03528665742</v>
       </c>
       <c r="D82">
-        <v>3328.423598385057</v>
+        <v>5042.562750686949</v>
       </c>
       <c r="E82">
         <v>5686.900490663908</v>
@@ -8017,45 +8017,45 @@
         <v>803.5</v>
       </c>
       <c r="M82">
-        <v>1692.835926704459</v>
+        <v>958.8594774745858</v>
       </c>
       <c r="N82">
-        <v>-889.3359267044586</v>
+        <v>-155.3594774745858</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-889.3359267044586</v>
+        <v>-155.3594774745858</v>
       </c>
       <c r="Q82">
-        <v>-861.9359267044587</v>
+        <v>-127.9594774745858</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3241311877255723</v>
+        <v>0.3240171956405452</v>
       </c>
       <c r="T82">
         <v>5.095645643999949</v>
       </c>
       <c r="U82">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V82">
         <v>0</v>
       </c>
       <c r="W82">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.4746472988461556</v>
+        <v>0.8379747177513782</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2459549333050946</v>
+        <v>0.1672001348880892</v>
       </c>
       <c r="C83">
-        <v>-3320.31928351536</v>
+        <v>-1607.393003659123</v>
       </c>
       <c r="D83">
-        <v>3302.668729295813</v>
+        <v>5015.595009152051</v>
       </c>
       <c r="E83">
         <v>5781.290466130713</v>
@@ -8099,45 +8099,45 @@
         <v>803.5</v>
       </c>
       <c r="M83">
-        <v>1713.996375788264</v>
+        <v>970.8452209430181</v>
       </c>
       <c r="N83">
-        <v>-910.4963757882642</v>
+        <v>-167.3452209430181</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-910.4963757882642</v>
+        <v>-167.3452209430181</v>
       </c>
       <c r="Q83">
-        <v>-883.0963757882643</v>
+        <v>-139.9452209430181</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3387801976058656</v>
+        <v>0.338660205937416</v>
       </c>
       <c r="T83">
         <v>5.363837519999946</v>
       </c>
       <c r="U83">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V83">
         <v>0</v>
       </c>
       <c r="W83">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.4687874556505242</v>
+        <v>0.8276293508655587</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2477387443638598</v>
+        <v>0.1680119459468544</v>
       </c>
       <c r="C84">
-        <v>-3440.068613468809</v>
+        <v>-1728.463806878726</v>
       </c>
       <c r="D84">
-        <v>3277.309374809169</v>
+        <v>4988.914181399252</v>
       </c>
       <c r="E84">
         <v>5875.680441597518</v>
@@ -8181,45 +8181,45 @@
         <v>803.5</v>
       </c>
       <c r="M84">
-        <v>1735.15682487207</v>
+        <v>982.8309644114504</v>
       </c>
       <c r="N84">
-        <v>-931.65682487207</v>
+        <v>-179.3309644114504</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-931.65682487207</v>
+        <v>-179.3309644114504</v>
       </c>
       <c r="Q84">
-        <v>-904.2568248720701</v>
+        <v>-151.9309644114504</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3550568752506359</v>
+        <v>0.3549302173783835</v>
       </c>
       <c r="T84">
         <v>5.661828493333276</v>
       </c>
       <c r="U84">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V84">
         <v>0</v>
       </c>
       <c r="W84">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.463070535459664</v>
+        <v>0.8175363100013446</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.249522555422625</v>
+        <v>0.1688237570056196</v>
       </c>
       <c r="C85">
-        <v>-3559.431470205213</v>
+        <v>-1849.252250865078</v>
       </c>
       <c r="D85">
-        <v>3252.33649353957</v>
+        <v>4962.515712879705</v>
       </c>
       <c r="E85">
         <v>5970.070417064322</v>
@@ -8263,45 +8263,45 @@
         <v>803.5</v>
       </c>
       <c r="M85">
-        <v>1756.317273955876</v>
+        <v>994.8167078798828</v>
       </c>
       <c r="N85">
-        <v>-952.8172739558756</v>
+        <v>-191.3167078798828</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-952.8172739558756</v>
+        <v>-191.3167078798828</v>
       </c>
       <c r="Q85">
-        <v>-925.4172739558757</v>
+        <v>-163.9167078798828</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3732484561477322</v>
+        <v>0.3731143478124062</v>
       </c>
       <c r="T85">
         <v>5.994877228235235</v>
       </c>
       <c r="U85">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V85">
         <v>0</v>
       </c>
       <c r="W85">
-        <v>0.2241811058765187</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.4574913723818368</v>
+        <v>0.8076864749410875</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2513063664813902</v>
+        <v>0.1933235680643848</v>
       </c>
       <c r="C86">
-        <v>-3678.416621615091</v>
+        <v>-2626.987311252172</v>
       </c>
       <c r="D86">
-        <v>3227.741317596496</v>
+        <v>4279.170627959415</v>
       </c>
       <c r="E86">
         <v>6064.460392531126</v>
@@ -8345,45 +8345,45 @@
         <v>803.5</v>
       </c>
       <c r="M86">
-        <v>1777.477723039681</v>
+        <v>1230.393425234082</v>
       </c>
       <c r="N86">
-        <v>-973.9777230396812</v>
+        <v>-426.8934252340816</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-973.9777230396812</v>
+        <v>-426.8934252340816</v>
       </c>
       <c r="Q86">
-        <v>-946.5777230396812</v>
+        <v>-399.4934252340817</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3937139846569652</v>
+        <v>0.3935714945506814</v>
       </c>
       <c r="T86">
         <v>6.369557054999934</v>
       </c>
       <c r="U86">
-        <v>0.2241811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V86">
         <v>0</v>
       </c>
       <c r="W86">
-        <v>0.2241811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.4520450465201483</v>
+        <v>0.6530431515002078</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2530901775401554</v>
+        <v>0.2403173791231499</v>
       </c>
       <c r="C87">
-        <v>-3797.032572357585</v>
+        <v>-3615.473624135903</v>
       </c>
       <c r="D87">
-        <v>3203.515342320806</v>
+        <v>3385.074290542488</v>
       </c>
       <c r="E87">
         <v>6158.85036799793</v>
@@ -8427,37 +8427,37 @@
         <v>803.5</v>
       </c>
       <c r="M87">
-        <v>1798.638172123487</v>
+        <v>1678.290953403311</v>
       </c>
       <c r="N87">
-        <v>-995.138172123487</v>
+        <v>-874.7909534033111</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-995.138172123487</v>
+        <v>-874.7909534033111</v>
       </c>
       <c r="Q87">
-        <v>-967.7381721234871</v>
+        <v>-847.3909534033111</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.416908250300763</v>
+        <v>0.4167562608540601</v>
       </c>
       <c r="T87">
         <v>6.79419419199993</v>
       </c>
       <c r="U87">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V87">
         <v>0</v>
       </c>
       <c r="W87">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4467268695022641</v>
+        <v>0.4787608479749164</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2548739885989206</v>
+        <v>0.2419511901819151</v>
       </c>
       <c r="C88">
-        <v>-3915.287573665353</v>
+        <v>-3734.276011917634</v>
       </c>
       <c r="D88">
-        <v>3179.650316479843</v>
+        <v>3360.661878227562</v>
       </c>
       <c r="E88">
         <v>6253.240343464735</v>
@@ -8509,37 +8509,37 @@
         <v>803.5</v>
       </c>
       <c r="M88">
-        <v>1819.798621207293</v>
+        <v>1698.035552855115</v>
       </c>
       <c r="N88">
-        <v>-1016.298621207293</v>
+        <v>-894.5355528551147</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-1016.298621207293</v>
+        <v>-894.5355528551147</v>
       </c>
       <c r="Q88">
-        <v>-988.8986212072926</v>
+        <v>-867.1355528551147</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4434159824651032</v>
+        <v>0.4432531366293502</v>
       </c>
       <c r="T88">
         <v>7.279493777142782</v>
       </c>
       <c r="U88">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V88">
         <v>0</v>
       </c>
       <c r="W88">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4415323710196798</v>
+        <v>0.4731938613705569</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2566577996576858</v>
+        <v>0.2435850012406803</v>
       </c>
       <c r="C89">
-        <v>-4033.189632714433</v>
+        <v>-3852.728806973554</v>
       </c>
       <c r="D89">
-        <v>3156.138232897567</v>
+        <v>3336.599058638446</v>
       </c>
       <c r="E89">
         <v>6347.630318931539</v>
@@ -8591,37 +8591,37 @@
         <v>803.5</v>
       </c>
       <c r="M89">
-        <v>1840.959070291098</v>
+        <v>1717.780152306918</v>
       </c>
       <c r="N89">
-        <v>-1037.459070291098</v>
+        <v>-914.2801523069184</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-1037.459070291098</v>
+        <v>-914.2801523069184</v>
       </c>
       <c r="Q89">
-        <v>-1010.059070291098</v>
+        <v>-886.8801523069184</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4740018272701111</v>
+        <v>0.4738264548316078</v>
       </c>
       <c r="T89">
         <v>7.839454836922996</v>
       </c>
       <c r="U89">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V89">
         <v>0</v>
       </c>
       <c r="W89">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4364572862953157</v>
+        <v>0.4677548514697458</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2584416107164509</v>
+        <v>0.2452188122994455</v>
       </c>
       <c r="C90">
-        <v>-4150.746521581466</v>
+        <v>-3970.839465319242</v>
       </c>
       <c r="D90">
-        <v>3132.97131949734</v>
+        <v>3312.878375759564</v>
       </c>
       <c r="E90">
         <v>6442.020294398345</v>
@@ -8673,37 +8673,37 @@
         <v>803.5</v>
       </c>
       <c r="M90">
-        <v>1862.119519374904</v>
+        <v>1737.524751758722</v>
       </c>
       <c r="N90">
-        <v>-1058.619519374904</v>
+        <v>-934.0247517587222</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-1058.619519374904</v>
+        <v>-934.0247517587222</v>
       </c>
       <c r="Q90">
-        <v>-1031.219519374904</v>
+        <v>-906.6247517587223</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.5096853128759538</v>
+        <v>0.5094953260675752</v>
       </c>
       <c r="T90">
         <v>8.492742739999914</v>
       </c>
       <c r="U90">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V90">
         <v>0</v>
       </c>
       <c r="W90">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4314975444055961</v>
+        <v>0.4624394554303168</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2602254217752161</v>
+        <v>0.2468526233582107</v>
       </c>
       <c r="C91">
-        <v>-4267.965785809278</v>
+        <v>-4088.615232440567</v>
       </c>
       <c r="D91">
-        <v>3110.142030736332</v>
+        <v>3289.492584105043</v>
       </c>
       <c r="E91">
         <v>6536.410269865149</v>
@@ -8755,37 +8755,37 @@
         <v>803.5</v>
       </c>
       <c r="M91">
-        <v>1883.27996845871</v>
+        <v>1757.269351210526</v>
       </c>
       <c r="N91">
-        <v>-1079.77996845871</v>
+        <v>-953.7693512105257</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-1079.77996845871</v>
+        <v>-953.7693512105257</v>
       </c>
       <c r="Q91">
-        <v>-1052.37996845871</v>
+        <v>-926.3693512105257</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5518567049555859</v>
+        <v>0.5516494466191729</v>
       </c>
       <c r="T91">
         <v>9.264810261818088</v>
       </c>
       <c r="U91">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V91">
         <v>0</v>
       </c>
       <c r="W91">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4266492573898029</v>
+        <v>0.4572435064928977</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2620092328339813</v>
+        <v>0.2484864344169759</v>
       </c>
       <c r="C92">
-        <v>-4384.854752600701</v>
+        <v>-4206.063150672318</v>
       </c>
       <c r="D92">
-        <v>3087.643039411714</v>
+        <v>3266.434641340098</v>
       </c>
       <c r="E92">
         <v>6630.800245331954</v>
@@ -8837,37 +8837,37 @@
         <v>803.5</v>
       </c>
       <c r="M92">
-        <v>1904.440417542516</v>
+        <v>1777.01395066233</v>
       </c>
       <c r="N92">
-        <v>-1100.940417542516</v>
+        <v>-973.5139506623295</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-1100.940417542516</v>
+        <v>-973.5139506623295</v>
       </c>
       <c r="Q92">
-        <v>-1073.540417542516</v>
+        <v>-946.1139506623296</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.6024623754511446</v>
+        <v>0.6022343912810904</v>
       </c>
       <c r="T92">
         <v>10.1912912879999</v>
       </c>
       <c r="U92">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V92">
         <v>0</v>
       </c>
       <c r="W92">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4219087100854717</v>
+        <v>0.452163023087421</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2637930438927465</v>
+        <v>0.2501202454757411</v>
       </c>
       <c r="C93">
-        <v>-4501.420538659278</v>
+        <v>-4323.190066268642</v>
       </c>
       <c r="D93">
-        <v>3065.467228819941</v>
+        <v>3243.697701210577</v>
       </c>
       <c r="E93">
         <v>6725.190220798758</v>
@@ -8919,37 +8919,37 @@
         <v>803.5</v>
       </c>
       <c r="M93">
-        <v>1925.600866626321</v>
+        <v>1796.758550114133</v>
       </c>
       <c r="N93">
-        <v>-1122.100866626321</v>
+        <v>-993.258550114133</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-1122.100866626321</v>
+        <v>-993.258550114133</v>
       </c>
       <c r="Q93">
-        <v>-1094.700866626321</v>
+        <v>-965.858550114133</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.6643137505012717</v>
+        <v>0.664060434756767</v>
       </c>
       <c r="T93">
         <v>11.32365698666655</v>
       </c>
       <c r="U93">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V93">
         <v>0</v>
       </c>
       <c r="W93">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.417272350633983</v>
+        <v>0.4471941986578889</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2655768549515117</v>
+        <v>0.2517540565345063</v>
       </c>
       <c r="C94">
-        <v>-4617.670057694519</v>
+        <v>-4440.002636180258</v>
       </c>
       <c r="D94">
-        <v>3043.607685251506</v>
+        <v>3221.275106765766</v>
       </c>
       <c r="E94">
         <v>6819.580196265563</v>
@@ -9001,37 +9001,37 @@
         <v>803.5</v>
       </c>
       <c r="M94">
-        <v>1946.761315710127</v>
+        <v>1816.503149565937</v>
       </c>
       <c r="N94">
-        <v>-1143.261315710127</v>
+        <v>-1013.003149565937</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-1143.261315710127</v>
+        <v>-1013.003149565937</v>
       </c>
       <c r="Q94">
-        <v>-1115.861315710127</v>
+        <v>-985.6031495659369</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.7416279693139309</v>
+        <v>0.7413429891013632</v>
       </c>
       <c r="T94">
         <v>12.73911410999988</v>
       </c>
       <c r="U94">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V94">
         <v>0</v>
       </c>
       <c r="W94">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4127367816053528</v>
+        <v>0.4423333921507379</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2673606660102769</v>
+        <v>0.2533878675932714</v>
       </c>
       <c r="C95">
-        <v>-4733.610027608305</v>
+        <v>-4556.507334552478</v>
       </c>
       <c r="D95">
-        <v>3022.057690804525</v>
+        <v>3199.160383860351</v>
       </c>
       <c r="E95">
         <v>6913.970171732369</v>
@@ -9083,37 +9083,37 @@
         <v>803.5</v>
       </c>
       <c r="M95">
-        <v>1967.921764793933</v>
+        <v>1836.24774901774</v>
       </c>
       <c r="N95">
-        <v>-1164.421764793933</v>
+        <v>-1032.74774901774</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-1164.421764793933</v>
+        <v>-1032.74774901774</v>
       </c>
       <c r="Q95">
-        <v>-1137.021764793933</v>
+        <v>-1005.347749017741</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.8410319649302068</v>
+        <v>0.8407062732587008</v>
       </c>
       <c r="T95">
         <v>14.55898755428557</v>
       </c>
       <c r="U95">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V95">
         <v>0</v>
       </c>
       <c r="W95">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4082987516956178</v>
+        <v>0.4375771191168589</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2691444770690421</v>
+        <v>0.2550216786520366</v>
       </c>
       <c r="C96">
-        <v>-4849.246977378141</v>
+        <v>-4672.710458957418</v>
       </c>
       <c r="D96">
-        <v>3000.810716501493</v>
+        <v>3177.347234922215</v>
       </c>
       <c r="E96">
         <v>7008.360147199172</v>
@@ -9165,37 +9165,37 @@
         <v>803.5</v>
       </c>
       <c r="M96">
-        <v>1989.082213877739</v>
+        <v>1855.992348469544</v>
       </c>
       <c r="N96">
-        <v>-1185.582213877739</v>
+        <v>-1052.492348469544</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-1185.582213877739</v>
+        <v>-1052.492348469544</v>
       </c>
       <c r="Q96">
-        <v>-1158.182213877739</v>
+        <v>-1025.092348469544</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.9735706257519082</v>
+        <v>0.9731906521351512</v>
       </c>
       <c r="T96">
         <v>16.98548547999984</v>
       </c>
       <c r="U96">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V96">
         <v>0</v>
       </c>
       <c r="W96">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4039551479541751</v>
+        <v>0.4329220433815733</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2709282881278073</v>
+        <v>0.2566554897108018</v>
       </c>
       <c r="C97">
-        <v>-4964.587253652084</v>
+        <v>-4788.618136372963</v>
       </c>
       <c r="D97">
-        <v>2979.860415694356</v>
+        <v>3155.829532973476</v>
       </c>
       <c r="E97">
         <v>7102.750122665978</v>
@@ -9247,37 +9247,37 @@
         <v>803.5</v>
       </c>
       <c r="M97">
-        <v>2010.242662961545</v>
+        <v>1875.736947921348</v>
       </c>
       <c r="N97">
-        <v>-1206.742662961545</v>
+        <v>-1072.236947921348</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-1206.742662961545</v>
+        <v>-1072.236947921348</v>
       </c>
       <c r="Q97">
-        <v>-1179.342662961544</v>
+        <v>-1044.836947921348</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.159124750902291</v>
+        <v>1.158668782562182</v>
       </c>
       <c r="T97">
         <v>20.38258257599982</v>
       </c>
       <c r="U97">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V97">
         <v>0</v>
       </c>
       <c r="W97">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3997029885020258</v>
+        <v>0.4283649692407145</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2727120991865724</v>
+        <v>0.258289300769567</v>
       </c>
       <c r="C98">
-        <v>-5079.637027069315</v>
+        <v>-4904.236328920408</v>
       </c>
       <c r="D98">
-        <v>2959.200617743927</v>
+        <v>3134.601315892834</v>
       </c>
       <c r="E98">
         <v>7197.140098132782</v>
@@ -9329,37 +9329,37 @@
         <v>803.5</v>
       </c>
       <c r="M98">
-        <v>2031.40311204535</v>
+        <v>1895.481547373151</v>
       </c>
       <c r="N98">
-        <v>-1227.90311204535</v>
+        <v>-1091.981547373151</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-1227.90311204535</v>
+        <v>-1091.981547373151</v>
       </c>
       <c r="Q98">
-        <v>-1200.50311204535</v>
+        <v>-1064.581547373151</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.43745593862786</v>
+        <v>1.436885978202725</v>
       </c>
       <c r="T98">
         <v>25.47822821999972</v>
       </c>
       <c r="U98">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V98">
         <v>0</v>
       </c>
       <c r="W98">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3955394157051297</v>
+        <v>0.4239028341444572</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2744959102453376</v>
+        <v>0.2599231118283322</v>
       </c>
       <c r="C99">
-        <v>-5194.402298319616</v>
+        <v>-5019.570839372107</v>
       </c>
       <c r="D99">
-        <v>2938.82532196043</v>
+        <v>3113.656780907939</v>
       </c>
       <c r="E99">
         <v>7291.530073599585</v>
@@ -9411,37 +9411,37 @@
         <v>803.5</v>
       </c>
       <c r="M99">
-        <v>2052.563561129155</v>
+        <v>1915.226146824955</v>
       </c>
       <c r="N99">
-        <v>-1249.063561129155</v>
+        <v>-1111.726146824955</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-1249.063561129155</v>
+        <v>-1111.726146824955</v>
       </c>
       <c r="Q99">
-        <v>-1221.663561129155</v>
+        <v>-1084.326146824955</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.901341251503814</v>
+        <v>1.900581304270299</v>
       </c>
       <c r="T99">
         <v>33.97097095999963</v>
       </c>
       <c r="U99">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V99">
         <v>0</v>
       </c>
       <c r="W99">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3914616897700254</v>
+        <v>0.4195327018336896</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2762797213041028</v>
+        <v>0.2615569228870974</v>
       </c>
       <c r="C100">
-        <v>-5308.888903954197</v>
+        <v>-5134.627316439749</v>
       </c>
       <c r="D100">
-        <v>2918.728691792654</v>
+        <v>3092.990279307102</v>
       </c>
       <c r="E100">
         <v>7385.920049066391</v>
@@ -9493,37 +9493,37 @@
         <v>803.5</v>
       </c>
       <c r="M100">
-        <v>2073.724010212962</v>
+        <v>1934.970746276759</v>
       </c>
       <c r="N100">
-        <v>-1270.224010212962</v>
+        <v>-1131.470746276759</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-1270.224010212962</v>
+        <v>-1131.470746276759</v>
       </c>
       <c r="Q100">
-        <v>-1242.824010212962</v>
+        <v>-1104.070746276759</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.82911187725572</v>
+        <v>2.827971956405449</v>
       </c>
       <c r="T100">
         <v>50.95645643999944</v>
       </c>
       <c r="U100">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V100">
         <v>0</v>
       </c>
       <c r="W100">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3874671827315557</v>
+        <v>0.4152517558966111</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.278063532362868</v>
+        <v>0.2631907339458626</v>
       </c>
       <c r="C101">
-        <v>-5423.102521959745</v>
+        <v>-5249.411259853443</v>
       </c>
       <c r="D101">
-        <v>2898.90504925391</v>
+        <v>3072.596311360213</v>
       </c>
       <c r="E101">
         <v>7480.310024533194</v>
@@ -9575,37 +9575,37 @@
         <v>803.5</v>
       </c>
       <c r="M101">
-        <v>2094.884459296767</v>
+        <v>1954.715345728562</v>
       </c>
       <c r="N101">
-        <v>-1291.384459296767</v>
+        <v>-1151.215345728562</v>
       </c>
       <c r="O101">
         <v>-0</v>
       </c>
       <c r="P101">
-        <v>-1291.384459296767</v>
+        <v>-1151.215345728562</v>
       </c>
       <c r="Q101">
-        <v>-1263.984459296767</v>
+        <v>-1123.815345728562</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.61242375451144</v>
+        <v>5.610143912810898</v>
       </c>
       <c r="T101">
         <v>101.9129128799989</v>
       </c>
       <c r="U101">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V101">
         <v>0</v>
       </c>
       <c r="W101">
-        <v>0.2241811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3835533728049744</v>
+        <v>0.4110572937158373</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/bermuda/bermuda_information_services.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_information_services.xlsx
@@ -1139,43 +1139,43 @@
         <v>10.4080310880829</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>145.064691289961</v>
       </c>
       <c r="G2">
         <v>2.24370868537786</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.113599681630527</v>
       </c>
       <c r="I2">
         <v>0.197510120906441</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>7574.7</v>
       </c>
       <c r="L2">
-        <v>9871.409639791211</v>
+        <v>9763.7918224319</v>
       </c>
       <c r="M2">
         <v>8416.39754668046</v>
       </c>
       <c r="N2">
-        <v>8848.8096397912</v>
+        <v>8835.581797898711</v>
       </c>
       <c r="O2">
         <v>1864.29754668046</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>94.3899754668046</v>
       </c>
       <c r="Q2">
         <v>0.1058639340558</v>
       </c>
       <c r="R2">
-        <v>0.101443439128109</v>
+        <v>0.101572250186874</v>
       </c>
       <c r="S2">
         <v>0.0681811058765187</v>
@@ -1197,13 +1197,13 @@
         <v>0.115138493328988</v>
       </c>
       <c r="X2">
-        <v>0.101443439128109</v>
+        <v>0.102005494068797</v>
       </c>
       <c r="Y2">
         <v>1.26995885599346</v>
       </c>
       <c r="Z2">
-        <v>1.01912912879999</v>
+        <v>1.02942336242423</v>
       </c>
       <c r="AA2">
         <v>1646.1</v>
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.101443439128109</v>
+        <v>0.1015722501868742</v>
       </c>
       <c r="C2">
-        <v>9871.409639791205</v>
+        <v>9763.791822431904</v>
       </c>
       <c r="D2">
-        <v>8848.809639791205</v>
+        <v>8835.581797898709</v>
       </c>
       <c r="E2">
-        <v>-1864.297546680461</v>
+        <v>-1769.907571213656</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>94.38997546680461</v>
       </c>
       <c r="G2">
         <v>1022.6</v>
@@ -1457,28 +1457,28 @@
         <v>803.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.538908144049567</v>
       </c>
       <c r="N2">
-        <v>803.5</v>
+        <v>797.9610918559505</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>803.5</v>
+        <v>797.9610918559505</v>
       </c>
       <c r="Q2">
-        <v>830.9</v>
+        <v>825.3610918559505</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.101443439128109</v>
+        <v>0.102005494068797</v>
       </c>
       <c r="T2">
-        <v>1.01912912879999</v>
+        <v>1.029423362424232</v>
       </c>
       <c r="U2">
         <v>0.05868110587651873</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>145.0646912899608</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1015722501868742</v>
+        <v>0.1017010612456394</v>
       </c>
       <c r="C3">
-        <v>9763.791822431904</v>
+        <v>9656.213493915098</v>
       </c>
       <c r="D3">
-        <v>8835.581797898709</v>
+        <v>8822.393444848707</v>
       </c>
       <c r="E3">
-        <v>-1769.907571213656</v>
+        <v>-1675.517595746852</v>
       </c>
       <c r="F3">
-        <v>94.38997546680461</v>
+        <v>188.7799509336092</v>
       </c>
       <c r="G3">
         <v>1022.6</v>
@@ -1539,28 +1539,28 @@
         <v>803.5</v>
       </c>
       <c r="M3">
-        <v>5.538908144049567</v>
+        <v>11.07781628809913</v>
       </c>
       <c r="N3">
-        <v>797.9610918559505</v>
+        <v>792.4221837119009</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>797.9610918559505</v>
+        <v>792.4221837119009</v>
       </c>
       <c r="Q3">
-        <v>825.3610918559505</v>
+        <v>819.8221837119008</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.102005494068797</v>
+        <v>0.1025790195184786</v>
       </c>
       <c r="T3">
-        <v>1.029423362424232</v>
+        <v>1.039927682448969</v>
       </c>
       <c r="U3">
         <v>0.05868110587651873</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>145.0646912899608</v>
+        <v>72.53234564498038</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1017010612456394</v>
+        <v>0.1018298723044046</v>
       </c>
       <c r="C4">
-        <v>9656.213493915098</v>
+        <v>9548.674477676313</v>
       </c>
       <c r="D4">
-        <v>8822.393444848707</v>
+        <v>8809.244404076728</v>
       </c>
       <c r="E4">
-        <v>-1675.517595746852</v>
+        <v>-1581.127620280047</v>
       </c>
       <c r="F4">
-        <v>188.7799509336092</v>
+        <v>283.1699264004138</v>
       </c>
       <c r="G4">
         <v>1022.6</v>
@@ -1621,28 +1621,28 @@
         <v>803.5</v>
       </c>
       <c r="M4">
-        <v>11.07781628809913</v>
+        <v>16.6167244321487</v>
       </c>
       <c r="N4">
-        <v>792.4221837119009</v>
+        <v>786.8832755678513</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>792.4221837119009</v>
+        <v>786.8832755678513</v>
       </c>
       <c r="Q4">
-        <v>819.8221837119008</v>
+        <v>814.2832755678513</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1025790195184786</v>
+        <v>0.1031643702351639</v>
       </c>
       <c r="T4">
-        <v>1.039927682448969</v>
+        <v>1.050648586391742</v>
       </c>
       <c r="U4">
         <v>0.05868110587651873</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>72.53234564498038</v>
+        <v>48.35489709665359</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1018298723044046</v>
+        <v>0.1019586833631698</v>
       </c>
       <c r="C5">
-        <v>9548.674477676313</v>
+        <v>9441.174598202138</v>
       </c>
       <c r="D5">
-        <v>8809.244404076728</v>
+        <v>8796.134500069356</v>
       </c>
       <c r="E5">
-        <v>-1581.127620280047</v>
+        <v>-1486.737644813242</v>
       </c>
       <c r="F5">
-        <v>283.1699264004138</v>
+        <v>377.5599018672185</v>
       </c>
       <c r="G5">
         <v>1022.6</v>
@@ -1703,28 +1703,28 @@
         <v>803.5</v>
       </c>
       <c r="M5">
-        <v>16.6167244321487</v>
+        <v>22.15563257619827</v>
       </c>
       <c r="N5">
-        <v>786.8832755678513</v>
+        <v>781.3443674238017</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>786.8832755678513</v>
+        <v>781.3443674238017</v>
       </c>
       <c r="Q5">
-        <v>814.2832755678513</v>
+        <v>808.7443674238017</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1031643702351639</v>
+        <v>0.1037619157584469</v>
       </c>
       <c r="T5">
-        <v>1.050648586391742</v>
+        <v>1.061592842499989</v>
       </c>
       <c r="U5">
         <v>0.05868110587651873</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.35489709665359</v>
+        <v>36.26617282249019</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1019586833631698</v>
+        <v>0.102087494421935</v>
       </c>
       <c r="C6">
-        <v>9441.174598202138</v>
+        <v>9333.713681022396</v>
       </c>
       <c r="D6">
-        <v>8796.134500069356</v>
+        <v>8783.06355835642</v>
       </c>
       <c r="E6">
-        <v>-1486.737644813242</v>
+        <v>-1392.347669346438</v>
       </c>
       <c r="F6">
-        <v>377.5599018672185</v>
+        <v>471.9498773340231</v>
       </c>
       <c r="G6">
         <v>1022.6</v>
@@ -1785,28 +1785,28 @@
         <v>803.5</v>
       </c>
       <c r="M6">
-        <v>22.15563257619827</v>
+        <v>27.69454072024784</v>
       </c>
       <c r="N6">
-        <v>781.3443674238017</v>
+        <v>775.8054592797522</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>781.3443674238017</v>
+        <v>775.8054592797522</v>
       </c>
       <c r="Q6">
-        <v>808.7443674238017</v>
+        <v>803.2054592797522</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1037619157584469</v>
+        <v>0.1043720411874832</v>
       </c>
       <c r="T6">
-        <v>1.061592842499989</v>
+        <v>1.072767503999989</v>
       </c>
       <c r="U6">
         <v>0.05868110587651873</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.26617282249019</v>
+        <v>29.01293825799215</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.102087494421935</v>
+        <v>0.1022163054807001</v>
       </c>
       <c r="C7">
-        <v>9333.713681022396</v>
+        <v>9226.291552702423</v>
       </c>
       <c r="D7">
-        <v>8783.06355835642</v>
+        <v>8770.03140550325</v>
       </c>
       <c r="E7">
-        <v>-1392.347669346438</v>
+        <v>-1297.957693879633</v>
       </c>
       <c r="F7">
-        <v>471.9498773340231</v>
+        <v>566.3398528008277</v>
       </c>
       <c r="G7">
         <v>1022.6</v>
@@ -1867,28 +1867,28 @@
         <v>803.5</v>
       </c>
       <c r="M7">
-        <v>27.69454072024784</v>
+        <v>33.2334488642974</v>
       </c>
       <c r="N7">
-        <v>775.8054592797522</v>
+        <v>770.2665511357026</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>775.8054592797522</v>
+        <v>770.2665511357026</v>
       </c>
       <c r="Q7">
-        <v>803.2054592797522</v>
+        <v>797.6665511357025</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1043720411874832</v>
+        <v>0.1049951480086266</v>
       </c>
       <c r="T7">
-        <v>1.072767503999989</v>
+        <v>1.084179924255308</v>
       </c>
       <c r="U7">
         <v>0.05868110587651873</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.01293825799215</v>
+        <v>24.17744854832679</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1022163054807001</v>
+        <v>0.1023451165394653</v>
       </c>
       <c r="C8">
-        <v>9226.291552702423</v>
+        <v>9118.908040835375</v>
       </c>
       <c r="D8">
-        <v>8770.03140550325</v>
+        <v>8757.037869103007</v>
       </c>
       <c r="E8">
-        <v>-1297.957693879633</v>
+        <v>-1203.567718412829</v>
       </c>
       <c r="F8">
-        <v>566.3398528008277</v>
+        <v>660.7298282676322</v>
       </c>
       <c r="G8">
         <v>1022.6</v>
@@ -1949,28 +1949,28 @@
         <v>803.5</v>
       </c>
       <c r="M8">
-        <v>33.2334488642974</v>
+        <v>38.77235700834697</v>
       </c>
       <c r="N8">
-        <v>770.2665511357026</v>
+        <v>764.7276429916531</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>770.2665511357026</v>
+        <v>764.7276429916531</v>
       </c>
       <c r="Q8">
-        <v>797.6665511357025</v>
+        <v>792.127642991653</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1049951480086266</v>
+        <v>0.1056316549764613</v>
       </c>
       <c r="T8">
-        <v>1.084179924255308</v>
+        <v>1.095837772903214</v>
       </c>
       <c r="U8">
         <v>0.05868110587651873</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.17744854832679</v>
+        <v>20.72352732713725</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1023451165394653</v>
+        <v>0.1024739275982305</v>
       </c>
       <c r="C9">
-        <v>9118.908040835375</v>
+        <v>9011.562974034649</v>
       </c>
       <c r="D9">
-        <v>8757.037869103007</v>
+        <v>8744.082777769085</v>
       </c>
       <c r="E9">
-        <v>-1203.567718412829</v>
+        <v>-1109.177742946024</v>
       </c>
       <c r="F9">
-        <v>660.7298282676323</v>
+        <v>755.1198037344369</v>
       </c>
       <c r="G9">
         <v>1022.6</v>
@@ -2031,28 +2031,28 @@
         <v>803.5</v>
       </c>
       <c r="M9">
-        <v>38.77235700834697</v>
+        <v>44.31126515239654</v>
       </c>
       <c r="N9">
-        <v>764.7276429916531</v>
+        <v>759.1887348476034</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>764.7276429916531</v>
+        <v>759.1887348476034</v>
       </c>
       <c r="Q9">
-        <v>792.127642991653</v>
+        <v>786.5887348476034</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1056316549764613</v>
+        <v>0.1062819990522924</v>
       </c>
       <c r="T9">
-        <v>1.095837772903214</v>
+        <v>1.107749053043467</v>
       </c>
       <c r="U9">
         <v>0.05868110587651873</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.72352732713725</v>
+        <v>18.1330864112451</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1024739275982305</v>
+        <v>0.1026027386569957</v>
       </c>
       <c r="C10">
-        <v>9011.562974034649</v>
+        <v>8904.256181926319</v>
       </c>
       <c r="D10">
-        <v>8744.082777769085</v>
+        <v>8731.165961127561</v>
       </c>
       <c r="E10">
-        <v>-1109.177742946024</v>
+        <v>-1014.787767479219</v>
       </c>
       <c r="F10">
-        <v>755.1198037344369</v>
+        <v>849.5097792012415</v>
       </c>
       <c r="G10">
         <v>1022.6</v>
@@ -2113,28 +2113,28 @@
         <v>803.5</v>
       </c>
       <c r="M10">
-        <v>44.31126515239654</v>
+        <v>49.8501732964461</v>
       </c>
       <c r="N10">
-        <v>759.1887348476034</v>
+        <v>753.6498267035539</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>759.1887348476034</v>
+        <v>753.6498267035539</v>
       </c>
       <c r="Q10">
-        <v>786.5887348476034</v>
+        <v>781.0498267035539</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1062819990522924</v>
+        <v>0.1069466364045154</v>
       </c>
       <c r="T10">
-        <v>1.107749053043467</v>
+        <v>1.119922119560428</v>
       </c>
       <c r="U10">
         <v>0.05868110587651873</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.1330864112451</v>
+        <v>16.11829903221786</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1026027386569957</v>
+        <v>0.1027315497157609</v>
       </c>
       <c r="C11">
-        <v>8904.256181926319</v>
+        <v>8796.987495141708</v>
       </c>
       <c r="D11">
-        <v>8731.165961127561</v>
+        <v>8718.287249809753</v>
       </c>
       <c r="E11">
-        <v>-1014.787767479219</v>
+        <v>-920.3977920124149</v>
       </c>
       <c r="F11">
-        <v>849.5097792012415</v>
+        <v>943.8997546680461</v>
       </c>
       <c r="G11">
         <v>1022.6</v>
@@ -2195,28 +2195,28 @@
         <v>803.5</v>
       </c>
       <c r="M11">
-        <v>49.8501732964461</v>
+        <v>55.38908144049567</v>
       </c>
       <c r="N11">
-        <v>753.6498267035539</v>
+        <v>748.1109185595043</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>753.6498267035539</v>
+        <v>748.1109185595043</v>
       </c>
       <c r="Q11">
-        <v>781.0498267035539</v>
+        <v>775.5109185595043</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1069466364045154</v>
+        <v>0.1076260434756767</v>
       </c>
       <c r="T11">
-        <v>1.119922119560428</v>
+        <v>1.132365698666655</v>
       </c>
       <c r="U11">
         <v>0.05868110587651873</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.11829903221786</v>
+        <v>14.50646912899608</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1027315497157609</v>
+        <v>0.1028603607745261</v>
       </c>
       <c r="C12">
-        <v>8796.987495141708</v>
+        <v>8689.75674530994</v>
       </c>
       <c r="D12">
-        <v>8718.287249809753</v>
+        <v>8705.446475444791</v>
       </c>
       <c r="E12">
-        <v>-920.3977920124148</v>
+        <v>-826.0078165456102</v>
       </c>
       <c r="F12">
-        <v>943.8997546680462</v>
+        <v>1038.289730134851</v>
       </c>
       <c r="G12">
         <v>1022.6</v>
@@ -2277,28 +2277,28 @@
         <v>803.5</v>
       </c>
       <c r="M12">
-        <v>55.38908144049567</v>
+        <v>60.92798958454524</v>
       </c>
       <c r="N12">
-        <v>748.1109185595043</v>
+        <v>742.5720104154548</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>748.1109185595043</v>
+        <v>742.5720104154548</v>
       </c>
       <c r="Q12">
-        <v>775.5109185595043</v>
+        <v>769.9720104154547</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1076260434756767</v>
+        <v>0.1083207181214708</v>
       </c>
       <c r="T12">
-        <v>1.132365698666655</v>
+        <v>1.145088908764033</v>
       </c>
       <c r="U12">
         <v>0.05868110587651873</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.50646912899608</v>
+        <v>13.18769920817825</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1028603607745261</v>
+        <v>0.1029891718332913</v>
       </c>
       <c r="C13">
-        <v>8689.75674530994</v>
+        <v>8582.563765050638</v>
       </c>
       <c r="D13">
-        <v>8705.446475444791</v>
+        <v>8692.643470652292</v>
       </c>
       <c r="E13">
-        <v>-826.0078165456102</v>
+        <v>-731.6178410788057</v>
       </c>
       <c r="F13">
-        <v>1038.289730134851</v>
+        <v>1132.679705601655</v>
       </c>
       <c r="G13">
         <v>1022.6</v>
@@ -2359,28 +2359,28 @@
         <v>803.5</v>
       </c>
       <c r="M13">
-        <v>60.92798958454524</v>
+        <v>66.4668977285948</v>
       </c>
       <c r="N13">
-        <v>742.5720104154548</v>
+        <v>737.0331022714051</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>742.5720104154548</v>
+        <v>737.0331022714051</v>
       </c>
       <c r="Q13">
-        <v>769.9720104154547</v>
+        <v>764.4331022714051</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1083207181214708</v>
+        <v>0.1090311808273966</v>
       </c>
       <c r="T13">
-        <v>1.145088908764033</v>
+        <v>1.158101282727261</v>
       </c>
       <c r="U13">
         <v>0.05868110587651873</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>13.18769920817825</v>
+        <v>12.0887242741634</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1029891718332913</v>
+        <v>0.1031179828920565</v>
       </c>
       <c r="C14">
-        <v>8582.563765050638</v>
+        <v>8475.408387966621</v>
       </c>
       <c r="D14">
-        <v>8692.643470652292</v>
+        <v>8679.878069035081</v>
       </c>
       <c r="E14">
-        <v>-731.6178410788057</v>
+        <v>-637.2278656120011</v>
       </c>
       <c r="F14">
-        <v>1132.679705601655</v>
+        <v>1227.06968106846</v>
       </c>
       <c r="G14">
         <v>1022.6</v>
@@ -2441,28 +2441,28 @@
         <v>803.5</v>
       </c>
       <c r="M14">
-        <v>66.4668977285948</v>
+        <v>72.00580587264436</v>
       </c>
       <c r="N14">
-        <v>737.0331022714051</v>
+        <v>731.4941941273556</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>737.0331022714051</v>
+        <v>731.4941941273556</v>
       </c>
       <c r="Q14">
-        <v>764.4331022714051</v>
+        <v>758.8941941273556</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1090311808273966</v>
+        <v>0.1097579760093207</v>
       </c>
       <c r="T14">
-        <v>1.158101282727261</v>
+        <v>1.171412791724126</v>
       </c>
       <c r="U14">
         <v>0.05868110587651873</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.0887242741634</v>
+        <v>11.15882240692006</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1031179828920565</v>
+        <v>0.1032467939508216</v>
       </c>
       <c r="C15">
-        <v>8475.408387966621</v>
+        <v>8368.29044863673</v>
       </c>
       <c r="D15">
-        <v>8679.878069035081</v>
+        <v>8667.150105171993</v>
       </c>
       <c r="E15">
-        <v>-637.2278656120011</v>
+        <v>-542.8378901451963</v>
       </c>
       <c r="F15">
-        <v>1227.06968106846</v>
+        <v>1321.459656535265</v>
       </c>
       <c r="G15">
         <v>1022.6</v>
@@ -2523,28 +2523,28 @@
         <v>803.5</v>
       </c>
       <c r="M15">
-        <v>72.00580587264436</v>
+        <v>77.54471401669394</v>
       </c>
       <c r="N15">
-        <v>731.4941941273556</v>
+        <v>725.9552859833061</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>731.4941941273556</v>
+        <v>725.9552859833061</v>
       </c>
       <c r="Q15">
-        <v>758.8941941273556</v>
+        <v>753.3552859833061</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1097579760093207</v>
+        <v>0.1105016734047779</v>
       </c>
       <c r="T15">
-        <v>1.171412791724126</v>
+        <v>1.185033870697662</v>
       </c>
       <c r="U15">
         <v>0.05868110587651873</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.15882240692006</v>
+        <v>10.36176366356863</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1032467939508216</v>
+        <v>0.1033756050095868</v>
       </c>
       <c r="C16">
-        <v>8368.29044863673</v>
+        <v>8261.209782608648</v>
       </c>
       <c r="D16">
-        <v>8667.150105171993</v>
+        <v>8654.459414610717</v>
       </c>
       <c r="E16">
-        <v>-542.8378901451963</v>
+        <v>-448.4479146783917</v>
       </c>
       <c r="F16">
-        <v>1321.459656535265</v>
+        <v>1415.849632002069</v>
       </c>
       <c r="G16">
         <v>1022.6</v>
@@ -2605,28 +2605,28 @@
         <v>803.5</v>
       </c>
       <c r="M16">
-        <v>77.54471401669394</v>
+        <v>83.0836221607435</v>
       </c>
       <c r="N16">
-        <v>725.9552859833061</v>
+        <v>720.4163778392565</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>725.9552859833061</v>
+        <v>720.4163778392565</v>
       </c>
       <c r="Q16">
-        <v>753.3552859833061</v>
+        <v>747.8163778392565</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1105016734047779</v>
+        <v>0.1112628695624812</v>
       </c>
       <c r="T16">
-        <v>1.185033870697662</v>
+        <v>1.198975445647047</v>
       </c>
       <c r="U16">
         <v>0.05868110587651873</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.36176366356863</v>
+        <v>9.670979419330719</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1033756050095868</v>
+        <v>0.103504416068352</v>
       </c>
       <c r="C17">
-        <v>8261.209782608648</v>
+        <v>8154.166226391849</v>
       </c>
       <c r="D17">
-        <v>8654.459414610717</v>
+        <v>8641.805833860722</v>
       </c>
       <c r="E17">
-        <v>-448.447914678392</v>
+        <v>-354.0579392115872</v>
       </c>
       <c r="F17">
-        <v>1415.849632002069</v>
+        <v>1510.239607468874</v>
       </c>
       <c r="G17">
         <v>1022.6</v>
@@ -2687,28 +2687,28 @@
         <v>803.5</v>
       </c>
       <c r="M17">
-        <v>83.08362216074349</v>
+        <v>88.62253030479307</v>
       </c>
       <c r="N17">
-        <v>720.4163778392565</v>
+        <v>714.877469695207</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>720.4163778392565</v>
+        <v>714.877469695207</v>
       </c>
       <c r="Q17">
-        <v>747.8163778392565</v>
+        <v>742.2774696952069</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1112628695624812</v>
+        <v>0.112042189438225</v>
       </c>
       <c r="T17">
-        <v>1.198975445647047</v>
+        <v>1.21324896285713</v>
       </c>
       <c r="U17">
         <v>0.05868110587651873</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.67097941933072</v>
+        <v>9.066543205622548</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.103504416068352</v>
+        <v>0.1038882271271172</v>
       </c>
       <c r="C18">
-        <v>8154.166226391849</v>
+        <v>8022.291516482552</v>
       </c>
       <c r="D18">
-        <v>8641.805833860722</v>
+        <v>8604.32109941823</v>
       </c>
       <c r="E18">
-        <v>-354.0579392115872</v>
+        <v>-259.6679637447826</v>
       </c>
       <c r="F18">
-        <v>1510.239607468874</v>
+        <v>1604.629582935678</v>
       </c>
       <c r="G18">
         <v>1022.6</v>
@@ -2769,45 +2769,45 @@
         <v>803.5</v>
       </c>
       <c r="M18">
-        <v>88.62253030479307</v>
+        <v>96.56838282324614</v>
       </c>
       <c r="N18">
-        <v>714.877469695207</v>
+        <v>706.9316171767539</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>714.877469695207</v>
+        <v>706.9316171767539</v>
       </c>
       <c r="Q18">
-        <v>742.2774696952069</v>
+        <v>734.3316171767539</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.112042189438225</v>
+        <v>0.1128402881061555</v>
       </c>
       <c r="T18">
-        <v>1.21324896285713</v>
+        <v>1.227866420240951</v>
       </c>
       <c r="U18">
-        <v>0.05868110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
       <c r="W18">
-        <v>0.05868110587651873</v>
+        <v>0.06018110587651872</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.066543205622548</v>
+        <v>8.320528691783993</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1038882271271172</v>
+        <v>0.1040320381858824</v>
       </c>
       <c r="C19">
-        <v>8022.291516482552</v>
+        <v>7913.93991271659</v>
       </c>
       <c r="D19">
-        <v>8604.32109941823</v>
+        <v>8590.359471119073</v>
       </c>
       <c r="E19">
-        <v>-259.6679637447826</v>
+        <v>-165.2779882779778</v>
       </c>
       <c r="F19">
-        <v>1604.629582935678</v>
+        <v>1699.019558402483</v>
       </c>
       <c r="G19">
         <v>1022.6</v>
@@ -2851,28 +2851,28 @@
         <v>803.5</v>
       </c>
       <c r="M19">
-        <v>96.56838282324614</v>
+        <v>102.2488759304959</v>
       </c>
       <c r="N19">
-        <v>706.9316171767539</v>
+        <v>701.251124069504</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>706.9316171767539</v>
+        <v>701.251124069504</v>
       </c>
       <c r="Q19">
-        <v>734.3316171767539</v>
+        <v>728.651124069504</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1128402881061555</v>
+        <v>0.1136578525952549</v>
       </c>
       <c r="T19">
-        <v>1.227866420240951</v>
+        <v>1.242840400975597</v>
       </c>
       <c r="U19">
         <v>0.06018110587651872</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.320528691783993</v>
+        <v>7.858277097795992</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1040320381858824</v>
+        <v>0.1041758492446476</v>
       </c>
       <c r="C20">
-        <v>7913.939912716588</v>
+        <v>7805.633544659622</v>
       </c>
       <c r="D20">
-        <v>8590.359471119071</v>
+        <v>8576.44307852891</v>
       </c>
       <c r="E20">
-        <v>-165.277988277978</v>
+        <v>-70.88801281117344</v>
       </c>
       <c r="F20">
-        <v>1699.019558402483</v>
+        <v>1793.409533869288</v>
       </c>
       <c r="G20">
         <v>1022.6</v>
@@ -2933,28 +2933,28 @@
         <v>803.5</v>
       </c>
       <c r="M20">
-        <v>102.2488759304959</v>
+        <v>107.9293690377457</v>
       </c>
       <c r="N20">
-        <v>701.251124069504</v>
+        <v>695.5706309622543</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>701.251124069504</v>
+        <v>695.5706309622543</v>
       </c>
       <c r="Q20">
-        <v>728.651124069504</v>
+        <v>722.9706309622543</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1136578525952549</v>
+        <v>0.114495603861863</v>
       </c>
       <c r="T20">
-        <v>1.242840400975597</v>
+        <v>1.258184109629617</v>
       </c>
       <c r="U20">
         <v>0.06018110587651872</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.858277097795993</v>
+        <v>7.444683566333046</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1041758492446476</v>
+        <v>0.1043196603034128</v>
       </c>
       <c r="C21">
-        <v>7805.633544659622</v>
+        <v>7697.372192821521</v>
       </c>
       <c r="D21">
-        <v>8576.44307852891</v>
+        <v>8562.571702157613</v>
       </c>
       <c r="E21">
-        <v>-70.88801281117344</v>
+        <v>23.50196265563136</v>
       </c>
       <c r="F21">
-        <v>1793.409533869288</v>
+        <v>1887.799509336092</v>
       </c>
       <c r="G21">
         <v>1022.6</v>
@@ -3015,28 +3015,28 @@
         <v>803.5</v>
       </c>
       <c r="M21">
-        <v>107.9293690377457</v>
+        <v>113.6098621449955</v>
       </c>
       <c r="N21">
-        <v>695.5706309622543</v>
+        <v>689.8901378550045</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>695.5706309622543</v>
+        <v>689.8901378550045</v>
       </c>
       <c r="Q21">
-        <v>722.9706309622543</v>
+        <v>717.2901378550044</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.114495603861863</v>
+        <v>0.1153542989101363</v>
       </c>
       <c r="T21">
-        <v>1.258184109629617</v>
+        <v>1.273911410999987</v>
       </c>
       <c r="U21">
         <v>0.06018110587651872</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.444683566333046</v>
+        <v>7.072449388016392</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1043196603034128</v>
+        <v>0.104463471362178</v>
       </c>
       <c r="C22">
-        <v>7697.372192821521</v>
+        <v>7589.155639129855</v>
       </c>
       <c r="D22">
-        <v>8562.571702157613</v>
+        <v>8548.745123932751</v>
       </c>
       <c r="E22">
-        <v>23.50196265563136</v>
+        <v>117.8919381224359</v>
       </c>
       <c r="F22">
-        <v>1887.799509336092</v>
+        <v>1982.189484802897</v>
       </c>
       <c r="G22">
         <v>1022.6</v>
@@ -3097,28 +3097,28 @@
         <v>803.5</v>
       </c>
       <c r="M22">
-        <v>113.6098621449955</v>
+        <v>119.2903552522452</v>
       </c>
       <c r="N22">
-        <v>689.8901378550045</v>
+        <v>684.2096447477547</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>689.8901378550045</v>
+        <v>684.2096447477547</v>
       </c>
       <c r="Q22">
-        <v>717.2901378550044</v>
+        <v>711.6096447477547</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1153542989101363</v>
+        <v>0.1162347330735557</v>
       </c>
       <c r="T22">
-        <v>1.273911410999987</v>
+        <v>1.290036871898721</v>
       </c>
       <c r="U22">
         <v>0.06018110587651872</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.072449388016392</v>
+        <v>6.735666083825136</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.104463471362178</v>
+        <v>0.1049812824209432</v>
       </c>
       <c r="C23">
-        <v>7589.155639129856</v>
+        <v>7445.348918141129</v>
       </c>
       <c r="D23">
-        <v>8548.745123932753</v>
+        <v>8499.32837841083</v>
       </c>
       <c r="E23">
-        <v>117.8919381224357</v>
+        <v>212.2819135892405</v>
       </c>
       <c r="F23">
-        <v>1982.189484802897</v>
+        <v>2076.579460269701</v>
       </c>
       <c r="G23">
         <v>1022.6</v>
@@ -3179,45 +3179,45 @@
         <v>803.5</v>
       </c>
       <c r="M23">
-        <v>119.2903552522452</v>
+        <v>128.5010334419535</v>
       </c>
       <c r="N23">
-        <v>684.2096447477547</v>
+        <v>674.9989665580465</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>684.2096447477547</v>
+        <v>674.9989665580465</v>
       </c>
       <c r="Q23">
-        <v>711.6096447477547</v>
+        <v>702.3989665580465</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1162347330735557</v>
+        <v>0.1171377424719346</v>
       </c>
       <c r="T23">
-        <v>1.290036871898721</v>
+        <v>1.306575806153833</v>
       </c>
       <c r="U23">
-        <v>0.06018110587651872</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="V23">
         <v>0</v>
       </c>
       <c r="W23">
-        <v>0.06018110587651872</v>
+        <v>0.06188110587651872</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.735666083825136</v>
+        <v>6.252868000185829</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1049812824209432</v>
+        <v>0.1051420934797083</v>
       </c>
       <c r="C24">
-        <v>7445.348918141129</v>
+        <v>7335.728167151305</v>
       </c>
       <c r="D24">
-        <v>8499.32837841083</v>
+        <v>8484.09760288781</v>
       </c>
       <c r="E24">
-        <v>212.2819135892405</v>
+        <v>306.6718890560451</v>
       </c>
       <c r="F24">
-        <v>2076.579460269701</v>
+        <v>2170.969435736506</v>
       </c>
       <c r="G24">
         <v>1022.6</v>
@@ -3261,28 +3261,28 @@
         <v>803.5</v>
       </c>
       <c r="M24">
-        <v>128.5010334419535</v>
+        <v>134.3419895074968</v>
       </c>
       <c r="N24">
-        <v>674.9989665580465</v>
+        <v>669.1580104925032</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>674.9989665580465</v>
+        <v>669.1580104925032</v>
       </c>
       <c r="Q24">
-        <v>702.3989665580465</v>
+        <v>696.5580104925032</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1171377424719346</v>
+        <v>0.1180642066598818</v>
       </c>
       <c r="T24">
-        <v>1.306575806153833</v>
+        <v>1.32354432311687</v>
       </c>
       <c r="U24">
         <v>0.06188110587651872</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.252868000185829</v>
+        <v>5.981004174090793</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1051420934797083</v>
+        <v>0.1053029045384735</v>
       </c>
       <c r="C25">
-        <v>7335.728167151305</v>
+        <v>7226.161905541098</v>
       </c>
       <c r="D25">
-        <v>8484.09760288781</v>
+        <v>8468.921316744409</v>
       </c>
       <c r="E25">
-        <v>306.6718890560451</v>
+        <v>401.0618645228496</v>
       </c>
       <c r="F25">
-        <v>2170.969435736506</v>
+        <v>2265.359411203311</v>
       </c>
       <c r="G25">
         <v>1022.6</v>
@@ -3343,28 +3343,28 @@
         <v>803.5</v>
       </c>
       <c r="M25">
-        <v>134.3419895074968</v>
+        <v>140.1829455730402</v>
       </c>
       <c r="N25">
-        <v>669.1580104925032</v>
+        <v>663.3170544269599</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>669.1580104925032</v>
+        <v>663.3170544269599</v>
       </c>
       <c r="Q25">
-        <v>696.5580104925032</v>
+        <v>690.7170544269599</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1180642066598818</v>
+        <v>0.119015051484354</v>
       </c>
       <c r="T25">
-        <v>1.32354432311687</v>
+        <v>1.340959379999986</v>
       </c>
       <c r="U25">
         <v>0.06188110587651872</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.981004174090793</v>
+        <v>5.73179566683701</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1053029045384735</v>
+        <v>0.1056637155972387</v>
       </c>
       <c r="C26">
-        <v>7226.1619055411</v>
+        <v>7097.917748231956</v>
       </c>
       <c r="D26">
-        <v>8468.92131674441</v>
+        <v>8435.06713490207</v>
       </c>
       <c r="E26">
-        <v>401.0618645228496</v>
+        <v>495.4518399896542</v>
       </c>
       <c r="F26">
-        <v>2265.359411203311</v>
+        <v>2359.749386670115</v>
       </c>
       <c r="G26">
         <v>1022.6</v>
@@ -3425,45 +3425,45 @@
         <v>803.5</v>
       </c>
       <c r="M26">
-        <v>140.1829455730402</v>
+        <v>147.9117011479196</v>
       </c>
       <c r="N26">
-        <v>663.3170544269599</v>
+        <v>655.5882988520804</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>663.3170544269599</v>
+        <v>655.5882988520804</v>
       </c>
       <c r="Q26">
-        <v>690.7170544269599</v>
+        <v>682.9882988520803</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.119015051484354</v>
+        <v>0.119991252170812</v>
       </c>
       <c r="T26">
-        <v>1.340959379999986</v>
+        <v>1.358838838399986</v>
       </c>
       <c r="U26">
-        <v>0.06188110587651872</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.06188110587651872</v>
+        <v>0.06268110587651873</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>5.73179566683701</v>
+        <v>5.432295036593872</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1056637155972387</v>
+        <v>0.1058325266560039</v>
       </c>
       <c r="C27">
-        <v>7097.917748231956</v>
+        <v>6987.781334650405</v>
       </c>
       <c r="D27">
-        <v>8435.06713490207</v>
+        <v>8419.320696787325</v>
       </c>
       <c r="E27">
-        <v>495.4518399896542</v>
+        <v>589.8418154564588</v>
       </c>
       <c r="F27">
-        <v>2359.749386670115</v>
+        <v>2454.13936213692</v>
       </c>
       <c r="G27">
         <v>1022.6</v>
@@ -3507,28 +3507,28 @@
         <v>803.5</v>
       </c>
       <c r="M27">
-        <v>147.9117011479196</v>
+        <v>153.8281691938364</v>
       </c>
       <c r="N27">
-        <v>655.5882988520804</v>
+        <v>649.6718308061636</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>655.5882988520804</v>
+        <v>649.6718308061636</v>
       </c>
       <c r="Q27">
-        <v>682.9882988520803</v>
+        <v>677.0718308061636</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.119991252170812</v>
+        <v>0.1209938366596068</v>
       </c>
       <c r="T27">
-        <v>1.358838838399986</v>
+        <v>1.377201525405391</v>
       </c>
       <c r="U27">
         <v>0.06268110587651873</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.432295036593872</v>
+        <v>5.223360612109492</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1058325266560039</v>
+        <v>0.1060013377147691</v>
       </c>
       <c r="C28">
-        <v>6987.781334650405</v>
+        <v>6877.703601883701</v>
       </c>
       <c r="D28">
-        <v>8419.320696787325</v>
+        <v>8403.632939487425</v>
       </c>
       <c r="E28">
-        <v>589.8418154564588</v>
+        <v>684.2317909232638</v>
       </c>
       <c r="F28">
-        <v>2454.13936213692</v>
+        <v>2548.529337603725</v>
       </c>
       <c r="G28">
         <v>1022.6</v>
@@ -3589,28 +3589,28 @@
         <v>803.5</v>
       </c>
       <c r="M28">
-        <v>153.8281691938364</v>
+        <v>159.7446372397532</v>
       </c>
       <c r="N28">
-        <v>649.6718308061636</v>
+        <v>643.7553627602467</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>649.6718308061636</v>
+        <v>643.7553627602467</v>
       </c>
       <c r="Q28">
-        <v>677.0718308061636</v>
+        <v>671.1553627602467</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1209938366596068</v>
+        <v>0.1220238892165877</v>
       </c>
       <c r="T28">
-        <v>1.377201525405391</v>
+        <v>1.396067299726013</v>
       </c>
       <c r="U28">
         <v>0.06268110587651873</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.223360612109492</v>
+        <v>5.029902811660993</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1060013377147691</v>
+        <v>0.1061701487735343</v>
       </c>
       <c r="C29">
-        <v>6877.703601883701</v>
+        <v>6767.684222521253</v>
       </c>
       <c r="D29">
-        <v>8403.632939487425</v>
+        <v>8388.003535591783</v>
       </c>
       <c r="E29">
-        <v>684.2317909232638</v>
+        <v>778.6217663900684</v>
       </c>
       <c r="F29">
-        <v>2548.529337603725</v>
+        <v>2642.919313070529</v>
       </c>
       <c r="G29">
         <v>1022.6</v>
@@ -3671,28 +3671,28 @@
         <v>803.5</v>
       </c>
       <c r="M29">
-        <v>159.7446372397532</v>
+        <v>165.66110528567</v>
       </c>
       <c r="N29">
-        <v>643.7553627602467</v>
+        <v>637.83889471433</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>643.7553627602467</v>
+        <v>637.83889471433</v>
       </c>
       <c r="Q29">
-        <v>671.1553627602467</v>
+        <v>665.2388947143299</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1220238892165877</v>
+        <v>0.1230825543445959</v>
       </c>
       <c r="T29">
-        <v>1.396067299726013</v>
+        <v>1.415457123333319</v>
       </c>
       <c r="U29">
         <v>0.06268110587651873</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.029902811660993</v>
+        <v>4.850263425530242</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1061701487735343</v>
+        <v>0.1063389598322994</v>
       </c>
       <c r="C30">
-        <v>6767.684222521253</v>
+        <v>6657.722871583665</v>
       </c>
       <c r="D30">
-        <v>8388.003535591783</v>
+        <v>8372.432160120998</v>
       </c>
       <c r="E30">
-        <v>778.6217663900684</v>
+        <v>873.011741856873</v>
       </c>
       <c r="F30">
-        <v>2642.919313070529</v>
+        <v>2737.309288537334</v>
       </c>
       <c r="G30">
         <v>1022.6</v>
@@ -3753,28 +3753,28 @@
         <v>803.5</v>
       </c>
       <c r="M30">
-        <v>165.66110528567</v>
+        <v>171.5775733315868</v>
       </c>
       <c r="N30">
-        <v>637.83889471433</v>
+        <v>631.9224266684132</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>637.83889471433</v>
+        <v>631.9224266684132</v>
       </c>
       <c r="Q30">
-        <v>665.2388947143299</v>
+        <v>659.3224266684132</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1230825543445959</v>
+        <v>0.1241710410255057</v>
       </c>
       <c r="T30">
-        <v>1.415457123333319</v>
+        <v>1.435393139154915</v>
       </c>
       <c r="U30">
         <v>0.06268110587651873</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.850263425530242</v>
+        <v>4.683012962580924</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1063389598322994</v>
+        <v>0.1065077708910646</v>
       </c>
       <c r="C31">
-        <v>6657.722871583665</v>
+        <v>6547.819226500217</v>
       </c>
       <c r="D31">
-        <v>8372.432160120998</v>
+        <v>8356.918490504355</v>
       </c>
       <c r="E31">
-        <v>873.0117418568725</v>
+        <v>967.4017173236771</v>
       </c>
       <c r="F31">
-        <v>2737.309288537333</v>
+        <v>2831.699264004138</v>
       </c>
       <c r="G31">
         <v>1022.6</v>
@@ -3835,28 +3835,28 @@
         <v>803.5</v>
       </c>
       <c r="M31">
-        <v>171.5775733315868</v>
+        <v>177.4940413775035</v>
       </c>
       <c r="N31">
-        <v>631.9224266684132</v>
+        <v>626.0059586224965</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>631.9224266684132</v>
+        <v>626.0059586224965</v>
       </c>
       <c r="Q31">
-        <v>659.3224266684132</v>
+        <v>653.4059586224964</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1241710410255057</v>
+        <v>0.12529062732587</v>
       </c>
       <c r="T31">
-        <v>1.435393139154915</v>
+        <v>1.455898755428557</v>
       </c>
       <c r="U31">
         <v>0.06268110587651873</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.683012962580925</v>
+        <v>4.526912530494894</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1065077708910646</v>
+        <v>0.1066765819498298</v>
       </c>
       <c r="C32">
-        <v>6547.819226500217</v>
+        <v>6437.972967086602</v>
       </c>
       <c r="D32">
-        <v>8356.918490504355</v>
+        <v>8341.462206557544</v>
       </c>
       <c r="E32">
-        <v>967.4017173236771</v>
+        <v>1061.791692790482</v>
       </c>
       <c r="F32">
-        <v>2831.699264004138</v>
+        <v>2926.089239470943</v>
       </c>
       <c r="G32">
         <v>1022.6</v>
@@ -3917,28 +3917,28 @@
         <v>803.5</v>
       </c>
       <c r="M32">
-        <v>177.4940413775035</v>
+        <v>183.4105094234203</v>
       </c>
       <c r="N32">
-        <v>626.0059586224965</v>
+        <v>620.0894905765797</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>626.0059586224965</v>
+        <v>620.0894905765797</v>
       </c>
       <c r="Q32">
-        <v>653.4059586224964</v>
+        <v>647.4894905765797</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.12529062732587</v>
+        <v>0.1264426654030566</v>
       </c>
       <c r="T32">
-        <v>1.455898755428557</v>
+        <v>1.476998737391289</v>
       </c>
       <c r="U32">
         <v>0.06268110587651873</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.526912530494894</v>
+        <v>4.380883094027316</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1066765819498298</v>
+        <v>0.107165393008595</v>
       </c>
       <c r="C33">
-        <v>6437.972967086602</v>
+        <v>6299.148360031922</v>
       </c>
       <c r="D33">
-        <v>8341.462206557544</v>
+        <v>8297.02757496967</v>
       </c>
       <c r="E33">
-        <v>1061.791692790482</v>
+        <v>1156.181668257287</v>
       </c>
       <c r="F33">
-        <v>2926.089239470943</v>
+        <v>3020.479214937748</v>
       </c>
       <c r="G33">
         <v>1022.6</v>
@@ -3999,45 +3999,45 @@
         <v>803.5</v>
       </c>
       <c r="M33">
-        <v>183.4105094234203</v>
+        <v>192.3474566842749</v>
       </c>
       <c r="N33">
-        <v>620.0894905765797</v>
+        <v>611.1525433157251</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>620.0894905765797</v>
+        <v>611.1525433157251</v>
       </c>
       <c r="Q33">
-        <v>647.4894905765797</v>
+        <v>638.5525433157251</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1264426654030566</v>
+        <v>0.1276285869531015</v>
       </c>
       <c r="T33">
-        <v>1.476998737391289</v>
+        <v>1.498719307058808</v>
       </c>
       <c r="U33">
-        <v>0.06268110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="V33">
         <v>0</v>
       </c>
       <c r="W33">
-        <v>0.06268110587651873</v>
+        <v>0.06368110587651873</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.380883094027316</v>
+        <v>4.177336232310521</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.107165393008595</v>
+        <v>0.1073442040673602</v>
       </c>
       <c r="C34">
-        <v>6299.148360031922</v>
+        <v>6188.621866801333</v>
       </c>
       <c r="D34">
-        <v>8297.02757496967</v>
+        <v>8280.891057205885</v>
       </c>
       <c r="E34">
-        <v>1156.181668257287</v>
+        <v>1250.571643724091</v>
       </c>
       <c r="F34">
-        <v>3020.479214937748</v>
+        <v>3114.869190404552</v>
       </c>
       <c r="G34">
         <v>1022.6</v>
@@ -4081,28 +4081,28 @@
         <v>803.5</v>
       </c>
       <c r="M34">
-        <v>192.3474566842749</v>
+        <v>198.3583147056585</v>
       </c>
       <c r="N34">
-        <v>611.1525433157251</v>
+        <v>605.1416852943415</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>611.1525433157251</v>
+        <v>605.1416852943415</v>
       </c>
       <c r="Q34">
-        <v>638.5525433157251</v>
+        <v>632.5416852943415</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1276285869531015</v>
+        <v>0.1288499091464314</v>
       </c>
       <c r="T34">
-        <v>1.498719307058808</v>
+        <v>1.521088251940283</v>
       </c>
       <c r="U34">
         <v>0.06368110587651873</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.177336232310521</v>
+        <v>4.05075028587687</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1073442040673602</v>
+        <v>0.1075230151261254</v>
       </c>
       <c r="C35">
-        <v>6188.621866801333</v>
+        <v>6078.158018119229</v>
       </c>
       <c r="D35">
-        <v>8280.891057205885</v>
+        <v>8264.817183990586</v>
       </c>
       <c r="E35">
-        <v>1250.571643724091</v>
+        <v>1344.961619190896</v>
       </c>
       <c r="F35">
-        <v>3114.869190404552</v>
+        <v>3209.259165871357</v>
       </c>
       <c r="G35">
         <v>1022.6</v>
@@ -4163,28 +4163,28 @@
         <v>803.5</v>
       </c>
       <c r="M35">
-        <v>198.3583147056585</v>
+        <v>204.3691727270421</v>
       </c>
       <c r="N35">
-        <v>605.1416852943415</v>
+        <v>599.130827272958</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>605.1416852943415</v>
+        <v>599.130827272958</v>
       </c>
       <c r="Q35">
-        <v>632.5416852943415</v>
+        <v>626.5308272729579</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1288499091464314</v>
+        <v>0.1301082411031955</v>
       </c>
       <c r="T35">
-        <v>1.521088251940283</v>
+        <v>1.544135043636348</v>
       </c>
       <c r="U35">
         <v>0.06368110587651873</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.05075028587687</v>
+        <v>3.931610571586373</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1075230151261254</v>
+        <v>0.1077018261848906</v>
       </c>
       <c r="C36">
-        <v>6078.158018119229</v>
+        <v>5967.756449898066</v>
       </c>
       <c r="D36">
-        <v>8264.817183990586</v>
+        <v>8248.805591236227</v>
       </c>
       <c r="E36">
-        <v>1344.961619190896</v>
+        <v>1439.3515946577</v>
       </c>
       <c r="F36">
-        <v>3209.259165871357</v>
+        <v>3303.649141338161</v>
       </c>
       <c r="G36">
         <v>1022.6</v>
@@ -4245,28 +4245,28 @@
         <v>803.5</v>
       </c>
       <c r="M36">
-        <v>204.3691727270421</v>
+        <v>210.3800307484257</v>
       </c>
       <c r="N36">
-        <v>599.130827272958</v>
+        <v>593.1199692515743</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>599.130827272958</v>
+        <v>593.1199692515743</v>
       </c>
       <c r="Q36">
-        <v>626.5308272729579</v>
+        <v>620.5199692515743</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1301082411031955</v>
+        <v>0.1314052909663216</v>
       </c>
       <c r="T36">
-        <v>1.544135043636348</v>
+        <v>1.567890967384599</v>
       </c>
       <c r="U36">
         <v>0.06368110587651873</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.931610571586373</v>
+        <v>3.819278840969619</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1077018261848906</v>
+        <v>0.1078806372436557</v>
       </c>
       <c r="C37">
-        <v>5967.756449898066</v>
+        <v>5857.416800866262</v>
       </c>
       <c r="D37">
-        <v>8248.805591236227</v>
+        <v>8232.855917671228</v>
       </c>
       <c r="E37">
-        <v>1439.3515946577</v>
+        <v>1533.741570124505</v>
       </c>
       <c r="F37">
-        <v>3303.649141338161</v>
+        <v>3398.039116804966</v>
       </c>
       <c r="G37">
         <v>1022.6</v>
@@ -4327,28 +4327,28 @@
         <v>803.5</v>
       </c>
       <c r="M37">
-        <v>210.3800307484257</v>
+        <v>216.3908887698093</v>
       </c>
       <c r="N37">
-        <v>593.1199692515743</v>
+        <v>587.1091112301907</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>593.1199692515743</v>
+        <v>587.1091112301907</v>
       </c>
       <c r="Q37">
-        <v>620.5199692515743</v>
+        <v>614.5091112301907</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1314052909663216</v>
+        <v>0.1327428736376703</v>
       </c>
       <c r="T37">
-        <v>1.567890967384599</v>
+        <v>1.592389263749984</v>
       </c>
       <c r="U37">
         <v>0.06368110587651873</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.819278840969619</v>
+        <v>3.713187762053796</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1078806372436558</v>
+        <v>0.108059448302421</v>
       </c>
       <c r="C38">
-        <v>5857.416800866262</v>
+        <v>5747.138712541015</v>
       </c>
       <c r="D38">
-        <v>8232.855917671228</v>
+        <v>8216.967804812784</v>
       </c>
       <c r="E38">
-        <v>1533.741570124505</v>
+        <v>1628.13154559131</v>
       </c>
       <c r="F38">
-        <v>3398.039116804966</v>
+        <v>3492.429092271771</v>
       </c>
       <c r="G38">
         <v>1022.6</v>
@@ -4409,28 +4409,28 @@
         <v>803.5</v>
       </c>
       <c r="M38">
-        <v>216.3908887698092</v>
+        <v>222.4017467911928</v>
       </c>
       <c r="N38">
-        <v>587.1091112301908</v>
+        <v>581.0982532088071</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>587.1091112301908</v>
+        <v>581.0982532088071</v>
       </c>
       <c r="Q38">
-        <v>614.5091112301908</v>
+        <v>608.4982532088071</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1327428736376703</v>
+        <v>0.1341229192509667</v>
       </c>
       <c r="T38">
-        <v>1.592389263749984</v>
+        <v>1.617665283809507</v>
       </c>
       <c r="U38">
         <v>0.06368110587651873</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.713187762053797</v>
+        <v>3.612831336052342</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.108059448302421</v>
+        <v>0.1082382593611862</v>
       </c>
       <c r="C39">
-        <v>5747.138712541015</v>
+        <v>5636.92182920147</v>
       </c>
       <c r="D39">
-        <v>8216.967804812784</v>
+        <v>8201.140896940045</v>
       </c>
       <c r="E39">
-        <v>1628.13154559131</v>
+        <v>1722.521521058114</v>
       </c>
       <c r="F39">
-        <v>3492.429092271771</v>
+        <v>3586.819067738575</v>
       </c>
       <c r="G39">
         <v>1022.6</v>
@@ -4491,28 +4491,28 @@
         <v>803.5</v>
       </c>
       <c r="M39">
-        <v>222.4017467911928</v>
+        <v>228.4126048125764</v>
       </c>
       <c r="N39">
-        <v>581.0982532088071</v>
+        <v>575.0873951874236</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>581.0982532088071</v>
+        <v>575.0873951874236</v>
       </c>
       <c r="Q39">
-        <v>608.4982532088071</v>
+        <v>602.4873951874235</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1341229192509667</v>
+        <v>0.135547482464692</v>
       </c>
       <c r="T39">
-        <v>1.617665283809507</v>
+        <v>1.643756659354822</v>
       </c>
       <c r="U39">
         <v>0.06368110587651873</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.612831336052342</v>
+        <v>3.51775682720886</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1082382593611862</v>
+        <v>0.1084170704199513</v>
       </c>
       <c r="C40">
-        <v>5636.92182920147</v>
+        <v>5526.765797862139</v>
       </c>
       <c r="D40">
-        <v>8201.140896940045</v>
+        <v>8185.374841067518</v>
       </c>
       <c r="E40">
-        <v>1722.521521058114</v>
+        <v>1816.911496524919</v>
       </c>
       <c r="F40">
-        <v>3586.819067738575</v>
+        <v>3681.20904320538</v>
       </c>
       <c r="G40">
         <v>1022.6</v>
@@ -4573,28 +4573,28 @@
         <v>803.5</v>
       </c>
       <c r="M40">
-        <v>228.4126048125764</v>
+        <v>234.42346283396</v>
       </c>
       <c r="N40">
-        <v>575.0873951874236</v>
+        <v>569.07653716604</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>575.0873951874236</v>
+        <v>569.07653716604</v>
       </c>
       <c r="Q40">
-        <v>602.4873951874235</v>
+        <v>596.47653716604</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.135547482464692</v>
+        <v>0.1370187526690312</v>
       </c>
       <c r="T40">
-        <v>1.643756659354822</v>
+        <v>1.670703489836048</v>
       </c>
       <c r="U40">
         <v>0.06368110587651873</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.51775682720886</v>
+        <v>3.427557934203505</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1084170704199513</v>
+        <v>0.1085958814787165</v>
       </c>
       <c r="C41">
-        <v>5526.765797862139</v>
+        <v>5416.670268246678</v>
       </c>
       <c r="D41">
-        <v>8185.374841067518</v>
+        <v>8169.669286918863</v>
       </c>
       <c r="E41">
-        <v>1816.911496524919</v>
+        <v>1911.301471991724</v>
       </c>
       <c r="F41">
-        <v>3681.20904320538</v>
+        <v>3775.599018672185</v>
       </c>
       <c r="G41">
         <v>1022.6</v>
@@ -4655,28 +4655,28 @@
         <v>803.5</v>
       </c>
       <c r="M41">
-        <v>234.42346283396</v>
+        <v>240.4343208553436</v>
       </c>
       <c r="N41">
-        <v>569.07653716604</v>
+        <v>563.0656791446563</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>569.07653716604</v>
+        <v>563.0656791446563</v>
       </c>
       <c r="Q41">
-        <v>596.47653716604</v>
+        <v>590.4656791446563</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1370187526690312</v>
+        <v>0.1385390652135151</v>
       </c>
       <c r="T41">
-        <v>1.670703489836048</v>
+        <v>1.698548547999983</v>
       </c>
       <c r="U41">
         <v>0.06368110587651873</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.427557934203505</v>
+        <v>3.341868985848417</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1085958814787165</v>
+        <v>0.1087746925374817</v>
       </c>
       <c r="C42">
-        <v>5416.670268246678</v>
+        <v>5306.63489276195</v>
       </c>
       <c r="D42">
-        <v>8169.669286918863</v>
+        <v>8154.023886900939</v>
       </c>
       <c r="E42">
-        <v>1911.301471991724</v>
+        <v>2005.691447458528</v>
       </c>
       <c r="F42">
-        <v>3775.599018672185</v>
+        <v>3869.988994138989</v>
       </c>
       <c r="G42">
         <v>1022.6</v>
@@ -4737,28 +4737,28 @@
         <v>803.5</v>
       </c>
       <c r="M42">
-        <v>240.4343208553436</v>
+        <v>246.4451788767272</v>
       </c>
       <c r="N42">
-        <v>563.0656791446563</v>
+        <v>557.0548211232727</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>563.0656791446563</v>
+        <v>557.0548211232727</v>
       </c>
       <c r="Q42">
-        <v>590.4656791446563</v>
+        <v>584.4548211232727</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1385390652135151</v>
+        <v>0.140110913776456</v>
       </c>
       <c r="T42">
-        <v>1.698548547999983</v>
+        <v>1.72733750644066</v>
       </c>
       <c r="U42">
         <v>0.06368110587651873</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.341868985848417</v>
+        <v>3.260359986193577</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1087746925374817</v>
+        <v>0.1089535035962469</v>
       </c>
       <c r="C43">
-        <v>5306.63489276195</v>
+        <v>5196.659326472369</v>
       </c>
       <c r="D43">
-        <v>8154.023886900939</v>
+        <v>8138.438296078162</v>
       </c>
       <c r="E43">
-        <v>2005.691447458528</v>
+        <v>2100.081422925333</v>
       </c>
       <c r="F43">
-        <v>3869.988994138989</v>
+        <v>3964.378969605794</v>
       </c>
       <c r="G43">
         <v>1022.6</v>
@@ -4819,28 +4819,28 @@
         <v>803.5</v>
       </c>
       <c r="M43">
-        <v>246.4451788767272</v>
+        <v>252.4560368981108</v>
       </c>
       <c r="N43">
-        <v>557.0548211232727</v>
+        <v>551.0439631018892</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>557.0548211232727</v>
+        <v>551.0439631018892</v>
       </c>
       <c r="Q43">
-        <v>584.4548211232727</v>
+        <v>578.4439631018892</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.140110913776456</v>
+        <v>0.1417369640139811</v>
       </c>
       <c r="T43">
-        <v>1.72733750644066</v>
+        <v>1.757119187586189</v>
       </c>
       <c r="U43">
         <v>0.06368110587651873</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.260359986193577</v>
+        <v>3.182732367474682</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1089535035962469</v>
+        <v>0.1091323146550121</v>
       </c>
       <c r="C44">
-        <v>5196.659326472369</v>
+        <v>5086.743227074558</v>
       </c>
       <c r="D44">
-        <v>8138.438296078163</v>
+        <v>8122.912172147155</v>
       </c>
       <c r="E44">
-        <v>2100.081422925332</v>
+        <v>2194.471398392137</v>
       </c>
       <c r="F44">
-        <v>3964.378969605793</v>
+        <v>4058.768945072598</v>
       </c>
       <c r="G44">
         <v>1022.6</v>
@@ -4901,28 +4901,28 @@
         <v>803.5</v>
       </c>
       <c r="M44">
-        <v>252.4560368981108</v>
+        <v>258.4668949194943</v>
       </c>
       <c r="N44">
-        <v>551.0439631018892</v>
+        <v>545.0331050805057</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>551.0439631018892</v>
+        <v>545.0331050805057</v>
       </c>
       <c r="Q44">
-        <v>578.4439631018892</v>
+        <v>572.4331050805057</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1417369640139811</v>
+        <v>0.1434200686458053</v>
       </c>
       <c r="T44">
-        <v>1.757119187586189</v>
+        <v>1.787945839999981</v>
       </c>
       <c r="U44">
         <v>0.06368110587651873</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.182732367474683</v>
+        <v>3.108715335672946</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1091323146550121</v>
+        <v>0.1093111257137773</v>
       </c>
       <c r="C45">
-        <v>5086.743227074558</v>
+        <v>4976.886254872275</v>
       </c>
       <c r="D45">
-        <v>8122.912172147155</v>
+        <v>8107.445175411678</v>
       </c>
       <c r="E45">
-        <v>2194.471398392137</v>
+        <v>2288.861373858942</v>
       </c>
       <c r="F45">
-        <v>4058.768945072598</v>
+        <v>4153.158920539403</v>
       </c>
       <c r="G45">
         <v>1022.6</v>
@@ -4983,28 +4983,28 @@
         <v>803.5</v>
       </c>
       <c r="M45">
-        <v>258.4668949194943</v>
+        <v>264.477752940878</v>
       </c>
       <c r="N45">
-        <v>545.0331050805057</v>
+        <v>539.022247059122</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>545.0331050805057</v>
+        <v>539.022247059122</v>
       </c>
       <c r="Q45">
-        <v>572.4331050805057</v>
+        <v>566.422247059122</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1434200686458053</v>
+        <v>0.1451632841573375</v>
       </c>
       <c r="T45">
-        <v>1.787945839999981</v>
+        <v>1.819873444285695</v>
       </c>
       <c r="U45">
         <v>0.06368110587651873</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.108715335672946</v>
+        <v>3.038062714407652</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1093111257137773</v>
+        <v>0.1106149367725425</v>
       </c>
       <c r="C46">
-        <v>4976.886254872275</v>
+        <v>4771.473965612763</v>
       </c>
       <c r="D46">
-        <v>8107.445175411678</v>
+        <v>7996.42286161897</v>
       </c>
       <c r="E46">
-        <v>2288.861373858942</v>
+        <v>2383.251349325747</v>
       </c>
       <c r="F46">
-        <v>4153.158920539403</v>
+        <v>4247.548896006208</v>
       </c>
       <c r="G46">
         <v>1022.6</v>
@@ -5065,45 +5065,45 @@
         <v>803.5</v>
       </c>
       <c r="M46">
-        <v>264.477752940878</v>
+        <v>281.107483202277</v>
       </c>
       <c r="N46">
-        <v>539.022247059122</v>
+        <v>522.3925167977229</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>539.022247059122</v>
+        <v>522.3925167977229</v>
       </c>
       <c r="Q46">
-        <v>566.422247059122</v>
+        <v>549.7925167977229</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1451632841573375</v>
+        <v>0.1469698893238346</v>
       </c>
       <c r="T46">
-        <v>1.819873444285695</v>
+        <v>1.852962052363617</v>
       </c>
       <c r="U46">
-        <v>0.06368110587651873</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="V46">
         <v>0</v>
       </c>
       <c r="W46">
-        <v>0.06368110587651873</v>
+        <v>0.06618110587651872</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.038062714407652</v>
+        <v>2.858337283827567</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1106149367725425</v>
+        <v>0.1108187478313077</v>
       </c>
       <c r="C47">
-        <v>4771.473965612763</v>
+        <v>4660.00326024879</v>
       </c>
       <c r="D47">
-        <v>7996.42286161897</v>
+        <v>7979.342131721803</v>
       </c>
       <c r="E47">
-        <v>2383.251349325747</v>
+        <v>2477.641324792551</v>
       </c>
       <c r="F47">
-        <v>4247.548896006208</v>
+        <v>4341.938871473012</v>
       </c>
       <c r="G47">
         <v>1022.6</v>
@@ -5147,28 +5147,28 @@
         <v>803.5</v>
       </c>
       <c r="M47">
-        <v>281.107483202277</v>
+        <v>287.3543161623276</v>
       </c>
       <c r="N47">
-        <v>522.3925167977229</v>
+        <v>516.1456838376723</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>522.3925167977229</v>
+        <v>516.1456838376723</v>
       </c>
       <c r="Q47">
-        <v>549.7925167977229</v>
+        <v>543.5456838376723</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1469698893238346</v>
+        <v>0.1488434057927945</v>
       </c>
       <c r="T47">
-        <v>1.852962052363617</v>
+        <v>1.887276164444425</v>
       </c>
       <c r="U47">
         <v>0.06618110587651872</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.858337283827567</v>
+        <v>2.796199516787837</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1108187478313077</v>
+        <v>0.1110225588900728</v>
       </c>
       <c r="C48">
-        <v>4660.00326024879</v>
+        <v>4548.6053698104</v>
       </c>
       <c r="D48">
-        <v>7979.342131721803</v>
+        <v>7962.334216750217</v>
       </c>
       <c r="E48">
-        <v>2477.641324792551</v>
+        <v>2572.031300259356</v>
       </c>
       <c r="F48">
-        <v>4341.938871473012</v>
+        <v>4436.328846939817</v>
       </c>
       <c r="G48">
         <v>1022.6</v>
@@ -5229,28 +5229,28 @@
         <v>803.5</v>
       </c>
       <c r="M48">
-        <v>287.3543161623276</v>
+        <v>293.6011491223782</v>
       </c>
       <c r="N48">
-        <v>516.1456838376723</v>
+        <v>509.8988508776218</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>516.1456838376723</v>
+        <v>509.8988508776218</v>
       </c>
       <c r="Q48">
-        <v>543.5456838376723</v>
+        <v>537.2988508776218</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1488434057927945</v>
+        <v>0.1507876209964321</v>
       </c>
       <c r="T48">
-        <v>1.887276164444425</v>
+        <v>1.922885148679226</v>
       </c>
       <c r="U48">
         <v>0.06618110587651872</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.796199516787837</v>
+        <v>2.736705910047671</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1110225588900728</v>
+        <v>0.111226369948838</v>
       </c>
       <c r="C49">
-        <v>4548.6053698104</v>
+        <v>4437.279829674329</v>
       </c>
       <c r="D49">
-        <v>7962.334216750217</v>
+        <v>7945.398652080951</v>
       </c>
       <c r="E49">
-        <v>2572.031300259356</v>
+        <v>2666.42127572616</v>
       </c>
       <c r="F49">
-        <v>4436.328846939817</v>
+        <v>4530.718822406621</v>
       </c>
       <c r="G49">
         <v>1022.6</v>
@@ -5311,28 +5311,28 @@
         <v>803.5</v>
       </c>
       <c r="M49">
-        <v>293.6011491223782</v>
+        <v>299.8479820824288</v>
       </c>
       <c r="N49">
-        <v>509.8988508776218</v>
+        <v>503.6520179175712</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>509.8988508776218</v>
+        <v>503.6520179175712</v>
       </c>
       <c r="Q49">
-        <v>537.2988508776218</v>
+        <v>531.0520179175712</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1507876209964321</v>
+        <v>0.152806613707902</v>
       </c>
       <c r="T49">
-        <v>1.922885148679226</v>
+        <v>1.959863709230749</v>
       </c>
       <c r="U49">
         <v>0.06618110587651872</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.736705910047671</v>
+        <v>2.679691203588344</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.111226369948838</v>
+        <v>0.1114301810076032</v>
       </c>
       <c r="C50">
-        <v>4437.279829674331</v>
+        <v>4326.026179161879</v>
       </c>
       <c r="D50">
-        <v>7945.398652080952</v>
+        <v>7928.534977035304</v>
       </c>
       <c r="E50">
-        <v>2666.42127572616</v>
+        <v>2760.811251192965</v>
       </c>
       <c r="F50">
-        <v>4530.718822406621</v>
+        <v>4625.108797873426</v>
       </c>
       <c r="G50">
         <v>1022.6</v>
@@ -5393,28 +5393,28 @@
         <v>803.5</v>
       </c>
       <c r="M50">
-        <v>299.8479820824288</v>
+        <v>306.0948150424794</v>
       </c>
       <c r="N50">
-        <v>503.6520179175712</v>
+        <v>497.4051849575206</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>503.6520179175712</v>
+        <v>497.4051849575206</v>
       </c>
       <c r="Q50">
-        <v>531.0520179175712</v>
+        <v>524.8051849575206</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.152806613707902</v>
+        <v>0.1549047826041353</v>
       </c>
       <c r="T50">
-        <v>1.959863709230749</v>
+        <v>1.998292409411744</v>
       </c>
       <c r="U50">
         <v>0.06618110587651872</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.679691203588344</v>
+        <v>2.625003628004909</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1114301810076032</v>
+        <v>0.1116339920663684</v>
       </c>
       <c r="C51">
-        <v>4326.026179161879</v>
+        <v>4214.843961497119</v>
       </c>
       <c r="D51">
-        <v>7928.534977035304</v>
+        <v>7911.742734837349</v>
       </c>
       <c r="E51">
-        <v>2760.811251192965</v>
+        <v>2855.201226659769</v>
       </c>
       <c r="F51">
-        <v>4625.108797873426</v>
+        <v>4719.49877334023</v>
       </c>
       <c r="G51">
         <v>1022.6</v>
@@ -5475,28 +5475,28 @@
         <v>803.5</v>
       </c>
       <c r="M51">
-        <v>306.0948150424794</v>
+        <v>312.34164800253</v>
       </c>
       <c r="N51">
-        <v>497.4051849575206</v>
+        <v>491.15835199747</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>497.4051849575206</v>
+        <v>491.15835199747</v>
       </c>
       <c r="Q51">
-        <v>524.8051849575206</v>
+        <v>518.55835199747</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1549047826041353</v>
+        <v>0.1570868782562181</v>
       </c>
       <c r="T51">
-        <v>1.998292409411744</v>
+        <v>2.038258257599979</v>
       </c>
       <c r="U51">
         <v>0.06618110587651872</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.625003628004909</v>
+        <v>2.572503555444811</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1116339920663684</v>
+        <v>0.1118378031251336</v>
       </c>
       <c r="C52">
-        <v>4214.843961497119</v>
+        <v>4103.732723765658</v>
       </c>
       <c r="D52">
-        <v>7911.742734837349</v>
+        <v>7895.021472572694</v>
       </c>
       <c r="E52">
-        <v>2855.201226659769</v>
+        <v>2949.591202126574</v>
       </c>
       <c r="F52">
-        <v>4719.49877334023</v>
+        <v>4813.888748807035</v>
       </c>
       <c r="G52">
         <v>1022.6</v>
@@ -5557,28 +5557,28 @@
         <v>803.5</v>
       </c>
       <c r="M52">
-        <v>312.34164800253</v>
+        <v>318.5884809625806</v>
       </c>
       <c r="N52">
-        <v>491.15835199747</v>
+        <v>484.9115190374194</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>491.15835199747</v>
+        <v>484.9115190374194</v>
       </c>
       <c r="Q52">
-        <v>518.55835199747</v>
+        <v>512.3115190374194</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1570868782562181</v>
+        <v>0.1593580390369572</v>
       </c>
       <c r="T52">
-        <v>2.038258257599979</v>
+        <v>2.079855364897938</v>
       </c>
       <c r="U52">
         <v>0.06618110587651872</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.572503555444811</v>
+        <v>2.522062309259618</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1118378031251336</v>
+        <v>0.1138616141838988</v>
       </c>
       <c r="C53">
-        <v>4103.732723765658</v>
+        <v>3847.05996203784</v>
       </c>
       <c r="D53">
-        <v>7895.021472572694</v>
+        <v>7732.73868631168</v>
       </c>
       <c r="E53">
-        <v>2949.591202126574</v>
+        <v>3043.981177593379</v>
       </c>
       <c r="F53">
-        <v>4813.888748807035</v>
+        <v>4908.27872427384</v>
       </c>
       <c r="G53">
         <v>1022.6</v>
@@ -5639,45 +5639,45 @@
         <v>803.5</v>
       </c>
       <c r="M53">
-        <v>318.5884809625806</v>
+        <v>342.0142894575897</v>
       </c>
       <c r="N53">
-        <v>484.9115190374194</v>
+        <v>461.4857105424103</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>484.9115190374194</v>
+        <v>461.4857105424103</v>
       </c>
       <c r="Q53">
-        <v>512.3115190374194</v>
+        <v>488.8857105424103</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1593580390369572</v>
+        <v>0.1617238315168938</v>
       </c>
       <c r="T53">
-        <v>2.079855364897938</v>
+        <v>2.123185684999978</v>
       </c>
       <c r="U53">
-        <v>0.06618110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="V53">
         <v>0</v>
       </c>
       <c r="W53">
-        <v>0.06618110587651872</v>
+        <v>0.06968110587651873</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.522062309259618</v>
+        <v>2.349317045420219</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1138616141838988</v>
+        <v>0.1141004252426639</v>
       </c>
       <c r="C54">
-        <v>3847.05996203784</v>
+        <v>3733.959510745845</v>
       </c>
       <c r="D54">
-        <v>7732.73868631168</v>
+        <v>7714.02821048649</v>
       </c>
       <c r="E54">
-        <v>3043.981177593379</v>
+        <v>3138.371153060183</v>
       </c>
       <c r="F54">
-        <v>4908.27872427384</v>
+        <v>5002.668699740644</v>
       </c>
       <c r="G54">
         <v>1022.6</v>
@@ -5721,28 +5721,28 @@
         <v>803.5</v>
       </c>
       <c r="M54">
-        <v>342.0142894575897</v>
+        <v>348.5914873317741</v>
       </c>
       <c r="N54">
-        <v>461.4857105424103</v>
+        <v>454.9085126682259</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>461.4857105424103</v>
+        <v>454.9085126682259</v>
       </c>
       <c r="Q54">
-        <v>488.8857105424103</v>
+        <v>482.3085126682259</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1617238315168938</v>
+        <v>0.1641902960172532</v>
       </c>
       <c r="T54">
-        <v>2.123185684999978</v>
+        <v>2.168359848510616</v>
       </c>
       <c r="U54">
         <v>0.06968110587651873</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.349317045420219</v>
+        <v>2.304990308714177</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1141004252426639</v>
+        <v>0.1143392363014291</v>
       </c>
       <c r="C55">
-        <v>3733.959510745845</v>
+        <v>3620.949386281333</v>
       </c>
       <c r="D55">
-        <v>7714.02821048649</v>
+        <v>7695.408061488783</v>
       </c>
       <c r="E55">
-        <v>3138.371153060183</v>
+        <v>3232.761128526989</v>
       </c>
       <c r="F55">
-        <v>5002.668699740644</v>
+        <v>5097.05867520745</v>
       </c>
       <c r="G55">
         <v>1022.6</v>
@@ -5803,28 +5803,28 @@
         <v>803.5</v>
       </c>
       <c r="M55">
-        <v>348.5914873317741</v>
+        <v>355.1686852059586</v>
       </c>
       <c r="N55">
-        <v>454.9085126682259</v>
+        <v>448.3313147940414</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>454.9085126682259</v>
+        <v>448.3313147940414</v>
       </c>
       <c r="Q55">
-        <v>482.3085126682259</v>
+        <v>475.7313147940414</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1641902960172532</v>
+        <v>0.1667639981045848</v>
       </c>
       <c r="T55">
-        <v>2.168359848510616</v>
+        <v>2.215498106086934</v>
       </c>
       <c r="U55">
         <v>0.06968110587651873</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.304990308714177</v>
+        <v>2.262305302997247</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1143392363014291</v>
+        <v>0.1161180473601943</v>
       </c>
       <c r="C56">
-        <v>3620.949386281333</v>
+        <v>3390.64361177212</v>
       </c>
       <c r="D56">
-        <v>7695.408061488783</v>
+        <v>7559.492262446375</v>
       </c>
       <c r="E56">
-        <v>3232.761128526989</v>
+        <v>3327.151103993793</v>
       </c>
       <c r="F56">
-        <v>5097.05867520745</v>
+        <v>5191.448650674254</v>
       </c>
       <c r="G56">
         <v>1022.6</v>
@@ -5885,45 +5885,45 @@
         <v>803.5</v>
       </c>
       <c r="M56">
-        <v>355.1686852059586</v>
+        <v>376.2819393020309</v>
       </c>
       <c r="N56">
-        <v>448.3313147940414</v>
+        <v>427.2180606979691</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>448.3313147940414</v>
+        <v>427.2180606979691</v>
       </c>
       <c r="Q56">
-        <v>475.7313147940414</v>
+        <v>454.6180606979691</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1667639981045848</v>
+        <v>0.1694520869513534</v>
       </c>
       <c r="T56">
-        <v>2.215498106086934</v>
+        <v>2.26473139733331</v>
       </c>
       <c r="U56">
-        <v>0.06968110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="V56">
         <v>0</v>
       </c>
       <c r="W56">
-        <v>0.06968110587651873</v>
+        <v>0.07248110587651872</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.262305302997247</v>
+        <v>2.135366904641823</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1161180473601943</v>
+        <v>0.1163848584189595</v>
       </c>
       <c r="C57">
-        <v>3390.64361177212</v>
+        <v>3276.280056191353</v>
       </c>
       <c r="D57">
-        <v>7559.492262446375</v>
+        <v>7539.518682332411</v>
       </c>
       <c r="E57">
-        <v>3327.151103993793</v>
+        <v>3421.541079460598</v>
       </c>
       <c r="F57">
-        <v>5191.448650674254</v>
+        <v>5285.838626141059</v>
       </c>
       <c r="G57">
         <v>1022.6</v>
@@ -5967,28 +5967,28 @@
         <v>803.5</v>
       </c>
       <c r="M57">
-        <v>376.2819393020309</v>
+        <v>383.1234291075223</v>
       </c>
       <c r="N57">
-        <v>427.2180606979691</v>
+        <v>420.3765708924777</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>427.2180606979691</v>
+        <v>420.3765708924777</v>
       </c>
       <c r="Q57">
-        <v>454.6180606979691</v>
+        <v>447.7765708924777</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1694520869513534</v>
+        <v>0.1722623616547933</v>
       </c>
       <c r="T57">
-        <v>2.26473139733331</v>
+        <v>2.316202565454522</v>
       </c>
       <c r="U57">
         <v>0.07248110587651872</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.135366904641823</v>
+        <v>2.097235352773219</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1163848584189595</v>
+        <v>0.1166516694777247</v>
       </c>
       <c r="C58">
-        <v>3276.280056191353</v>
+        <v>3162.021770272288</v>
       </c>
       <c r="D58">
-        <v>7539.518682332411</v>
+        <v>7519.65037188015</v>
       </c>
       <c r="E58">
-        <v>3421.541079460598</v>
+        <v>3515.931054927402</v>
       </c>
       <c r="F58">
-        <v>5285.838626141059</v>
+        <v>5380.228601607863</v>
       </c>
       <c r="G58">
         <v>1022.6</v>
@@ -6049,28 +6049,28 @@
         <v>803.5</v>
       </c>
       <c r="M58">
-        <v>383.1234291075223</v>
+        <v>389.9649189130138</v>
       </c>
       <c r="N58">
-        <v>420.3765708924777</v>
+        <v>413.5350810869862</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>420.3765708924777</v>
+        <v>413.5350810869862</v>
       </c>
       <c r="Q58">
-        <v>447.7765708924777</v>
+        <v>440.9350810869861</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1722623616547933</v>
+        <v>0.1752033468095559</v>
       </c>
       <c r="T58">
-        <v>2.316202565454522</v>
+        <v>2.370067741395325</v>
       </c>
       <c r="U58">
         <v>0.07248110587651872</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.097235352773219</v>
+        <v>2.060441750092987</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1166516694777247</v>
+        <v>0.1169184805364899</v>
       </c>
       <c r="C59">
-        <v>3162.021770272288</v>
+        <v>3047.86792397527</v>
       </c>
       <c r="D59">
-        <v>7519.65037188015</v>
+        <v>7499.886501049938</v>
       </c>
       <c r="E59">
-        <v>3515.931054927402</v>
+        <v>3610.321030394207</v>
       </c>
       <c r="F59">
-        <v>5380.228601607863</v>
+        <v>5474.618577074668</v>
       </c>
       <c r="G59">
         <v>1022.6</v>
@@ -6131,28 +6131,28 @@
         <v>803.5</v>
       </c>
       <c r="M59">
-        <v>389.9649189130138</v>
+        <v>396.8064087185053</v>
       </c>
       <c r="N59">
-        <v>413.5350810869862</v>
+        <v>406.6935912814947</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>413.5350810869862</v>
+        <v>406.6935912814947</v>
       </c>
       <c r="Q59">
-        <v>440.9350810869861</v>
+        <v>434.0935912814947</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1752033468095559</v>
+        <v>0.1782843788764501</v>
       </c>
       <c r="T59">
-        <v>2.370067741395325</v>
+        <v>2.426497925714261</v>
       </c>
       <c r="U59">
         <v>0.07248110587651872</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.060441750092987</v>
+        <v>2.024916892332763</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1169184805364899</v>
+        <v>0.1217872915952551</v>
       </c>
       <c r="C60">
-        <v>3047.867923975273</v>
+        <v>2610.234082380697</v>
       </c>
       <c r="D60">
-        <v>7499.886501049939</v>
+        <v>7156.642634922168</v>
       </c>
       <c r="E60">
-        <v>3610.321030394206</v>
+        <v>3704.711005861011</v>
       </c>
       <c r="F60">
-        <v>5474.618577074667</v>
+        <v>5569.008552541472</v>
       </c>
       <c r="G60">
         <v>1022.6</v>
@@ -6213,45 +6213,45 @@
         <v>803.5</v>
       </c>
       <c r="M60">
-        <v>396.8064087185052</v>
+        <v>447.0861652338202</v>
       </c>
       <c r="N60">
-        <v>406.6935912814948</v>
+        <v>356.4138347661798</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>406.6935912814948</v>
+        <v>356.4138347661798</v>
       </c>
       <c r="Q60">
-        <v>434.0935912814948</v>
+        <v>383.8138347661798</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.17828437887645</v>
+        <v>0.1815157051905098</v>
       </c>
       <c r="T60">
-        <v>2.42649792571426</v>
+        <v>2.485680801951193</v>
       </c>
       <c r="U60">
-        <v>0.07248110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="V60">
         <v>0</v>
       </c>
       <c r="W60">
-        <v>0.07248110587651872</v>
+        <v>0.08028110587651874</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.024916892332763</v>
+        <v>1.797192716933614</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1217872915952551</v>
+        <v>0.1221321026540203</v>
       </c>
       <c r="C61">
-        <v>2610.234082380697</v>
+        <v>2492.722909106579</v>
       </c>
       <c r="D61">
-        <v>7156.642634922168</v>
+        <v>7133.521437114855</v>
       </c>
       <c r="E61">
-        <v>3704.711005861011</v>
+        <v>3799.100981327815</v>
       </c>
       <c r="F61">
-        <v>5569.008552541472</v>
+        <v>5663.398528008276</v>
       </c>
       <c r="G61">
         <v>1022.6</v>
@@ -6295,28 +6295,28 @@
         <v>803.5</v>
       </c>
       <c r="M61">
-        <v>447.0861652338202</v>
+        <v>454.6638968479528</v>
       </c>
       <c r="N61">
-        <v>356.4138347661798</v>
+        <v>348.8361031520472</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>356.4138347661798</v>
+        <v>348.8361031520472</v>
       </c>
       <c r="Q61">
-        <v>383.8138347661798</v>
+        <v>376.2361031520472</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1815157051905098</v>
+        <v>0.1849085978202726</v>
       </c>
       <c r="T61">
-        <v>2.485680801951193</v>
+        <v>2.547822821999974</v>
       </c>
       <c r="U61">
         <v>0.08028110587651874</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.797192716933614</v>
+        <v>1.76723950498472</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1221321026540203</v>
+        <v>0.1248559137127855</v>
       </c>
       <c r="C62">
-        <v>2492.722909106579</v>
+        <v>2220.809280821872</v>
       </c>
       <c r="D62">
-        <v>7133.521437114855</v>
+        <v>6955.997784296952</v>
       </c>
       <c r="E62">
-        <v>3799.100981327815</v>
+        <v>3893.49095679462</v>
       </c>
       <c r="F62">
-        <v>5663.398528008276</v>
+        <v>5757.788503475081</v>
       </c>
       <c r="G62">
         <v>1022.6</v>
@@ -6377,45 +6377,45 @@
         <v>803.5</v>
       </c>
       <c r="M62">
-        <v>454.6638968479528</v>
+        <v>484.697003625638</v>
       </c>
       <c r="N62">
-        <v>348.8361031520472</v>
+        <v>318.802996374362</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>348.8361031520472</v>
+        <v>318.802996374362</v>
       </c>
       <c r="Q62">
-        <v>376.2361031520472</v>
+        <v>346.2029963743619</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1849085978202726</v>
+        <v>0.1884754849438693</v>
       </c>
       <c r="T62">
-        <v>2.547822821999974</v>
+        <v>2.613151612307665</v>
       </c>
       <c r="U62">
-        <v>0.08028110587651874</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="V62">
         <v>0</v>
       </c>
       <c r="W62">
-        <v>0.08028110587651874</v>
+        <v>0.08418110587651872</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.76723950498472</v>
+        <v>1.657736676706575</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1248559137127855</v>
+        <v>0.1252397247715507</v>
       </c>
       <c r="C63">
-        <v>2220.809280821872</v>
+        <v>2102.112273002615</v>
       </c>
       <c r="D63">
-        <v>6955.997784296952</v>
+        <v>6931.690751944499</v>
       </c>
       <c r="E63">
-        <v>3893.49095679462</v>
+        <v>3987.880932261424</v>
       </c>
       <c r="F63">
-        <v>5757.788503475081</v>
+        <v>5852.178478941885</v>
       </c>
       <c r="G63">
         <v>1022.6</v>
@@ -6459,28 +6459,28 @@
         <v>803.5</v>
       </c>
       <c r="M63">
-        <v>484.697003625638</v>
+        <v>492.6428561440911</v>
       </c>
       <c r="N63">
-        <v>318.802996374362</v>
+        <v>310.8571438559089</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>318.802996374362</v>
+        <v>310.8571438559089</v>
       </c>
       <c r="Q63">
-        <v>346.2029963743619</v>
+        <v>338.2571438559089</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1884754849438693</v>
+        <v>0.192230102968708</v>
       </c>
       <c r="T63">
-        <v>2.613151612307665</v>
+        <v>2.681918759999973</v>
       </c>
       <c r="U63">
         <v>0.08418110587651872</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.657736676706575</v>
+        <v>1.630998988372598</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1252397247715507</v>
+        <v>0.1256235358303158</v>
       </c>
       <c r="C64">
-        <v>2102.112273002615</v>
+        <v>1983.584550576275</v>
       </c>
       <c r="D64">
-        <v>6931.690751944499</v>
+        <v>6907.553004984966</v>
       </c>
       <c r="E64">
-        <v>3987.880932261424</v>
+        <v>4082.27090772823</v>
       </c>
       <c r="F64">
-        <v>5852.178478941885</v>
+        <v>5946.568454408691</v>
       </c>
       <c r="G64">
         <v>1022.6</v>
@@ -6541,28 +6541,28 @@
         <v>803.5</v>
       </c>
       <c r="M64">
-        <v>492.6428561440911</v>
+        <v>500.5887086625443</v>
       </c>
       <c r="N64">
-        <v>310.8571438559089</v>
+        <v>302.9112913374557</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>310.8571438559089</v>
+        <v>302.9112913374557</v>
       </c>
       <c r="Q64">
-        <v>338.2571438559089</v>
+        <v>330.3112913374557</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.192230102968708</v>
+        <v>0.1961876733192136</v>
       </c>
       <c r="T64">
-        <v>2.681918759999973</v>
+        <v>2.754403050810782</v>
       </c>
       <c r="U64">
         <v>0.08418110587651872</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.630998988372598</v>
+        <v>1.605110115541287</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1256235358303158</v>
+        <v>0.126007346889081</v>
       </c>
       <c r="C65">
-        <v>1983.584550576275</v>
+        <v>1865.224351207292</v>
       </c>
       <c r="D65">
-        <v>6907.553004984966</v>
+        <v>6883.582781082787</v>
       </c>
       <c r="E65">
-        <v>4082.27090772823</v>
+        <v>4176.660883195034</v>
       </c>
       <c r="F65">
-        <v>5946.568454408691</v>
+        <v>6040.958429875495</v>
       </c>
       <c r="G65">
         <v>1022.6</v>
@@ -6623,28 +6623,28 @@
         <v>803.5</v>
       </c>
       <c r="M65">
-        <v>500.5887086625443</v>
+        <v>508.5345611809974</v>
       </c>
       <c r="N65">
-        <v>302.9112913374557</v>
+        <v>294.9654388190026</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>302.9112913374557</v>
+        <v>294.9654388190026</v>
       </c>
       <c r="Q65">
-        <v>330.3112913374557</v>
+        <v>322.3654388190026</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1961876733192136</v>
+        <v>0.2003651086891917</v>
       </c>
       <c r="T65">
-        <v>2.754403050810782</v>
+        <v>2.830914246666637</v>
       </c>
       <c r="U65">
         <v>0.08418110587651872</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.605110115541287</v>
+        <v>1.580030269985954</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.126007346889081</v>
+        <v>0.1263911579478462</v>
       </c>
       <c r="C66">
-        <v>1865.224351207292</v>
+        <v>1747.029936937755</v>
       </c>
       <c r="D66">
-        <v>6883.582781082787</v>
+        <v>6859.778342280055</v>
       </c>
       <c r="E66">
-        <v>4176.660883195034</v>
+        <v>4271.050858661839</v>
       </c>
       <c r="F66">
-        <v>6040.958429875495</v>
+        <v>6135.3484053423</v>
       </c>
       <c r="G66">
         <v>1022.6</v>
@@ -6705,28 +6705,28 @@
         <v>803.5</v>
       </c>
       <c r="M66">
-        <v>508.5345611809974</v>
+        <v>516.4804136994504</v>
       </c>
       <c r="N66">
-        <v>294.9654388190026</v>
+        <v>287.0195863005496</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>294.9654388190026</v>
+        <v>287.0195863005496</v>
       </c>
       <c r="Q66">
-        <v>322.3654388190026</v>
+        <v>314.4195863005496</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2003651086891917</v>
+        <v>0.2047812546517401</v>
       </c>
       <c r="T66">
-        <v>2.830914246666637</v>
+        <v>2.911797510857113</v>
       </c>
       <c r="U66">
         <v>0.08418110587651872</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.580030269985954</v>
+        <v>1.55572211198617</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1263911579478462</v>
+        <v>0.1267749690066114</v>
       </c>
       <c r="C67">
-        <v>1747.029936937755</v>
+        <v>1628.999593767369</v>
       </c>
       <c r="D67">
-        <v>6859.778342280055</v>
+        <v>6836.137974576473</v>
       </c>
       <c r="E67">
-        <v>4271.050858661839</v>
+        <v>4365.440834128643</v>
       </c>
       <c r="F67">
-        <v>6135.3484053423</v>
+        <v>6229.738380809104</v>
       </c>
       <c r="G67">
         <v>1022.6</v>
@@ -6787,28 +6787,28 @@
         <v>803.5</v>
       </c>
       <c r="M67">
-        <v>516.4804136994504</v>
+        <v>524.4262662179035</v>
       </c>
       <c r="N67">
-        <v>287.0195863005496</v>
+        <v>279.0737337820965</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>287.0195863005496</v>
+        <v>279.0737337820965</v>
       </c>
       <c r="Q67">
-        <v>314.4195863005496</v>
+        <v>306.4737337820965</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2047812546517401</v>
+        <v>0.2094571739062031</v>
       </c>
       <c r="T67">
-        <v>2.911797510857113</v>
+        <v>2.997438614117617</v>
       </c>
       <c r="U67">
         <v>0.08418110587651872</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.55572211198617</v>
+        <v>1.532150564834865</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1267749690066114</v>
+        <v>0.1271587800653766</v>
       </c>
       <c r="C68">
-        <v>1628.999593767369</v>
+        <v>1511.131631242043</v>
       </c>
       <c r="D68">
-        <v>6836.137974576473</v>
+        <v>6812.659987517952</v>
       </c>
       <c r="E68">
-        <v>4365.440834128643</v>
+        <v>4459.830809595448</v>
       </c>
       <c r="F68">
-        <v>6229.738380809104</v>
+        <v>6324.128356275909</v>
       </c>
       <c r="G68">
         <v>1022.6</v>
@@ -6869,28 +6869,28 @@
         <v>803.5</v>
       </c>
       <c r="M68">
-        <v>524.4262662179035</v>
+        <v>532.3721187363566</v>
       </c>
       <c r="N68">
-        <v>279.0737337820965</v>
+        <v>271.1278812636434</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>279.0737337820965</v>
+        <v>271.1278812636434</v>
       </c>
       <c r="Q68">
-        <v>306.4737337820965</v>
+        <v>298.5278812636434</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2094571739062031</v>
+        <v>0.214416482206391</v>
       </c>
       <c r="T68">
-        <v>2.997438614117617</v>
+        <v>3.088270087272696</v>
       </c>
       <c r="U68">
         <v>0.08418110587651872</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.532150564834865</v>
+        <v>1.509282645956732</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1271587800653766</v>
+        <v>0.1371985911241418</v>
       </c>
       <c r="C69">
-        <v>1511.131631242043</v>
+        <v>855.1598537421269</v>
       </c>
       <c r="D69">
-        <v>6812.659987517952</v>
+        <v>6251.07818548484</v>
       </c>
       <c r="E69">
-        <v>4459.830809595448</v>
+        <v>4554.220785062253</v>
       </c>
       <c r="F69">
-        <v>6324.128356275909</v>
+        <v>6418.518331742714</v>
       </c>
       <c r="G69">
         <v>1022.6</v>
@@ -6951,45 +6951,45 @@
         <v>803.5</v>
       </c>
       <c r="M69">
-        <v>532.3721187363566</v>
+        <v>631.4609315655563</v>
       </c>
       <c r="N69">
-        <v>271.1278812636434</v>
+        <v>172.0390684344437</v>
       </c>
       <c r="O69">
         <v>0</v>
       </c>
       <c r="P69">
-        <v>271.1278812636434</v>
+        <v>172.0390684344437</v>
       </c>
       <c r="Q69">
-        <v>298.5278812636434</v>
+        <v>199.4390684344437</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.214416482206391</v>
+        <v>0.2196857472753407</v>
       </c>
       <c r="T69">
-        <v>3.088270087272696</v>
+        <v>3.184778527499968</v>
       </c>
       <c r="U69">
-        <v>0.08418110587651872</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="V69">
         <v>0</v>
       </c>
       <c r="W69">
-        <v>0.08418110587651872</v>
+        <v>0.09838110587651873</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>1.509282645956732</v>
+        <v>1.272446100517912</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1371985911241418</v>
+        <v>0.137724402182907</v>
       </c>
       <c r="C70">
-        <v>855.1598537421269</v>
+        <v>733.8988351797843</v>
       </c>
       <c r="D70">
-        <v>6251.07818548484</v>
+        <v>6224.207142389302</v>
       </c>
       <c r="E70">
-        <v>4554.220785062253</v>
+        <v>4648.610760529057</v>
       </c>
       <c r="F70">
-        <v>6418.518331742714</v>
+        <v>6512.908307209518</v>
       </c>
       <c r="G70">
         <v>1022.6</v>
@@ -7033,28 +7033,28 @@
         <v>803.5</v>
       </c>
       <c r="M70">
-        <v>631.4609315655563</v>
+        <v>640.747121735638</v>
       </c>
       <c r="N70">
-        <v>172.0390684344437</v>
+        <v>162.752878264362</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>172.0390684344437</v>
+        <v>162.752878264362</v>
       </c>
       <c r="Q70">
-        <v>199.4390684344437</v>
+        <v>190.152878264362</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2196857472753407</v>
+        <v>0.225294964929384</v>
       </c>
       <c r="T70">
-        <v>3.184778527499968</v>
+        <v>3.287513318709644</v>
       </c>
       <c r="U70">
         <v>0.09838110587651873</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.272446100517912</v>
+        <v>1.254004852684319</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.137724402182907</v>
+        <v>0.1582702132416721</v>
       </c>
       <c r="C71">
-        <v>733.8988351797843</v>
+        <v>-255.6018401452739</v>
       </c>
       <c r="D71">
-        <v>6224.207142389302</v>
+        <v>5329.096442531049</v>
       </c>
       <c r="E71">
-        <v>4648.610760529057</v>
+        <v>4743.000735995862</v>
       </c>
       <c r="F71">
-        <v>6512.908307209518</v>
+        <v>6607.298282676323</v>
       </c>
       <c r="G71">
         <v>1022.6</v>
@@ -7115,45 +7115,45 @@
         <v>803.5</v>
       </c>
       <c r="M71">
-        <v>640.747121735638</v>
+        <v>839.0020427902625</v>
       </c>
       <c r="N71">
-        <v>162.752878264362</v>
+        <v>-35.50204279026252</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P71">
-        <v>162.752878264362</v>
+        <v>-35.50204279026252</v>
       </c>
       <c r="Q71">
-        <v>190.152878264362</v>
+        <v>-8.102042790262523</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.225294964929384</v>
+        <v>0.2312781304270301</v>
       </c>
       <c r="T71">
-        <v>3.287513318709644</v>
+        <v>3.397097095999966</v>
       </c>
       <c r="U71">
-        <v>0.09838110587651873</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="V71">
         <v>0</v>
       </c>
       <c r="W71">
-        <v>0.09838110587651873</v>
+        <v>0.1269811058765187</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.254004852684319</v>
+        <v>0.9576853917158609</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1582702132416721</v>
+        <v>0.1590820243004373</v>
       </c>
       <c r="C72">
-        <v>-255.6018401452739</v>
+        <v>-380.1022593750313</v>
       </c>
       <c r="D72">
-        <v>5329.096442531049</v>
+        <v>5298.985998768097</v>
       </c>
       <c r="E72">
-        <v>4743.000735995862</v>
+        <v>4837.390711462667</v>
       </c>
       <c r="F72">
-        <v>6607.298282676323</v>
+        <v>6701.688258143128</v>
       </c>
       <c r="G72">
         <v>1022.6</v>
@@ -7197,28 +7197,28 @@
         <v>803.5</v>
       </c>
       <c r="M72">
-        <v>839.0020427902625</v>
+        <v>850.987786258695</v>
       </c>
       <c r="N72">
-        <v>-35.50204279026252</v>
+        <v>-47.487786258695</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-35.50204279026252</v>
+        <v>-47.487786258695</v>
       </c>
       <c r="Q72">
-        <v>-8.102042790262523</v>
+        <v>-20.087786258695</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2312781304270301</v>
+        <v>0.2376739280279622</v>
       </c>
       <c r="T72">
-        <v>3.397097095999966</v>
+        <v>3.514238375172379</v>
       </c>
       <c r="U72">
         <v>0.1269811058765187</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.9576853917158609</v>
+        <v>0.9441968650719753</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1590820243004373</v>
+        <v>0.1598938353592025</v>
       </c>
       <c r="C73">
-        <v>-380.1022593750295</v>
+        <v>-504.2643304712537</v>
       </c>
       <c r="D73">
-        <v>5298.985998768097</v>
+        <v>5269.213903138678</v>
       </c>
       <c r="E73">
-        <v>4837.390711462665</v>
+        <v>4931.780686929471</v>
       </c>
       <c r="F73">
-        <v>6701.688258143126</v>
+        <v>6796.078233609932</v>
       </c>
       <c r="G73">
         <v>1022.6</v>
@@ -7279,28 +7279,28 @@
         <v>803.5</v>
       </c>
       <c r="M73">
-        <v>850.9877862586948</v>
+        <v>862.9735297271271</v>
       </c>
       <c r="N73">
-        <v>-47.48778625869477</v>
+        <v>-59.47352972712713</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-47.48778625869477</v>
+        <v>-59.47352972712713</v>
       </c>
       <c r="Q73">
-        <v>-20.08778625869477</v>
+        <v>-32.07352972712713</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2376739280279621</v>
+        <v>0.2445265683146751</v>
       </c>
       <c r="T73">
-        <v>3.514238375172377</v>
+        <v>3.639746888571391</v>
       </c>
       <c r="U73">
         <v>0.1269811058765187</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.9441968650719755</v>
+        <v>0.9310830197237536</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1598938353592025</v>
+        <v>0.1607056464179677</v>
       </c>
       <c r="C74">
-        <v>-504.2643304712537</v>
+        <v>-628.0937245487548</v>
       </c>
       <c r="D74">
-        <v>5269.213903138678</v>
+        <v>5239.774484527981</v>
       </c>
       <c r="E74">
-        <v>4931.780686929471</v>
+        <v>5026.170662396275</v>
       </c>
       <c r="F74">
-        <v>6796.078233609932</v>
+        <v>6890.468209076736</v>
       </c>
       <c r="G74">
         <v>1022.6</v>
@@ -7361,28 +7361,28 @@
         <v>803.5</v>
       </c>
       <c r="M74">
-        <v>862.9735297271271</v>
+        <v>874.9592731955595</v>
       </c>
       <c r="N74">
-        <v>-59.47352972712713</v>
+        <v>-71.45927319555949</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-59.47352972712713</v>
+        <v>-71.45927319555949</v>
       </c>
       <c r="Q74">
-        <v>-32.07352972712713</v>
+        <v>-44.05927319555949</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2445265683146751</v>
+        <v>0.251886811585589</v>
       </c>
       <c r="T74">
-        <v>3.639746888571391</v>
+        <v>3.77455232888885</v>
       </c>
       <c r="U74">
         <v>0.1269811058765187</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9310830197237536</v>
+        <v>0.9183284578097296</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1607056464179677</v>
+        <v>0.1615174574767329</v>
       </c>
       <c r="C75">
-        <v>-628.0937245487548</v>
+        <v>-751.5959866870608</v>
       </c>
       <c r="D75">
-        <v>5239.774484527981</v>
+        <v>5210.66219785648</v>
       </c>
       <c r="E75">
-        <v>5026.170662396275</v>
+        <v>5120.56063786308</v>
       </c>
       <c r="F75">
-        <v>6890.468209076736</v>
+        <v>6984.858184543541</v>
       </c>
       <c r="G75">
         <v>1022.6</v>
@@ -7443,28 +7443,28 @@
         <v>803.5</v>
       </c>
       <c r="M75">
-        <v>874.9592731955595</v>
+        <v>886.9450166639917</v>
       </c>
       <c r="N75">
-        <v>-71.45927319555949</v>
+        <v>-83.44501666399174</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-71.45927319555949</v>
+        <v>-83.44501666399174</v>
       </c>
       <c r="Q75">
-        <v>-44.05927319555949</v>
+        <v>-56.04501666399174</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.251886811585589</v>
+        <v>0.2598132274158039</v>
       </c>
       <c r="T75">
-        <v>3.77455232888885</v>
+        <v>3.919727418461498</v>
       </c>
       <c r="U75">
         <v>0.1269811058765187</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9183284578097296</v>
+        <v>0.9059186137852738</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1615174574767329</v>
+        <v>0.1623292685354981</v>
       </c>
       <c r="C76">
-        <v>-751.5959866870608</v>
+        <v>-874.7765394123344</v>
       </c>
       <c r="D76">
-        <v>5210.66219785648</v>
+        <v>5181.871620598011</v>
       </c>
       <c r="E76">
-        <v>5120.56063786308</v>
+        <v>5214.950613329885</v>
       </c>
       <c r="F76">
-        <v>6984.858184543541</v>
+        <v>7079.248160010346</v>
       </c>
       <c r="G76">
         <v>1022.6</v>
@@ -7525,28 +7525,28 @@
         <v>803.5</v>
       </c>
       <c r="M76">
-        <v>886.9450166639917</v>
+        <v>898.9307601324241</v>
       </c>
       <c r="N76">
-        <v>-83.44501666399174</v>
+        <v>-95.4307601324241</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-83.44501666399174</v>
+        <v>-95.4307601324241</v>
       </c>
       <c r="Q76">
-        <v>-56.04501666399174</v>
+        <v>-68.03076013242409</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2598132274158039</v>
+        <v>0.2683737565124361</v>
       </c>
       <c r="T76">
-        <v>3.919727418461498</v>
+        <v>4.076516515199958</v>
       </c>
       <c r="U76">
         <v>0.1269811058765187</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.9059186137852738</v>
+        <v>0.8938396989348035</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1623292685354981</v>
+        <v>0.1631410795942633</v>
       </c>
       <c r="C77">
-        <v>-874.7765394123344</v>
+        <v>-997.6406860645129</v>
       </c>
       <c r="D77">
-        <v>5181.871620598011</v>
+        <v>5153.397449412637</v>
       </c>
       <c r="E77">
-        <v>5214.950613329885</v>
+        <v>5309.340588796689</v>
       </c>
       <c r="F77">
-        <v>7079.248160010346</v>
+        <v>7173.63813547715</v>
       </c>
       <c r="G77">
         <v>1022.6</v>
@@ -7607,28 +7607,28 @@
         <v>803.5</v>
       </c>
       <c r="M77">
-        <v>898.9307601324241</v>
+        <v>910.9165036008565</v>
       </c>
       <c r="N77">
-        <v>-95.4307601324241</v>
+        <v>-107.4165036008565</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-95.4307601324241</v>
+        <v>-107.4165036008565</v>
       </c>
       <c r="Q77">
-        <v>-68.03076013242409</v>
+        <v>-80.01650360085645</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2683737565124361</v>
+        <v>0.2776476630337876</v>
       </c>
       <c r="T77">
-        <v>4.076516515199958</v>
+        <v>4.246371369999957</v>
       </c>
       <c r="U77">
         <v>0.1269811058765187</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8938396989348035</v>
+        <v>0.8820786502646086</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1631410795942633</v>
+        <v>0.1639528906530284</v>
       </c>
       <c r="C78">
-        <v>-997.6406860645129</v>
+        <v>-1120.193614054015</v>
       </c>
       <c r="D78">
-        <v>5153.397449412637</v>
+        <v>5125.23449688994</v>
       </c>
       <c r="E78">
-        <v>5309.340588796689</v>
+        <v>5403.730564263494</v>
       </c>
       <c r="F78">
-        <v>7173.63813547715</v>
+        <v>7268.028110943955</v>
       </c>
       <c r="G78">
         <v>1022.6</v>
@@ -7689,28 +7689,28 @@
         <v>803.5</v>
       </c>
       <c r="M78">
-        <v>910.9165036008565</v>
+        <v>922.9022470692887</v>
       </c>
       <c r="N78">
-        <v>-107.4165036008565</v>
+        <v>-119.4022470692887</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-107.4165036008565</v>
+        <v>-119.4022470692887</v>
       </c>
       <c r="Q78">
-        <v>-80.01650360085645</v>
+        <v>-92.0022470692887</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2776476630337876</v>
+        <v>0.2877279962091697</v>
       </c>
       <c r="T78">
-        <v>4.246371369999957</v>
+        <v>4.430996212173867</v>
       </c>
       <c r="U78">
         <v>0.1269811058765187</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8820786502646086</v>
+        <v>0.8706230833780554</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1639528906530284</v>
+        <v>0.1647647017117936</v>
       </c>
       <c r="C79">
-        <v>-1120.193614054015</v>
+        <v>-1242.440398012273</v>
       </c>
       <c r="D79">
-        <v>5125.23449688994</v>
+        <v>5097.377688398486</v>
       </c>
       <c r="E79">
-        <v>5403.730564263494</v>
+        <v>5498.120539730298</v>
       </c>
       <c r="F79">
-        <v>7268.028110943955</v>
+        <v>7362.418086410759</v>
       </c>
       <c r="G79">
         <v>1022.6</v>
@@ -7771,28 +7771,28 @@
         <v>803.5</v>
       </c>
       <c r="M79">
-        <v>922.9022470692887</v>
+        <v>934.8879905377211</v>
       </c>
       <c r="N79">
-        <v>-119.4022470692887</v>
+        <v>-131.3879905377211</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-119.4022470692887</v>
+        <v>-131.3879905377211</v>
       </c>
       <c r="Q79">
-        <v>-92.0022470692887</v>
+        <v>-103.9879905377211</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2877279962091697</v>
+        <v>0.2987247233095865</v>
       </c>
       <c r="T79">
-        <v>4.430996212173867</v>
+        <v>4.632405130909044</v>
       </c>
       <c r="U79">
         <v>0.1269811058765187</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8706230833780554</v>
+        <v>0.8594612489757726</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1647647017117936</v>
+        <v>0.1655765127705588</v>
       </c>
       <c r="C80">
-        <v>-1242.440398012273</v>
+        <v>-1364.386002840049</v>
       </c>
       <c r="D80">
-        <v>5097.377688398486</v>
+        <v>5069.822059037516</v>
       </c>
       <c r="E80">
-        <v>5498.120539730298</v>
+        <v>5592.510515197104</v>
       </c>
       <c r="F80">
-        <v>7362.418086410759</v>
+        <v>7456.808061877565</v>
       </c>
       <c r="G80">
         <v>1022.6</v>
@@ -7853,28 +7853,28 @@
         <v>803.5</v>
       </c>
       <c r="M80">
-        <v>934.8879905377211</v>
+        <v>946.8737340061534</v>
       </c>
       <c r="N80">
-        <v>-131.3879905377211</v>
+        <v>-143.3737340061534</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-131.3879905377211</v>
+        <v>-143.3737340061534</v>
       </c>
       <c r="Q80">
-        <v>-103.9879905377211</v>
+        <v>-115.9737340061534</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2987247233095865</v>
+        <v>0.3107687577529002</v>
       </c>
       <c r="T80">
-        <v>4.632405130909044</v>
+        <v>4.852995851428522</v>
       </c>
       <c r="U80">
         <v>0.1269811058765187</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8594612489757726</v>
+        <v>0.8485819926596235</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1655765127705588</v>
+        <v>0.166388323829324</v>
       </c>
       <c r="C81">
-        <v>-1364.386002840049</v>
+        <v>-1486.03528665742</v>
       </c>
       <c r="D81">
-        <v>5069.822059037516</v>
+        <v>5042.562750686949</v>
       </c>
       <c r="E81">
-        <v>5592.510515197104</v>
+        <v>5686.900490663908</v>
       </c>
       <c r="F81">
-        <v>7456.808061877565</v>
+        <v>7551.198037344369</v>
       </c>
       <c r="G81">
         <v>1022.6</v>
@@ -7935,28 +7935,28 @@
         <v>803.5</v>
       </c>
       <c r="M81">
-        <v>946.8737340061534</v>
+        <v>958.8594774745858</v>
       </c>
       <c r="N81">
-        <v>-143.3737340061534</v>
+        <v>-155.3594774745858</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-143.3737340061534</v>
+        <v>-155.3594774745858</v>
       </c>
       <c r="Q81">
-        <v>-115.9737340061534</v>
+        <v>-127.9594774745858</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3107687577529002</v>
+        <v>0.3240171956405452</v>
       </c>
       <c r="T81">
-        <v>4.852995851428522</v>
+        <v>5.095645643999949</v>
       </c>
       <c r="U81">
         <v>0.1269811058765187</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8485819926596235</v>
+        <v>0.8379747177513782</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.166388323829324</v>
+        <v>0.1672001348880892</v>
       </c>
       <c r="C82">
-        <v>-1486.03528665742</v>
+        <v>-1607.393003659123</v>
       </c>
       <c r="D82">
-        <v>5042.562750686949</v>
+        <v>5015.595009152051</v>
       </c>
       <c r="E82">
-        <v>5686.900490663908</v>
+        <v>5781.290466130713</v>
       </c>
       <c r="F82">
-        <v>7551.198037344369</v>
+        <v>7645.588012811174</v>
       </c>
       <c r="G82">
         <v>1022.6</v>
@@ -8017,28 +8017,28 @@
         <v>803.5</v>
       </c>
       <c r="M82">
-        <v>958.8594774745858</v>
+        <v>970.8452209430181</v>
       </c>
       <c r="N82">
-        <v>-155.3594774745858</v>
+        <v>-167.3452209430181</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-155.3594774745858</v>
+        <v>-167.3452209430181</v>
       </c>
       <c r="Q82">
-        <v>-127.9594774745858</v>
+        <v>-139.9452209430181</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3240171956405452</v>
+        <v>0.338660205937416</v>
       </c>
       <c r="T82">
-        <v>5.095645643999949</v>
+        <v>5.363837519999946</v>
       </c>
       <c r="U82">
         <v>0.1269811058765187</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8379747177513782</v>
+        <v>0.8276293508655587</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1672001348880892</v>
+        <v>0.1680119459468544</v>
       </c>
       <c r="C83">
-        <v>-1607.393003659123</v>
+        <v>-1728.463806878726</v>
       </c>
       <c r="D83">
-        <v>5015.595009152051</v>
+        <v>4988.914181399252</v>
       </c>
       <c r="E83">
-        <v>5781.290466130713</v>
+        <v>5875.680441597518</v>
       </c>
       <c r="F83">
-        <v>7645.588012811174</v>
+        <v>7739.977988277979</v>
       </c>
       <c r="G83">
         <v>1022.6</v>
@@ -8099,28 +8099,28 @@
         <v>803.5</v>
       </c>
       <c r="M83">
-        <v>970.8452209430181</v>
+        <v>982.8309644114504</v>
       </c>
       <c r="N83">
-        <v>-167.3452209430181</v>
+        <v>-179.3309644114504</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-167.3452209430181</v>
+        <v>-179.3309644114504</v>
       </c>
       <c r="Q83">
-        <v>-139.9452209430181</v>
+        <v>-151.9309644114504</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.338660205937416</v>
+        <v>0.3549302173783835</v>
       </c>
       <c r="T83">
-        <v>5.363837519999946</v>
+        <v>5.661828493333276</v>
       </c>
       <c r="U83">
         <v>0.1269811058765187</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8276293508655587</v>
+        <v>0.8175363100013446</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1680119459468544</v>
+        <v>0.1688237570056196</v>
       </c>
       <c r="C84">
-        <v>-1728.463806878726</v>
+        <v>-1849.252250865078</v>
       </c>
       <c r="D84">
-        <v>4988.914181399252</v>
+        <v>4962.515712879705</v>
       </c>
       <c r="E84">
-        <v>5875.680441597518</v>
+        <v>5970.070417064322</v>
       </c>
       <c r="F84">
-        <v>7739.977988277979</v>
+        <v>7834.367963744783</v>
       </c>
       <c r="G84">
         <v>1022.6</v>
@@ -8181,28 +8181,28 @@
         <v>803.5</v>
       </c>
       <c r="M84">
-        <v>982.8309644114504</v>
+        <v>994.8167078798828</v>
       </c>
       <c r="N84">
-        <v>-179.3309644114504</v>
+        <v>-191.3167078798828</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-179.3309644114504</v>
+        <v>-191.3167078798828</v>
       </c>
       <c r="Q84">
-        <v>-151.9309644114504</v>
+        <v>-163.9167078798828</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3549302173783835</v>
+        <v>0.3731143478124062</v>
       </c>
       <c r="T84">
-        <v>5.661828493333276</v>
+        <v>5.994877228235235</v>
       </c>
       <c r="U84">
         <v>0.1269811058765187</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8175363100013446</v>
+        <v>0.8076864749410875</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1688237570056196</v>
+        <v>0.1933235680643848</v>
       </c>
       <c r="C85">
-        <v>-1849.252250865078</v>
+        <v>-2626.987311252173</v>
       </c>
       <c r="D85">
-        <v>4962.515712879705</v>
+        <v>4279.170627959415</v>
       </c>
       <c r="E85">
-        <v>5970.070417064322</v>
+        <v>6064.460392531127</v>
       </c>
       <c r="F85">
-        <v>7834.367963744783</v>
+        <v>7928.757939211588</v>
       </c>
       <c r="G85">
         <v>1022.6</v>
@@ -8263,45 +8263,45 @@
         <v>803.5</v>
       </c>
       <c r="M85">
-        <v>994.8167078798828</v>
+        <v>1230.393425234082</v>
       </c>
       <c r="N85">
-        <v>-191.3167078798828</v>
+        <v>-426.8934252340819</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-191.3167078798828</v>
+        <v>-426.8934252340819</v>
       </c>
       <c r="Q85">
-        <v>-163.9167078798828</v>
+        <v>-399.4934252340819</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3731143478124062</v>
+        <v>0.3935714945506816</v>
       </c>
       <c r="T85">
-        <v>5.994877228235235</v>
+        <v>6.369557054999938</v>
       </c>
       <c r="U85">
-        <v>0.1269811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="V85">
         <v>0</v>
       </c>
       <c r="W85">
-        <v>0.1269811058765187</v>
+        <v>0.1551811058765187</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.8076864749410875</v>
+        <v>0.6530431515002078</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1933235680643848</v>
+        <v>0.2403173791231499</v>
       </c>
       <c r="C86">
-        <v>-2626.987311252172</v>
+        <v>-3615.473624135903</v>
       </c>
       <c r="D86">
-        <v>4279.170627959415</v>
+        <v>3385.074290542488</v>
       </c>
       <c r="E86">
-        <v>6064.460392531126</v>
+        <v>6158.85036799793</v>
       </c>
       <c r="F86">
-        <v>7928.757939211587</v>
+        <v>8023.147914678391</v>
       </c>
       <c r="G86">
         <v>1022.6</v>
@@ -8345,45 +8345,45 @@
         <v>803.5</v>
       </c>
       <c r="M86">
-        <v>1230.393425234082</v>
+        <v>1678.290953403311</v>
       </c>
       <c r="N86">
-        <v>-426.8934252340816</v>
+        <v>-874.7909534033111</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-426.8934252340816</v>
+        <v>-874.7909534033111</v>
       </c>
       <c r="Q86">
-        <v>-399.4934252340817</v>
+        <v>-847.3909534033111</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3935714945506814</v>
+        <v>0.4167562608540601</v>
       </c>
       <c r="T86">
-        <v>6.369557054999934</v>
+        <v>6.79419419199993</v>
       </c>
       <c r="U86">
-        <v>0.1551811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="V86">
         <v>0</v>
       </c>
       <c r="W86">
-        <v>0.1551811058765187</v>
+        <v>0.2091811058765187</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.6530431515002078</v>
+        <v>0.4787608479749164</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2403173791231499</v>
+        <v>0.2419511901819151</v>
       </c>
       <c r="C87">
-        <v>-3615.473624135903</v>
+        <v>-3734.276011917634</v>
       </c>
       <c r="D87">
-        <v>3385.074290542488</v>
+        <v>3360.661878227562</v>
       </c>
       <c r="E87">
-        <v>6158.85036799793</v>
+        <v>6253.240343464735</v>
       </c>
       <c r="F87">
-        <v>8023.147914678391</v>
+        <v>8117.537890145196</v>
       </c>
       <c r="G87">
         <v>1022.6</v>
@@ -8427,28 +8427,28 @@
         <v>803.5</v>
       </c>
       <c r="M87">
-        <v>1678.290953403311</v>
+        <v>1698.035552855115</v>
       </c>
       <c r="N87">
-        <v>-874.7909534033111</v>
+        <v>-894.5355528551147</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-874.7909534033111</v>
+        <v>-894.5355528551147</v>
       </c>
       <c r="Q87">
-        <v>-847.3909534033111</v>
+        <v>-867.1355528551147</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4167562608540601</v>
+        <v>0.4432531366293502</v>
       </c>
       <c r="T87">
-        <v>6.79419419199993</v>
+        <v>7.279493777142782</v>
       </c>
       <c r="U87">
         <v>0.2091811058765187</v>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4787608479749164</v>
+        <v>0.4731938613705569</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2419511901819151</v>
+        <v>0.2435850012406803</v>
       </c>
       <c r="C88">
-        <v>-3734.276011917634</v>
+        <v>-3852.728806973554</v>
       </c>
       <c r="D88">
-        <v>3360.661878227562</v>
+        <v>3336.599058638446</v>
       </c>
       <c r="E88">
-        <v>6253.240343464735</v>
+        <v>6347.630318931539</v>
       </c>
       <c r="F88">
-        <v>8117.537890145196</v>
+        <v>8211.927865612</v>
       </c>
       <c r="G88">
         <v>1022.6</v>
@@ -8509,28 +8509,28 @@
         <v>803.5</v>
       </c>
       <c r="M88">
-        <v>1698.035552855115</v>
+        <v>1717.780152306918</v>
       </c>
       <c r="N88">
-        <v>-894.5355528551147</v>
+        <v>-914.2801523069184</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-894.5355528551147</v>
+        <v>-914.2801523069184</v>
       </c>
       <c r="Q88">
-        <v>-867.1355528551147</v>
+        <v>-886.8801523069184</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4432531366293502</v>
+        <v>0.4738264548316078</v>
       </c>
       <c r="T88">
-        <v>7.279493777142782</v>
+        <v>7.839454836922996</v>
       </c>
       <c r="U88">
         <v>0.2091811058765187</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4731938613705569</v>
+        <v>0.4677548514697458</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2435850012406803</v>
+        <v>0.2452188122994455</v>
       </c>
       <c r="C89">
-        <v>-3852.728806973554</v>
+        <v>-3970.839465319242</v>
       </c>
       <c r="D89">
-        <v>3336.599058638446</v>
+        <v>3312.878375759564</v>
       </c>
       <c r="E89">
-        <v>6347.630318931539</v>
+        <v>6442.020294398345</v>
       </c>
       <c r="F89">
-        <v>8211.927865612</v>
+        <v>8306.317841078806</v>
       </c>
       <c r="G89">
         <v>1022.6</v>
@@ -8591,28 +8591,28 @@
         <v>803.5</v>
       </c>
       <c r="M89">
-        <v>1717.780152306918</v>
+        <v>1737.524751758722</v>
       </c>
       <c r="N89">
-        <v>-914.2801523069184</v>
+        <v>-934.0247517587222</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-914.2801523069184</v>
+        <v>-934.0247517587222</v>
       </c>
       <c r="Q89">
-        <v>-886.8801523069184</v>
+        <v>-906.6247517587223</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4738264548316078</v>
+        <v>0.5094953260675752</v>
       </c>
       <c r="T89">
-        <v>7.839454836922996</v>
+        <v>8.492742739999914</v>
       </c>
       <c r="U89">
         <v>0.2091811058765187</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4677548514697458</v>
+        <v>0.4624394554303168</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2452188122994455</v>
+        <v>0.2468526233582107</v>
       </c>
       <c r="C90">
-        <v>-3970.839465319242</v>
+        <v>-4088.615232440567</v>
       </c>
       <c r="D90">
-        <v>3312.878375759564</v>
+        <v>3289.492584105043</v>
       </c>
       <c r="E90">
-        <v>6442.020294398345</v>
+        <v>6536.410269865149</v>
       </c>
       <c r="F90">
-        <v>8306.317841078806</v>
+        <v>8400.70781654561</v>
       </c>
       <c r="G90">
         <v>1022.6</v>
@@ -8673,28 +8673,28 @@
         <v>803.5</v>
       </c>
       <c r="M90">
-        <v>1737.524751758722</v>
+        <v>1757.269351210526</v>
       </c>
       <c r="N90">
-        <v>-934.0247517587222</v>
+        <v>-953.7693512105257</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-934.0247517587222</v>
+        <v>-953.7693512105257</v>
       </c>
       <c r="Q90">
-        <v>-906.6247517587223</v>
+        <v>-926.3693512105257</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5094953260675752</v>
+        <v>0.5516494466191729</v>
       </c>
       <c r="T90">
-        <v>8.492742739999914</v>
+        <v>9.264810261818088</v>
       </c>
       <c r="U90">
         <v>0.2091811058765187</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4624394554303168</v>
+        <v>0.4572435064928977</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2468526233582107</v>
+        <v>0.2484864344169759</v>
       </c>
       <c r="C91">
-        <v>-4088.615232440567</v>
+        <v>-4206.063150672318</v>
       </c>
       <c r="D91">
-        <v>3289.492584105043</v>
+        <v>3266.434641340098</v>
       </c>
       <c r="E91">
-        <v>6536.410269865149</v>
+        <v>6630.800245331954</v>
       </c>
       <c r="F91">
-        <v>8400.70781654561</v>
+        <v>8495.097792012415</v>
       </c>
       <c r="G91">
         <v>1022.6</v>
@@ -8755,28 +8755,28 @@
         <v>803.5</v>
       </c>
       <c r="M91">
-        <v>1757.269351210526</v>
+        <v>1777.01395066233</v>
       </c>
       <c r="N91">
-        <v>-953.7693512105257</v>
+        <v>-973.5139506623295</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-953.7693512105257</v>
+        <v>-973.5139506623295</v>
       </c>
       <c r="Q91">
-        <v>-926.3693512105257</v>
+        <v>-946.1139506623296</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5516494466191729</v>
+        <v>0.6022343912810904</v>
       </c>
       <c r="T91">
-        <v>9.264810261818088</v>
+        <v>10.1912912879999</v>
       </c>
       <c r="U91">
         <v>0.2091811058765187</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4572435064928977</v>
+        <v>0.452163023087421</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2484864344169759</v>
+        <v>0.2501202454757411</v>
       </c>
       <c r="C92">
-        <v>-4206.063150672318</v>
+        <v>-4323.190066268642</v>
       </c>
       <c r="D92">
-        <v>3266.434641340098</v>
+        <v>3243.697701210577</v>
       </c>
       <c r="E92">
-        <v>6630.800245331954</v>
+        <v>6725.190220798758</v>
       </c>
       <c r="F92">
-        <v>8495.097792012415</v>
+        <v>8589.487767479219</v>
       </c>
       <c r="G92">
         <v>1022.6</v>
@@ -8837,28 +8837,28 @@
         <v>803.5</v>
       </c>
       <c r="M92">
-        <v>1777.01395066233</v>
+        <v>1796.758550114133</v>
       </c>
       <c r="N92">
-        <v>-973.5139506623295</v>
+        <v>-993.258550114133</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-973.5139506623295</v>
+        <v>-993.258550114133</v>
       </c>
       <c r="Q92">
-        <v>-946.1139506623296</v>
+        <v>-965.858550114133</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6022343912810904</v>
+        <v>0.664060434756767</v>
       </c>
       <c r="T92">
-        <v>10.1912912879999</v>
+        <v>11.32365698666655</v>
       </c>
       <c r="U92">
         <v>0.2091811058765187</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.452163023087421</v>
+        <v>0.4471941986578889</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2501202454757411</v>
+        <v>0.2517540565345063</v>
       </c>
       <c r="C93">
-        <v>-4323.190066268642</v>
+        <v>-4440.002636180258</v>
       </c>
       <c r="D93">
-        <v>3243.697701210577</v>
+        <v>3221.275106765766</v>
       </c>
       <c r="E93">
-        <v>6725.190220798758</v>
+        <v>6819.580196265563</v>
       </c>
       <c r="F93">
-        <v>8589.487767479219</v>
+        <v>8683.877742946024</v>
       </c>
       <c r="G93">
         <v>1022.6</v>
@@ -8919,28 +8919,28 @@
         <v>803.5</v>
       </c>
       <c r="M93">
-        <v>1796.758550114133</v>
+        <v>1816.503149565937</v>
       </c>
       <c r="N93">
-        <v>-993.258550114133</v>
+        <v>-1013.003149565937</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-993.258550114133</v>
+        <v>-1013.003149565937</v>
       </c>
       <c r="Q93">
-        <v>-965.858550114133</v>
+        <v>-985.6031495659369</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.664060434756767</v>
+        <v>0.7413429891013632</v>
       </c>
       <c r="T93">
-        <v>11.32365698666655</v>
+        <v>12.73911410999988</v>
       </c>
       <c r="U93">
         <v>0.2091811058765187</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4471941986578889</v>
+        <v>0.4423333921507379</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2517540565345063</v>
+        <v>0.2533878675932714</v>
       </c>
       <c r="C94">
-        <v>-4440.002636180258</v>
+        <v>-4556.507334552478</v>
       </c>
       <c r="D94">
-        <v>3221.275106765766</v>
+        <v>3199.160383860351</v>
       </c>
       <c r="E94">
-        <v>6819.580196265563</v>
+        <v>6913.970171732369</v>
       </c>
       <c r="F94">
-        <v>8683.877742946024</v>
+        <v>8778.26771841283</v>
       </c>
       <c r="G94">
         <v>1022.6</v>
@@ -9001,28 +9001,28 @@
         <v>803.5</v>
       </c>
       <c r="M94">
-        <v>1816.503149565937</v>
+        <v>1836.24774901774</v>
       </c>
       <c r="N94">
-        <v>-1013.003149565937</v>
+        <v>-1032.74774901774</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-1013.003149565937</v>
+        <v>-1032.74774901774</v>
       </c>
       <c r="Q94">
-        <v>-985.6031495659369</v>
+        <v>-1005.347749017741</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7413429891013632</v>
+        <v>0.8407062732587008</v>
       </c>
       <c r="T94">
-        <v>12.73911410999988</v>
+        <v>14.55898755428557</v>
       </c>
       <c r="U94">
         <v>0.2091811058765187</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4423333921507379</v>
+        <v>0.4375771191168589</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2533878675932714</v>
+        <v>0.2550216786520366</v>
       </c>
       <c r="C95">
-        <v>-4556.507334552478</v>
+        <v>-4672.710458957418</v>
       </c>
       <c r="D95">
-        <v>3199.160383860351</v>
+        <v>3177.347234922215</v>
       </c>
       <c r="E95">
-        <v>6913.970171732369</v>
+        <v>7008.360147199172</v>
       </c>
       <c r="F95">
-        <v>8778.26771841283</v>
+        <v>8872.657693879633</v>
       </c>
       <c r="G95">
         <v>1022.6</v>
@@ -9083,28 +9083,28 @@
         <v>803.5</v>
       </c>
       <c r="M95">
-        <v>1836.24774901774</v>
+        <v>1855.992348469544</v>
       </c>
       <c r="N95">
-        <v>-1032.74774901774</v>
+        <v>-1052.492348469544</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-1032.74774901774</v>
+        <v>-1052.492348469544</v>
       </c>
       <c r="Q95">
-        <v>-1005.347749017741</v>
+        <v>-1025.092348469544</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8407062732587008</v>
+        <v>0.9731906521351512</v>
       </c>
       <c r="T95">
-        <v>14.55898755428557</v>
+        <v>16.98548547999984</v>
       </c>
       <c r="U95">
         <v>0.2091811058765187</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4375771191168589</v>
+        <v>0.4329220433815733</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2550216786520366</v>
+        <v>0.2566554897108018</v>
       </c>
       <c r="C96">
-        <v>-4672.710458957418</v>
+        <v>-4788.618136372963</v>
       </c>
       <c r="D96">
-        <v>3177.347234922215</v>
+        <v>3155.829532973476</v>
       </c>
       <c r="E96">
-        <v>7008.360147199172</v>
+        <v>7102.750122665978</v>
       </c>
       <c r="F96">
-        <v>8872.657693879633</v>
+        <v>8967.047669346439</v>
       </c>
       <c r="G96">
         <v>1022.6</v>
@@ -9165,28 +9165,28 @@
         <v>803.5</v>
       </c>
       <c r="M96">
-        <v>1855.992348469544</v>
+        <v>1875.736947921348</v>
       </c>
       <c r="N96">
-        <v>-1052.492348469544</v>
+        <v>-1072.236947921348</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-1052.492348469544</v>
+        <v>-1072.236947921348</v>
       </c>
       <c r="Q96">
-        <v>-1025.092348469544</v>
+        <v>-1044.836947921348</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9731906521351512</v>
+        <v>1.158668782562182</v>
       </c>
       <c r="T96">
-        <v>16.98548547999984</v>
+        <v>20.38258257599982</v>
       </c>
       <c r="U96">
         <v>0.2091811058765187</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4329220433815733</v>
+        <v>0.4283649692407145</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2566554897108018</v>
+        <v>0.258289300769567</v>
       </c>
       <c r="C97">
-        <v>-4788.618136372963</v>
+        <v>-4904.236328920408</v>
       </c>
       <c r="D97">
-        <v>3155.829532973476</v>
+        <v>3134.601315892834</v>
       </c>
       <c r="E97">
-        <v>7102.750122665978</v>
+        <v>7197.140098132782</v>
       </c>
       <c r="F97">
-        <v>8967.047669346439</v>
+        <v>9061.437644813243</v>
       </c>
       <c r="G97">
         <v>1022.6</v>
@@ -9247,28 +9247,28 @@
         <v>803.5</v>
       </c>
       <c r="M97">
-        <v>1875.736947921348</v>
+        <v>1895.481547373151</v>
       </c>
       <c r="N97">
-        <v>-1072.236947921348</v>
+        <v>-1091.981547373151</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-1072.236947921348</v>
+        <v>-1091.981547373151</v>
       </c>
       <c r="Q97">
-        <v>-1044.836947921348</v>
+        <v>-1064.581547373151</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.158668782562182</v>
+        <v>1.436885978202728</v>
       </c>
       <c r="T97">
-        <v>20.38258257599982</v>
+        <v>25.47822821999979</v>
       </c>
       <c r="U97">
         <v>0.2091811058765187</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4283649692407145</v>
+        <v>0.4239028341444572</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.258289300769567</v>
+        <v>0.2599231118283322</v>
       </c>
       <c r="C98">
-        <v>-4904.236328920408</v>
+        <v>-5019.570839372107</v>
       </c>
       <c r="D98">
-        <v>3134.601315892834</v>
+        <v>3113.656780907939</v>
       </c>
       <c r="E98">
-        <v>7197.140098132782</v>
+        <v>7291.530073599585</v>
       </c>
       <c r="F98">
-        <v>9061.437644813243</v>
+        <v>9155.827620280046</v>
       </c>
       <c r="G98">
         <v>1022.6</v>
@@ -9329,28 +9329,28 @@
         <v>803.5</v>
       </c>
       <c r="M98">
-        <v>1895.481547373151</v>
+        <v>1915.226146824955</v>
       </c>
       <c r="N98">
-        <v>-1091.981547373151</v>
+        <v>-1111.726146824955</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-1091.981547373151</v>
+        <v>-1111.726146824955</v>
       </c>
       <c r="Q98">
-        <v>-1064.581547373151</v>
+        <v>-1084.326146824955</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.436885978202725</v>
+        <v>1.900581304270299</v>
       </c>
       <c r="T98">
-        <v>25.47822821999972</v>
+        <v>33.97097095999963</v>
       </c>
       <c r="U98">
         <v>0.2091811058765187</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4239028341444572</v>
+        <v>0.4195327018336896</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2599231118283322</v>
+        <v>0.2615569228870974</v>
       </c>
       <c r="C99">
-        <v>-5019.570839372107</v>
+        <v>-5134.627316439749</v>
       </c>
       <c r="D99">
-        <v>3113.656780907939</v>
+        <v>3092.990279307102</v>
       </c>
       <c r="E99">
-        <v>7291.530073599585</v>
+        <v>7385.920049066391</v>
       </c>
       <c r="F99">
-        <v>9155.827620280046</v>
+        <v>9250.217595746852</v>
       </c>
       <c r="G99">
         <v>1022.6</v>
@@ -9411,28 +9411,28 @@
         <v>803.5</v>
       </c>
       <c r="M99">
-        <v>1915.226146824955</v>
+        <v>1934.970746276759</v>
       </c>
       <c r="N99">
-        <v>-1111.726146824955</v>
+        <v>-1131.470746276759</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-1111.726146824955</v>
+        <v>-1131.470746276759</v>
       </c>
       <c r="Q99">
-        <v>-1084.326146824955</v>
+        <v>-1104.070746276759</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.900581304270299</v>
+        <v>2.827971956405449</v>
       </c>
       <c r="T99">
-        <v>33.97097095999963</v>
+        <v>50.95645643999944</v>
       </c>
       <c r="U99">
         <v>0.2091811058765187</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4195327018336896</v>
+        <v>0.4152517558966111</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2615569228870974</v>
+        <v>0.2631907339458626</v>
       </c>
       <c r="C100">
-        <v>-5134.627316439749</v>
+        <v>-5249.411259853443</v>
       </c>
       <c r="D100">
-        <v>3092.990279307102</v>
+        <v>3072.596311360213</v>
       </c>
       <c r="E100">
-        <v>7385.920049066391</v>
+        <v>7480.310024533194</v>
       </c>
       <c r="F100">
-        <v>9250.217595746852</v>
+        <v>9344.607571213655</v>
       </c>
       <c r="G100">
         <v>1022.6</v>
@@ -9493,28 +9493,28 @@
         <v>803.5</v>
       </c>
       <c r="M100">
-        <v>1934.970746276759</v>
+        <v>1954.715345728562</v>
       </c>
       <c r="N100">
-        <v>-1131.470746276759</v>
+        <v>-1151.215345728562</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-1131.470746276759</v>
+        <v>-1151.215345728562</v>
       </c>
       <c r="Q100">
-        <v>-1104.070746276759</v>
+        <v>-1123.815345728562</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.827971956405449</v>
+        <v>5.610143912810898</v>
       </c>
       <c r="T100">
-        <v>50.95645643999944</v>
+        <v>101.9129128799989</v>
       </c>
       <c r="U100">
         <v>0.2091811058765187</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4152517558966111</v>
+        <v>0.4110572937158373</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2631907339458626</v>
-      </c>
-      <c r="C101">
-        <v>-5249.411259853443</v>
-      </c>
-      <c r="D101">
-        <v>3072.596311360213</v>
-      </c>
-      <c r="E101">
-        <v>7480.310024533194</v>
-      </c>
-      <c r="F101">
-        <v>9344.607571213655</v>
-      </c>
-      <c r="G101">
-        <v>1022.6</v>
-      </c>
-      <c r="H101">
-        <v>7574.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>830.9</v>
-      </c>
-      <c r="K101">
-        <v>27.4</v>
-      </c>
-      <c r="L101">
-        <v>803.5</v>
-      </c>
-      <c r="M101">
-        <v>1954.715345728562</v>
-      </c>
-      <c r="N101">
-        <v>-1151.215345728562</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-1151.215345728562</v>
-      </c>
-      <c r="Q101">
-        <v>-1123.815345728562</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.610143912810898</v>
-      </c>
-      <c r="T101">
-        <v>101.9129128799989</v>
-      </c>
-      <c r="U101">
-        <v>0.2091811058765187</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2091811058765187</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4110572937158373</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
